--- a/subnet_issues.xlsx
+++ b/subnet_issues.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,20 +439,35 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>답변자</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>요청사항</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>원인</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>해결방법</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
@@ -460,121 +475,5282 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17406</v>
+        <v>17433</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Question about Unaccounted Node Memory Usage on AIStor Nodes</t>
+          <t>Compatibility of ILM Tiering and Bucket Replication Across Different AIStor Versions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim03:04 PM</t>
+          <t>Youngkyoo Kim05:06 PM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>메모리 불일치</t>
+          <t>Jeeva</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MinIO AIStor 파드와 커널 메모리 사용을 추적한다</t>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>추가 정보 필요</t>
+          <t>고객이 핫 클러스터와 워 arm 클러스터가 서로 다른 AIStor 버전을 사용할 때 ILM 티어링이나 버킷 복제에 호환성 문제가 있는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://subnet.min.io/issues/17406</t>
+          <t>ILM 티어링은 표준 S3 연산만 사용하기 때문에 버전 차이가 영향을 주지 않지만, 복제는 버전마다 스키마나 메타데이터가 달라질 수 있어 호환성에 영향을 줄 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ILM 티어링은 2026.02(핫)와 2026.06(워 arm) 두 버전을 사용해도 호환성 문제가 없으며, 복제의 경우 두 클러스터가 동일한 버전을 실행하도록 권장합니다.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17433</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17404</v>
+        <v>17431</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Question About XMinioStorageFull Error</t>
+          <t>Question About Selecting All Folders and Objects in an AIStor Bucket</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>jungkeunlee09:53 AM</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>이슈는 드라이브가 가득 찬 것과 같은 비슷한 조건(쓰기 쿼럼 충족 실패)에서 XMinioStorageFull이 발생함. 현재 드라이브 사용률 89%이므로 실제 용량 초과는 아니며, 임시적인 드라이브 타임아웃·오프라인·힐링·네트워크 지연이 주된 원인.</t>
-        </is>
-      </c>
+          <t>jungkeunlee03:49 PM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1. 에러가 발생한 타임스탬프를 중심으로 각 노드의 journalctl 로그를 필터링해 드라이브 타임아웃, 오프라인, 힐링, 네트워크 지연 메시지 확인. 2. mc admin info &lt;alias&gt; 를 같은 시점에 실행해 드라이브 상태(online/offline/healing) 확인. 3. Prometheus 메트릭( minio_node_drive_latency_us, drive_used_bytes/total_bytes, drive_online_status )을 통해 드라이브 지연과 상태 변화를 모니터링. 4. 로그·메트릭에서 드라이브 타임아웃이 감지되면 max_timeout 값을 45~60초로 일시 증가시켜 재시도 후 타임아웃 발생을 완화.</t>
+          <t>애플리케이션(Application)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>preallocate 옵션은 파일 전용 공간을 미리 예약하지만 현재 문제와는 무관. max_timeout은 드라이브가 응답 지연 시 해당 드라이브를 실패 처리하도록 하는 임계값. 값을 높이면 타임아웃이 줄어들지만 실제로 느린 드라이브가 있을 경우 전체 클러스터 지연이 증가함. 따라서 로그에 타임아웃 증거가 없으면 변경하지 않는 것이 안전함. 5. 드라이브 사용률이 95% 목표에 근접할 때는 평균이 아닌 가장 높은 드라이브 사용률을 기준으로 알람을 설정하고, 재배치 후 힐링을 주기적으로 실행해 드라이브 간 사용률 편차를 최소화함. 6. 대량 소형 객체를 저장할 경우 최소 10,000개의 여유 인덱스가 확보되는지 확인. 7. 클러스터에 5xx, read/write quorum 오류가 지속적으로 발생하면, support profile 수집(각 노드의 /var/log/minio/*.log, /proc/meminfo, /proc/diskstats, /proc/interrupts 등) 및 MinIO 지원팀에 제출함. 8. 필요 시 MinIO 버전을 최신으로 업데이트하고, 하드웨어(SSD/HDD)와 펌웨어가 최신인지 확인함.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://subnet.min.io/issues/17404</t>
+          <t>사용자가 현재 사용 중인 MinIO 버전을 확인해 달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17431</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>17430</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Question About Selecting All Buckets in the AIStor Web Console</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kranthi03:56 PM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>이슈가 #17431과 중복되는 것 같으므로, #17431에서 논의를 계속하도록 제안합니다.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17430</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>17428</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Questions Regarding Memory Usage of MinIO Pods on a Specific Node</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>jungkeunlee09:05 AM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>고객은 MinIO pod의 RES 값이 노드마다 차이가 크고, buff/cache 메모리가 많이 차지하고 있는 상황을 보고, 메트릭이 해당 메모리를 포함하는지 확인하고 싶어했습니다. 또한 128-node 클러스터에서 일부 노드만 지속적으로 RSS가 3–5배 높은 이유와, 이러한 패턴이 서비스에 영향을 미칠 수 있는지 궁금해했습니다. 더불어 MinIO가 클라이언트 요청 이외에 내부 백그라운드 프로세스를 실행해 메모리를 더 사용하도록 하는지 물었습니다.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MinIO는 O_DIRECT 설정으로 인해 메타데이터 I/O가 페이지 캐시를 사용하고, 클러스터 전체에서 한 노드가 리더 락을 잡아 데이터-유스 스캐너와 배치 작업, 복제 리셈과 같은 백그라운드 서비스를 실행하기 때문에 RSS가 비정상적으로 높아집니다. 이러한 서비스는 리더 노드에서만 한 번씩 실행되므로 동일한 노드가 며칠간 높은 RSS를 보입니다. 또한 CPU 사용량이 높은 노드에서는 요청 수가 많아 에러리언과 I/O 버퍼가 메모리를 더 차지합니다.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>고객은 K8s 메모리 리밋을 지정하거나 서버 설정 파일에서 memLimit을 설정해 MinIO 프로세스의 메모리 사용을 제한할 수 있습니다. 또한 mc support profile --type mem,goroutines를 사용해 힙 프로파일을 캡처하고, mc admin info --json으로 리더 노드를 확인해 높은 RSS가 리더 락과 관련된 백그라운드 서비스 때문임을 검증하면 됩니다.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17428</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17406</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Question about Unaccounted Node Memory Usage on AIStor Nodes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim03:04 PM</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>네트워크(Network)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>고객은 AIStor 실행 중 Kubernetes 노드에서 메모리 사용량이 비정상적으로 높아지는 현상을 발견하고, MinIO 팀이 AIStor 관련 메모리 사용 현상을 인지하고 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NIC 드라이버 ice에서 발생한 CVE-2025-39948 버그로 커널 페이지 할당이 누수되어 약 560 GiB의 메모리가 비가시적으로 소비됩니다.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>커널을 6.12.0-55.72.1.el10_0 이상으로 업데이트하고 재부팅하면 누수된 메모리가 해제됩니다.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>해당 문제는 AIStor 자체와 무관하며, 재부팅 시 메모리 누수가 정리됩니다.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17406</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17404</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Question About XMinioStorageFull Error</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>jungkeunlee09:53 AM</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sarat Chandra</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>고객은 XMinioStorageFull 오류의 정확한 원인을 알고 싶습니다. 또한, 드라이브 사용량 임계값을 확인하고 조정할 수 있는지 여부를 문의했습니다. 마지막으로, max_timeout과 preallocate 옵션을 변경하면 서비스 성능에 어떤 영향을 미칠지 궁금합니다.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MinIO는 각 드라이브가 99% 사용량에 도달하면 쓰기를 일시적으로 중단하고, 특정 erasure set에 충분한 드라이브가 없으면 XMinioStorageFull 오류를 반환합니다. 고객 환경에서는 드라이브가 89% 사용량에 머물러 있지만, 일시적인 타임아웃이나 온라인 상태 변화로 인해 쿼럼이 깨져 오류가 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>로그와 메트릭을 수집해 드라이브 타임아웃·오프라인 현황을 확인하고, 필요 시 max_timeout 값을 45–60초로 늘려 타임아웃으로 인한 드라이브 드롭을 줄입니다. preallocate 옵션은 성능에 영향을 미치지 않으므로 변경하지 않습니다. 평균 95% 사용을 목표로 한다면 드라이브 수준에서 사용률을 모니터링하고, 스케일업 전에 가장 높은 드라이브가 99%를 넘지 않도록 확장합니다.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>추가 로그 및 메트릭 수집이 필요하다.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17404</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>17395</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Question About Goroutine Increase</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>jungkeunlee02:50 PM</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>12:35에 발생한 multipart upload 및 delete 요청으로 인해 디스크 I/O가 급증해 I/O 큐가 포화상태에 도달하면서 MinIO의 각 작업별 goroutine이 정상적으로 종료되지 못함. 결과적으로 12:50경에 goroutine 수가 20k에서 40k~60k로 급증했고, I/O 큐 Max는 420까지 상승했다. I/O 부하가 감소하면서 goroutine 수는 15:04경에 20k 이하로 복구됨.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1. 디스크 I/O 큐 및 대기열 메트릭(수집 포인트: minio_system_process_go_routine_total, disk_io_queue_max)을 지속적으로 모니터링하여 I/O 부하와 goroutine 수를 동시 비교함. 2. 부하가 급증할 수 있는 대량 요청(멀티파트 업로드, 대량 delete 등)에 대해 API QoS를 활성화하거나 스로틀링을 적용해 I/O와 네트워크 대역폭을 제한함. 3. 드라이브 slow 경고가 발생하면 즉시 대응하고, 필요시 디스크 교체 또는 스토리지 성능을 업그레이드함. 4. mc support profile --type goroutines 를 문제 발생 시점에 즉시 실행하여 자세한 goroutine 스택을 확보함. 5. 클러스터 전체에서 goroutine 증가가 분산되는지, 특정 노드에 집중되는지를 확인해 스캐너/복제 작업의 부하를 평가함.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>500 에러와 quorum 에러가 발생했으나 서비스에는 영향이 없었음. 현재 운영은 지속 가능하지만, API QoS 설정 및 성능 모니터링을 통해 재발 방지 권장. 128노드 이상으로 확장 예정이므로 각 노드의 I/O와 goroutine 사용률을 독립적으로 모니터링할 수 있는 다중 인스턴스 메트릭 수집을 설정함.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kranthi, Thomas</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>사용자는 12:35에 발생한 대량 요청이 12:50 이후에 goroutine 수를 급증시킬 수 있는지, 문제를 추적할 수 있는 방법, 그리고 API QoS 설정이 문제를 완화할 수 있는지 물었습니다.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Prometheus v3 메트릭을 활용해 서버별 go_routine 수를 모니터링하고, 과거 요청률을 기준으로 API QoS에서 RPS와 concurrency를 제한하여 디스크 부하를 낮추며, 15‑20% 여유를 두고 설정해 정상 동작을 유지하도록 조정합니다.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>환경이 에어갭 상태여서 로그 및 프로파일 파일을 업로드할 수 없으며, 클러스터 전체에 대해 프로파일링이 가능해 특정 노드만을 대상으로 할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17395</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>17388</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MinIO Memory Usage Increases as Object Count Grows</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RIA CHOI04:54 PM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kranthi, Jiuker</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>고객이 MinIO 서버가 객체 수가 증가함에 따라 메모리 사용량이 상승하고, 내부 메모리 관리 또는 임계값이 있는지, 그리고 메모리 사용이 계속 증가할 경우 어떤 조치를 취해야 할지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MinIO의 메모리 사용은 객체 수에 비례하지 않고 작업 부하에 따라 변동하며, 현재 Pod 메모리 제한 128 GiB 안에서 3~7 GiB 사이를 오가고 있습니다.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>메모리 사용이 90% 이하로 안정되면 정상으로 판단하고, 90%를 초과하며 지속적으로 상승하면 병렬 작업을 줄이거나 Pod 메모리 제한을 늘려야 합니다.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17388</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>17386</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ILM Tiering: Source Storage Usage Remains Unchanged</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RIA CHOI10:36 AM</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ali Yaldaz</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RIA CHOI는 객체가 워밍 트리에 성공적으로 전환되었음에도 원본 클러스터의 저장소 사용량이 감소하지 않는 것이 정상인지 궁금해했습니다. 또한, 전환 후 실제로 핫 티어에서 객체가 삭제되었는지 확인하고 회수된 저장 용량을 보는 방법을 요청했습니다. 그리고 대상 클러스터에서 객체 수와 사용량이 증가했다가 감소하는 현상에 대한 설명을 구했습니다.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>트리거는 데이터의 물리적 위치만 변경하므로 논리적 사용량 카운터는 여전히 전체 객체 크기를 그대로 표시합니다. 전환된 객체의 메타데이터가 핫 티어에 남아 있어 스캐너가 다음 주기까지 물리적 공간이 해제되는 것을 반영하지 못합니다. 콘솔에서 보여지는 드라이브 기반 수치는 회수된 공간을 나타내지만, 버킷 사용량은 변하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>핫 티어 노드의 드라이브 자유 공간(예: df 또는 zmc admin info)을 확인해 회수된 용량을 파악합니다. mc ilm tier info를 사용해 각 티어별 사용량과 객체 수를 보고, mc stat으로 객체의 스토리지 클래스를 확인합니다. 멀티파트 업로드나 덮어쓰기가 발생하면 대상 클러스터 사용량이 일시적으로 증가한 뒤 24시간 후 자동 정리로 감소합니다.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17386</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>17358</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Inquiry About Prefix-Level Metrics, Quotas, and ILM Support</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:33 AM</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Jiuker, Prakash</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>The user requests confirmation of current and planned support for prefix-level metrics such as storage usage, object count, API activity, quota, owner, usage statistics, alias mappings, and the ability to create and manage prefixes ahead of time like directories.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Currently there are no real-time prefix-level metrics or metadata.
+Inventory generation provides periodic data only.
+Prefixes are treated as part of the flat object namespace rather than as folders.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Use the ILM UI and the 'mc inventory generate' command to obtain prefix-level object count and size, though this data is periodic.
+The 'mc du' command can calculate usage, but it is not recommended for large prefixes due to high I/O load.
+Prefix-level quota, owner, usage statistics, and pre-creation of prefixes are not supported at this time.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17358</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>17349</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Using Apache Polaris as an external authorization service</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RIA CHOI04:58 PM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kranthi</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RIA CHOI는 AIStor IAM 관리 오버헤드를 줄이기 위해 Apache Polaris와의 연동을 통해 Polaris가 권한 부여를 처리할 수 있는 방법이 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Polaris가 테이블 카탈로그 수준에서 권한을 조회하고 AIStor가 S3 객체 수준에서 권한을 확인하기 때문에 두 시스템 간 연동이 복잡하고 번역 오버헤드가 발생합니다. 이러한 차이로 인해 통합이 단순화 목표를 달성하지 못할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AIStor는 외부 시스템에 접근 관리를 위임할 수 있는 Authorization Plugin을 제공하며, 이를 활용해 외부 인증 서비스를 연결할 수 있습니다. 하지만 Polaris와 AIStor의 레벨 차이로 인한 변환 오버헤드를 고려하면 AIStor 테이블 기반 PBAC를 권장합니다. 필요 시 AIStor 테이블에 대한 데모를 제공할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Kranthi는 AIStor 테이블을 활용하면 카탈로그 레이어 오버헤드를 제거하고 PBAC를 단일 포인트로 관리할 수 있다고 안내했습니다.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17349</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17348</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Inventory report generation ignores bucket quota limits</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RIA CHOI03:54 PM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kranthi</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>고객이 버킷이 할당량을 초과했음에도 인벤토리 보고서가 계속 작성되는 현상이 예상되는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MinIO AIStor의 할당량 검증은 내부 스캐너에 의해 주기적으로 수행되며, 인벤토리 같은 내부 프로세스는 현재 할당량 적용 대상이 아닙니다.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>인벤토리 프로세스는 할당량이 적용되지 않으므로 현재 그대로 사용하며, 향후 필요 시 문서에 추가 정보를 제공하도록 했습니다.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17348</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>17342</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Best Practices for Client Request Distribution in Large MinIO Workloads</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RIA CHOI10:46 AM</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kranthi</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>사용자는 AIStor가 대규모 쿠버네티스 환경에서 사용될 때 가장 적합한 로드 밸런싱 방식을 찾고자 한다. 특히 AIStor 전용 튜닝 파라미터, 클라이언트 측 설정(연결 풀, Keep-Alive, 멀티파트 등), 그리고 워크로드 특성이 로드 분포와 대역폭에 미치는 영향에 대한 권장사항을 요청했다. 또한 ECMP와 같은 서버‑사이드 로드 밸런싱을 활용한 베스트 프랙티스와 참조 아키텍처를 원한다.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>로드 밸런싱이 제대로 구성되지 않거나 단일 엔드포인트에 대한 요청이 특정 노드에 집중될 때, 요청이 균등하게 분산되지 않는다. 특히 지속적인 HTTP 연결 재사용은 특정 노드에 트래픽을 몰아 집중도를 높인다. 현재 사용 중인 로드 밸런싱 옵션(인그레스, Cilium BGP, Global Service)이 요청 분산을 충분히 지원하지 못해 이 문제가 발생한다.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MinIO는 일반 S3 클라이언트에게는 서버‑사이드 LB를 사용할 때 무작위(random) 선택 알고리즘을 권장한다. 그러나 Spark, Trino 같은 제한된 클라이언트의 경우 요청 수준에서 균등 분산을 보장하기 위해 Sidekick을 사용하도록 권장한다. Sidekick에서는 --host-balance 옵션을 'random'으로 설정하거나 기본 least를 활용해 요청 레벨에서 분산을 개선할 수 있다.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17342</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17316</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Empty prefix appears in mc ls, but cannot be removed with mc rm -r --force</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RIA CHOI03:24 PM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Jiuker</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>고객은 빈 디렉터리 접두사가 삭제 후에도 남아 있는 이유와 --purge 옵션을 사용해야만 완전 삭제가 가능한 이유를 이해하고 싶어하며, 이를 완전히 제거하는 방법을 알고 싶어합니다.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>mc rm 명령이 --purge 옵션 없이 실행되면 일부 디스크에서 동기화가 완전히 이루어지지 않아 남은 디렉터리 엔트리가 남게 됩니다. 이는 버전이 비활성화된 버킷에서도 발생할 수 있으며, --purge는 모든 디스크에 물리적 삭제를 강제해 이러한 잔여 항목을 제거합니다.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>mc rm -r --force --purge alias/bucket/prefix1/prefix2 명령을 사용하여 물리적으로 삭제를 강제하면 빈 디렉터리 접두사가 완전히 제거됩니다. 버전이 비활성화되어 있으므로 삭제 마커가 없으므로 위험이 최소화됩니다.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17316</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>17281</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DirectPV Repair Job Fails with "unable to verify license; no license found" on DirectPV 5.0.2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Jiuker02:11 PM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>RIA CHOI가 DirectPV 5.0.2에서 발생한 드라이브 오류와 라이선스 체크로 인한 복구 실패를 해결하기 위해 업그레이드 및 복구 절차를 문의했고, 오류 드라이브를 재활성화하고 조건 로그를 정리하는 방법을 요청했다.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DirectPV 5.0.2는 여전히 라이선스 Secret을 요구하므로 복구 작업이 실패하며, 드라이브가 파일시스템 오류로 Error 상태에 머무를 때는 DirectPV가 드라이브를 자동으로 Ready로 전환하지 못한다.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>DirectPV를 5.1.0+ 버전으로 업그레이드한 뒤, 드라이브를 suspend → repair → resume 순으로 복구하고, xfs_repair 후 node-server를 재시작한다. 직접 상태를 Ready로 변경하려면 kubectl patch 명령으로 status.conditions를 비워 주고 node-server를 재시작해 재조정하도록 한다.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DirectPVDrive 리소스 이름은 UUID가 아니라 드라이브 ID이며, 조건 로그를 정리할 때는 --subresource=status 옵션이 필요하다.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17281</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17274</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IAM Global Lock Suspected in AttachDetachPolicyLDAP API Delay</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim09:31 AM</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Jiuker</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>고객은 AttachDetachPolicyLDAP API가 40~50초 동안 지연되는 원인을 파악하기 위해 필요한 추가 메트릭과 로그를 요청했습니다. 특히, IAM 서브시스템이 전역 잠금을 획득할 때 다른 API 요청에 미치는 영향과 잠금 대기 큐 길이를 확인하고자 합니다. 또한, 이 연산이 비즈니스 시간대에 수행되는 것이 적절한지 여부도 궁금합니다.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AttachDetachPolicyLDAP는 정책 매핑 시 쓰기 잠금을 획득하며, 대량 요청이 동일 노드에서 처리될 때 잠금 대기 시간이 길어져 전체 요청 지연이 발생합니다. 이로 인해 Goroutine 수가 급증하고, 10~50초의 응답 시간이 기록됩니다.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17274</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17269</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Question regarding "Create a new path" in Object Browser</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Kannappan11:43 AM</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Prakash</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>사용자는 객체 브라우저에서 ‘새 경로 만들기’ 기능이 실제 접두어를 생성하는지, 혹은 이후 객체 업로드를 위한 논리적 경로만 제공하는지에 대해 명확히 해달라고 요청했다. 또한 mc mb 명령으로 생성된 빈 접두어가 0바이트 객체인지, 이로 인해 충돌이 발생할 가능성이 있는지 궁금했다.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>mc mb 또는 객체 브라우저에서 경로를 만들면 AIStor에 0바이트 길이의 접두어(폴더 마커) 객체가 생성된다. 이 객체는 실제 디렉터리로서 존재하지만, 나중에 동일한 접두어로 객체를 업로드하면 충돌이 발생한다.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>접두어를 만들 때는 mc mb 같은 명령을 사용하지 말고, 객체를 업로드할 때 접두어 경로를 함께 지정해 자동으로 생성되도록 한다. 이미 존재하는 0바이트 접두어가 있다면 삭제하고, ls -r --versions 로 충돌 여부를 확인한다. 이 방법이 충돌을 방지한다.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>콘솔에서도 접두어를 만들면 객체를 업로드해야만 유지되도록 설계된 것이므로, 이는 의도된 동작임을 명시하였다.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17269</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17268</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Correlation between high goroutine count and quorum loss errors</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:13 AM</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Jiuker</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>고객은 10.6 PiB 규모의 클러스터에서 ListObjectsV2 요청이 많아 goroutine 수가 급증하고, 이로 인해 일시적인 quorum loss 오류가 발생하는지 궁금합니다.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>다수의 ListObjectsV2 요청이 클러스터에 과부하를 주어 goroutine 수가 급증했고, 이로 인해 노드/드라이브가 오프라인으로 표시되고 5xx 오류와 quorum loss가 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17268</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17267</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Request for AIStor Binaries which has NFS feature</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim09:58 AM</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Arvind Gupta</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>고객이 AIStor에서 NFS 기능을 테스트하고자 하여 필요한 바이너리를 제공해달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>AIStor는 기본적으로 NFS를 지원하지 않는다는 것이 명시되었습니다.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17267</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17191</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Restrict Delete Access to Table Paths Only Using S3 Policy</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RIA CHOI01:25 PM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>사용자가 Polaris를 통해 DB 경로를 삭제하지 못하도록 하고, 테이블 경로만 삭제를 허용하는 S3 정책이 가능한지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>S3 정책에서는 경로를 단일 수준으로 제한할 수 없으며, 모든 객체가 개별적으로 삭제되기 때문에, 디렉터리 수준에서 삭제를 차단하려면 deny가 모든 하위 객체를 차단해 버립니다.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sentinel 파일을 DB 생성 시 넣어 DB 디렉터리를 남겨 두고, S3 정책에서 "s3:DeleteObject"를 두 단계 아래 객체에만 허용하도록 설정하며 sentinel 파일 삭제를 deny하고, Sentinel 파일은 특권 아이덴티티로만 생성하도록 조치했습니다.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sentinel 방식을 사용하면 버전링 없이도 DB 디렉터리가 사라지는 문제를 해결할 수 있고, Polaris를 통한 삭제만을 권장해 근본적인 원인을 차단합니다.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17191</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17179</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inquiry regarding NFS/POSIX shared filesystem layer support in AIStor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim11:26 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>고객은 MinIO AIStor가 AWS S3 Files와 비슷한 NFS/POSIX 공유 파일 시스템 레이어 기능을 지원하는지, 혹은 향후 로드맵에 포함될 예정인지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17179</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>17178</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Inquiry regarding high-frequency HealObject events in MinIO Audit Logs</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:50 AM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kranthi</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>고객이 감사 로그에서 높은 빈도로 발생하는 HealObject 이벤트가 정상적인 동작인지 확인해 달라고 요청했습니다. 또한 업그레이드 전까지 이 메시지를 무시해도 되는지 묻는 질문도 함께 했습니다.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>해당 로그는 실제로 복구가 수행되지 않았음에도 불구하고 로그에 기록되는 버그로 인해 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>RELEASE.2026-04-11 이상의 버전으로 업그레이드하면 이 로그 스팸이 사라집니다. 업그레이드 전까지는 해당 메시지를 안전하게 무시해도 됩니다.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>고객이 현재 저장소 사용률이 92%에 달하며, 인오드 사용량을 확인할 것을 권장했습니다.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17178</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>17167</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>error: missing request or run metadata for job</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RIA CHOI10:47 AM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Deepak Thimmaiah</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>고객이 inventory 작업을 실행 중에 삭제했을 때 발생하는 오류 메시지와 원인, 해결 방법을 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>삭제 명령이 실행 중인 inventory 작업의 내부 상태를 제거하지 않아, 상태 조회 시 메타데이터가 없다는 오류가 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>먼저 mc inventory cancel 명령으로 실행 중인 작업을 정상적으로 중지한 뒤, mc inventory rm 명령으로 작업 구성을 삭제합니다.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17167</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>17142</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MinIO Node NotReady Events with System OOM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RIA CHOI06:15 PM</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>고객이 18개의 MinIO 노드 중 2개의 노드가 30분간 NotReady 상태가 되면서 OOM 이벤트가 발생하고, Spark executor가 설치되었으나 메모리 사용량이 크게 보이지 않아 원인 파악을 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>500GB 노드의 inode 캐시(xfs_inode)와 lsm_inode_cache가 305GB에 달해 메모리 절대량을 차지하고, MinIO가 19%(약 95GB) 메모리를 사용하며 Spark 실행이 72GB를 추가로 차지해 총 470GB가 되면서 커널 OOM이 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AIStor 노드에서 Spark 실행을 중지하고, Spark 파드에 실제 메모리 요청/제한을 설정하며, 필요 시 MinIO 포드를 일시 중지 후 drop_caches를 실행해 inode 캐시를 해제하고, 노드 메모리를 늘리는 것을 검토합니다.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17142</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>17140</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>http-minio and management ports on MinIO service</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RIA CHOI09:51 AM</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>javier</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>사용자는 minio 서비스가 포트 9000에 두 개의 포트 이름(http‑minio와 management)을 가지고 있음을 발견하고, 각 포트 이름의 의도된 목적과 내부 사용자에게는 어떤 엔드포인트를 사용해야 하는지를 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>포트 9000에 두 개의 포트 이름이 지정되어 있어 혼란이 생긴 상태이며, 관리 포트 이름이 MinIO Operator에 의해 정의되지 않은 점이 불확실성을 높였습니다.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Javier는 MinIO Operator가 정의한 표준 포트 이름을 설명하고, 내부 사용자는 객체 작업을 위해 http‑minio(또는 TLS가 활성화된 경우 https‑minio) 포트 9000을 사용해야 함을 안내했습니다. 관리 포트 이름은 정의되지 않았으므로 Cesar Celis에게 확인을 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17140</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>17139</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>error operation lock timed out</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RIA CHOI09:37 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>javier</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ria가 'operation lock timed out' 오류가 무엇을 의미하며, 왜 그로 인해 포드에서 goroutine이 급증했는지를 설명해 달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>이 오류는 포드가 분산 락을 획득하는 데 필요한 정족수를 일정 시간 안에 충족하지 못했음을 나타내며, 흔한 원인은 락을 보유한 장기 작업, 포드 간 일시적 네트워크 지연, 또는 느린 디스크 I/O입니다.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>우리는 문제를 모니터링하고, 재발 시 해당 포드의 로그를 수집한 뒤 'mc admin profile --type goroutine' 명령으로 블로킹 작업을 확인하도록 권고했습니다. 빈번하게 발생하지 않는 한 즉각적인 조치는 필요하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17139</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>17116</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MinIO capacity metrics increased during node drain</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim09:31 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kranthi</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>고객이 노드 드레인 중 메트릭이 상승한 것이 정상인지 확인 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>드레인된 드라이브가 0 총 공간 보고 시 메트릭 계산이 불량해져 다른 풀의 공간이 포함돼 값이 상승했습니다. 이 버그는 다중 풀 환경에서 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Kranthi가 버그를 찾고 고친 버전을 릴리스했습니다. 고객은 새 버전으로 업그레이드하면 정상됩니다.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17116</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>17077</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Inquiry: MinIO healing delay and write_tolerance metric discrepancy</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:46 AM</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>고객이 디스크 교체 후 복구 중에 minio_cluster_erasure_set_write_tolerance 메트릭이 3에서 4로 증가한 이유와 복구 속도를 높이기 위한 설정 조정 방법을 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>복구가 진행될 때 MinIO는 손상된 드라이브 수에 따라 parity를 1씩 증가시켜 쓰기 허용 오류 수를 3에서 4로 높이는 동작을 수행합니다.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>heal 서브시스템의 max_sleep, max_io, drive_workers 값을 낮추고 서비스 재시작해 복구 속도를 높이며, 클러스터 활용률이 70%일 때 I/O 대기 시간이 병목인지 모니터링하도록 안내했습니다.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>I/O 대기 시간이 병목이 될 가능성이 있으므로, 드라이브 읽기 지연을 관찰해 설정을 조정해야 합니다.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17077</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>17065</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>vm.min_free_kbytes</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim09:55 AM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Kranthi</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>네트워크(Network)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim은 Cilium BGP가 10초간 연결이 끊겼다가 1분 뒤 재연결하면서 5xx 오류가 발생하고 GFP_ATOMIC 할당 오류를 관찰했다고 보고했습니다. Red Hat은 메모리 부족을 의심하며 vm.min_free_kbytes 값을 두 배 또는 네 배로 늘리면 AIStor 측에 영향을 미칠 수 있는지 확인해 주실 것을 요청했습니다. 따라서 그는 AIStor 측에 이 값을 증가시켜도 문제가 발생하지 않는지 검증해 주길 바랍니다.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Kranthi는 AIStor가 vm.min_free_kbytes에 대한 구체적 권장 사항이 없으며, 표준 기준에 따라 값을 증가시킬 수 있다고 답변했습니다. 그는 또한 transparent_hugepage와 같은 다른 메모리 매개변수를 검토할 것을 제안했습니다. 그리고 비프로덕션 환경에서 먼저 테스트해 보고 결과를 관찰할 것을 권고했습니다.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17065</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>17031</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Possible Causes of Readiness Probe Failure and Cross-Pool Quorum Errors</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim01:56 PM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>R RIA CHOI</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>고객은 객체스토어 pod의 readiness probe 실패와 EC set quorum 오류 발생 원인, 그리고 이러한 현상이 다른 풀에도 영향을 미치는 조건과, 반복되는 30 EC set 오류가 정상인지 여부를 문의했다.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>pod 0-47이 직접 엔드포인트로 과도한 요청을 받아 goroutine 수가 급증하고 메모리 사용량이 증가하면서 readiness probe 실패를 일으켰고, 이로 인해 클러스터에서 quorum 연결이 끊어져 여러 EC set에서 read/write quorum 오류가 발생했다.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>직접 pod에 접근하는 대신 LoadBalancer 서비스 엔드포인트를 사용하도록 전환하고, 트래픽 부하를 모니터링하며 필요 시 스케일링하거나 요청을 분산시켜 goroutine 스파이크와 메모리 증가를 방지한다.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>지속적으로 30 EC set 오류가 반복되는 경우는 비정상적이며, 클러스터 모니터링 도구를 활용해 트래픽 패턴과 노드 상태를 상세히 분석할 필요가 있다.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17031</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>17030</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Intermittent IAM Refresh Delays and Potential Impact on Data Access</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim08:28 AM</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Zach Burnham</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>사용자가 IAM 캐시 갱신 로그가 클러스터 성능에 영향을 주는지 확인하고, 개선 방안이 있는지 문의했습니다. 또한, 해당 처리 중 읽기/쓰기 접근에 영향을 받지 않는지 여부를 물었습니다.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>로그에 따르면, 오래된 IAM 데이터가 감지되어 캐시가 새로 빌드되었고, 서비스 계정 4786개와 정책 매핑 3741개를 로드하는 데 각각 14.82초와 9.85초가 걸려 전체 갱신이 35.85초가 소요되었습니다.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>시스템은 35.85초 동안 이전 캐시를 기반으로 접근 제어를 수행하므로 현재 읽기/쓰기 작업에 큰 영향이 없으며, 서비스 계정과 정책 매핑을 정리하거나 통합해 로드 시간을 단축하도록 권고합니다.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17030</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>17000</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Questions on AIStor ILM Tiering</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim09:13 AM</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Shubhendu Ram Tripathi</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>고객은 AIStor warm tier에 ILM을 적용할 때 버전 관리가 필요한지, 기존 데이터를 한 번에 warm tier로 이동하는 최선 방법은 무엇인지, 초기 마이그레이션 시 스캐너를 튜닝할 필요가 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>버전 관리는 필수는 아니며, ILM 규칙에 prefix 필터와 transition 조건을 설정하면 기존 객체를 한 번에 warm tier로 이동할 수 있습니다. 스캐너를 fastest 모드로 설정해도 되며, 필요에 따라 조정할 수 있습니다. ILM 규칙이 네임스페이스를 순회해 객체를 마크하고 다른 프로세스가 실제 전환을 수행합니다.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/17000</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>16958</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Is It Possible to List Objects Stored on a Failed Drive?</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RIA CHOI05:19 PM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kranthi</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>We would like to identify which objects were stored on the failed drive. Is there a supported way to list the objects that were located on a specific failed drive?</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>One disk is currently offline due to a physical issue.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>When you replace the drive, MinIO will automatically initiate healing and rebuild the data on the new drive using data from other drives in the erasure-coded set.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16958</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>16957</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unexpected Increase in minio_cluster_health_capacity_usable_total_bytes After Single Drive Failure</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RIA CHOI05:16 PM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kranthi</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>고객이 단일 드라이브가 실패한 후 minio_cluster_health_capacity_usable_total_bytes가 모든 서버에서 증가한 원인을 묻고 있다.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>드라이브가 degraded 상태에서 I/O 오류로 용량이 감소하고, 실패 후 오프라인 처리되면서 MinIO가 다음 최소 용량 드라이브를 사용해 클러스터 용량을 재계산해 증가했다.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>드라이브를 교체하고 노드를 드레인한 뒤 정상 용량이 복구되었으며, 단일 드라이브 교체 시에는 노드 드레인 없이 Direct PV 문서에 따라 교체하면 된다.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>인프라팀이 노드 종료를 요구했고, 온라인 교체가 선호된다.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16957</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>16908</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Custom Start Time for mc inventory Daily Schedule</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim01:30 PM</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Kaan Kabalak</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>고객이 mc inventory를 매일 실행하지만 특정 시각을 지정할 수 없어서 9시와 10시 사이에만 실행되는 상황에 대해 정확한 시작 시간을 맞출 수 있는 방법이 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>mc inventory의 스케줄링 옵션은 daily만 지원하고, 커스텀 시작 시간을 지정하는 옵션이 없기 때문에 원하는 시각에 실행되지 못합니다.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>크론 작업을 사용해 schedule: once 옵션과 함께 원하는 시각에 mc inventory를 실행하도록 설정하거나, 향후 Edge 릴리스에서 제공될 예정인 커스텀 시작 시간 기능을 기다리도록 안내했습니다.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16908</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>16752</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>[critical upgrade standby request on April 9th 9am China Standard Time]</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RIA CHOI04:23 PM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>오퍼레이터가 'policybindings.min.io' 리소스를 찾지 못해 정책 바인딩을 생성하거나 업데이트할 수 없다는 오류가 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16752</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>16746</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>"context canceled" errors after upgrading MinIO version during load testing</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>RIA CHOI03:51 PM</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Kranthi</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>고객이 시스템에서 "context canceled" 오류가 intermittent하게 발생하며, 이 오류가 언제 트리거되는지와 실제 애플리케이션에 미치는 영향을 확인하고 싶어 합니다.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>오류는 GetObjectInfo 호출 시 내부 메타 캐시 walk 과정 중에 클라이언트가 연결을 끊거나 타임아웃이 발생해 컨텍스트가 취소되면서 발생합니다. 업그레이드 이후 로깅 개선으로 오류가 더 빈번히 보이기도 합니다.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>오류는 업그레이드 이후에만 관찰되며, 고부하 상황에서 특히 빈번히 발생합니다. 문제는 클라이언트 연결 관리와 캐시 동기화에 관련되어 있습니다.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16746</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>16679</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LDAP Group Filter Change Requires Server Restart</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RIA CHOI06:07 PM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Matthieu ROLLA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>고객이 재시작 버튼을 클릭하면 서비스에 끊김이나 연결 중단이 발생하는지 여부와, 5초 간단단한 중단이 예상되는지 확인하고 싶어 합니다. 재시작이 전체 서비스 중단이 아닌 롤링 재시작인지 궁금합니다.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>롤링 재시작 시 노드가 한 번에 일부만 재시작되며, 인그레스/로드 밸런서가 재시작 노드를 즉시 감지하지 못해 잠시 트래픽이 중단됩니다. MinIO 자체는 가용성을 유지하며, 나머지 노드가 계속 서비스를 제공합니다.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>인그레스 헬스 체크 간격과 준비 프로브를 짧게 조정하고, 로드 밸런서의 활성 헬스 체크를 1~2초로 설정해 재시작 노드를 빠르게 감지하도록 하세요. 트래픽이 적은 시간에 재시작을 수행하면 사용자에게 영향을 최소화할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16679</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>16668</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>How to Enable SFTP on Existing MinIO Server</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>RIA CHOI02:09 PM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Matthieu ROLLA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>사용자는 MinIO AIStor 서버에서 TLS 없이 HTTP만으로 SFTP(및 FTP) 접근을 활성화하고, SFTP 비공개 키를 어떻게 제공할 수 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SFTP를 활성화했으나 TLS가 구성되지 않아 operator가 TLS 개인 키를 SSH 호스트 키로 사용하도록 설계되어 /tmp/minio/certs/private.key 파일이 없기 때문에 시작에 실패했습니다.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TLS를 먼저 구성하고(디폴트 자동 생성이 사용 가능) objectStore.sftp.enabled를 true로 설정해 Helm 업그레이드를 수행하면 operator가 TLS 개인 키를 SSH 호스트 키로 자동 사용합니다. 커스텀 인증서가 필요하면 certificates.disableAutoCert를 false로 두고 sftp.domainName을 인증서 도메인에 맞추면 됩니다.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>고객은 현재 TLS를 구성할 수 없으므로 SFTP 사용을 보류하기로 결정했습니다.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16668</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>16667</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>License Update via mc license update</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>RIA CHOI02:00 PM</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Matthieu ROLLA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>고객은 mc license update 명령 실행 후 내부 MinIO 서버에 라이선스가 적용되었는지 확인하고, 서비스 중단 여부를 묻습니다. 또한 전체 라이선스 업데이트 절차(Helm 업그레이드와 mc license update)를 문의하며, 에어갭 환경에서 나타나는 재신청 오류 로그가 계속 뜨는 이유와 이를 비활성화할 수 있는 방법을 요청합니다.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>mc license update는 MinIO 서버 내부 설정만 갱신하며, Operator가 사용하는 Kubernetes secret은 별도로 갱신되지 않습니다. 에어갭 환경에서는 SUBNET 포털에 접속하지 못해 정기 재신청 스케줄러가 인증서 오류를 발생시켜 로그를 남깁니다.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>내부 서버에 라이선스가 적용되었는지 확인하려면 mc license info ALIAS를 실행하고, mc license update는 서비스 재시작 없이 즉시 적용됩니다. 전체 라이선스 업데이트 절차는 Helm 차트에서 license 값을 먼저 업데이트한 뒤 mc license update를 실행하는 것이 권장됩니다. 에어갭 환경에서 발생하는 재신청 오류는 SUBNET 포털 접속이 불가능해 발생하며 현재는 스케줄러를 비활성화할 방법이 없으므로 무시해도 됩니다.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16667</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>16631</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Operator Replica Count for High Availability</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim06:06 PM</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Y Kim이 ObjectStore operator pod의 복제본 수가 1개 이상이어야 고가용성을 보장하는지 여부를 확인하도록 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Operator는 하나의 리더 pod만 활성화되고, 리더가 아닌 다른 pod는 대기 상태이며, 복수의 리더가 동시에 동작하면 동시성 문제가 발생합니다. 리더는 Lease를 사용해 상태를 관리하며, 리더가 만료되면 다른 pod가 자동으로 리더가 됩니다.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>리더-팔로워 구조 덕분에 replica 수를 1로 두어도 고가용성이 확보됩니다. pod가 중단되면 Lease 갱신이 중단되고 다른 pod가 즉시 리더가 되어 서비스를 계속 유지합니다.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16631</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>16630</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>[Review Request] MinIO Configuration Files For Migration</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>RIA CHOI03:32 PM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ali Yaldaz</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>고객은 MinIO 설정 파일을 검토해 주시고, minio-global 서비스의 목적과 포트 번호를 알려달라고 요청했으며, Helm 1.0.13 버전에서 .objectStore.configuration를 지정해야 하는지와 headless 및 NodePort 구성을 제외한 최종 values.yaml을 제공해 달라고 요구했습니다.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>고객은 서비스 노출 방식(NodePort vs. Ingress)과 minio-global 서비스가 존재하는지 여부, 오래된 Helm 차트에서 필요한 기본 설정 필드에 대해 혼란을 겪고 있습니다.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Helm 1.0.13에서는 .objectStore.configuration를 지정해야 하며, minio-global 서비스는 생성되지 않으므로 무시해도 됩니다. 제공된 값 중 headless 및 NodePort 항목을 제외하고 최종 values.yaml을 제공하면 됩니다.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16630</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>16629</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Different EC Configuration for New Pool</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim03:19 PM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>고객은 두 번째 풀에서 기존 풀과 다른 EC 설정을 사용하고 싶어합니다. 현재 Kubernetes 환경에서 이를 지원하는지 여부를 확인하고자 합니다. 새로운 릴리스가 나올 때까지 해당 구성을 진행하지 않을 예정입니다.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kubernetes ObjectStore CR은 현재 각 풀마다 다른 EC 설정을 지원하지 않습니다. 이 기능은 baremetal에서만 지원됩니다. 따라서 현재 환경에서는 해당 설정이 불가능합니다.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>팀은 Kubernetes에서 per-pool EC 설정을 지원하도록 작업 중입니다. 진행 상황을 계속 업데이트할 예정입니다. 사용자는 릴리스가 나오면 해당 기능을 활용할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>개발 진행이 다른 의존성 문제로 지연되고 있음.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16629</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>16608</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Downtime during pool expansion</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>RIA CHOI04:10 PM</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>고객은 풀 1을 추가할 때 10분 정도의 다운타임이 발생했는지 확인하고 싶어 합니다. 또한 DNS 해석 오류와 PV 바인딩 속도가 느린 점이 문제인지 묻고 있습니다. 이러한 현상이 예상되는지 여부와 개선 방법을 안내받으려 합니다.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>AIStor는 새로운 풀을 위해 상태집합을 생성하면서 재시작되며, 이 과정에서 기존 풀의 서비스가 중단됩니다. 동시에 다수의 PV 바인딩 요청이 클라이언트 사이드 스로틀링으로 지연되어 DNS가 느리게 반응합니다. 결과적으로 새로운 풀의 Pods가 완전히 준비되기 전에 기존 풀이 재시작되어 다운타임이 발생합니다.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>AIStor 재시작을 새 풀의 모든 Pods가 실행될 때까지 지연하도록 수정하고, DirectPV의 QPS/Burst를 조정해 클러스터 API 서버의 스로틀링을 완화합니다. PVC 사전 생성 및 이미지 사전 다운로드를 통해 Pod 생성 속도를 높이고, API 서버의 APF 설정을 검토해 최적화합니다. 이러한 조치를 통해 다운타임을 최소화하고 PV 바인딩 성능을 개선할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16608</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>16590</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Upgrade Steps from Open Source MinIO to AIStor</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Daniel05:50 AM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>요청자는 DirectPV Helm 업그레이드 시 kubectl directpv uninstall 명령을 건너뛸 수 있는지 확인하고, 전체 업그레이드 절차를 검증해 주시길 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>kubectl directpv uninstall이 직접 PV namespace를 삭제해 Helm 설치 시 namespace가 아직 종료 중이라 오류가 발생하고, CRD가 기존 필드 매니저 kubectl-directpv-oss를 소유해 Helm의 서버사이드 적용과 충돌합니다.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>CRD를 Helm 소유자로 주석/라벨링하고 force-apply를 사용하거나 --skip-crds 옵션을 적용하며, namespace가 완전히 삭제될 때까지 대기 루프를 넣습니다. 기존 secret을 백업·재생성하거나 existingSecret을 false로 설정하고, volumeSize를 size로 교체합니다. 필요 시 운영자 배포를 재시작해 바로 재조정합니다.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16590</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>16579</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DirectPV Upgrade (4.1.4 → 5.1.0): CRDs deleted after helm uninstall</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>RIA CHOI07:36 AM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Pedro Juarez</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>고객은 DirectPV 4.1.4에서 5.1.0으로 업그레이드할 때 CRDs이 Terminating 상태에 걸려 있는 상황을 안전하게 복구하고, 올바른 업그레이드 절차를 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>helm uninstall 시 DirectPV CRDs가 삭제되고, 최종자(finalizer)를 가진 CRDs가 Terminating 상태로 남아 삭제되지 않아 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>CRDs의 deletionTimestamp를 제거하고 최종자를 삭제한 뒤 DirectPV operator를 helm으로 재설치하고, 백업해 둔 CRs(drive, volume, node)를 복원해 재시동합니다. 업그레이드 시 kubectl directpv uninstall 후 helm repo add minio, helm repo update, helm install directpv minio/directpv 를 사용하며, -n directpv와 같은 namespace 옵션을 사용하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>helm 설치 시 -n directpv와 --create-namespace 옵션을 사용하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16579</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>16531</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AIStor Operator Upgrade - Zero-Downtime Guarantee Inquiry</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RIA CHOI01:22 PM</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>사용자는 AIStor Operator 업그레이드가 무중단인지 확인하고 싶다. 또한 서지 전략(maxSurge) 사용 여부와 Graceful Shutdown 보장 여부를 묻는다. 멀티파트 업로드와 복제 작업 처리, MinIO Operator 코드 참조 가능성에 대한 질문도 포함했다.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>업그레이드 중 모든 파드가 새 바이너리를 다운로드한 뒤 동시에 서비스를 재시작하면 기존 연결이 끊길 수 있다. 이후 롤링 재시작 시에도 파드 종료 시 연결이 끊길 가능성이 있다. 부적절한 시점에 재시작되면 오래된 이미지 사용으로 복구되지 않을 수 있다.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>최신 AIStor Operator는 Kubernetes 롤링 업데이트를 사용해 다운타임을 초 단위로 줄인다. 파드는 한 번에 한 개씩 재시작되며, maxUnavailable나 terminationGracePeriodSeconds를 조정할 수 없다. 클라이언트는 재시도 메커니즘을 구현해야 한다.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>업그레이드는 2026년 3월 말에 진행될 예정이며, 개발 환경에서 테스트가 진행 중이다.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16531</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>16519</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pod Fails to Start Due to Invalid OpenID Configuration (azure_tenant_id)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim03:58 PM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>사용자가 pod이 재시작 시 MinIO OpenID 초기화 오류가 발생해 pod이 실행되지 않으므로, 이 검사를 건너뛰거나 임시로 우회해 pod을 실행할 방법을 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>이 오류는 MinIO 버전을 다운그레이드했을 때 새로운 버전에서 추가된 인증 설정 키가 이전 버전에서 인식되지 않기 때문에 발생한 것입니다.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>MinIO를 최신 버전으로 다시 업그레이드하면 pod이 정상 실행됩니다. 또는 'mc admin config reset identity_openid' 명령으로 해당 서브시스템의 키를 제거하거나, MINIO_IDENTITY_OPENID_ENABLE=off 환경 변수를 설정해 OpenID 검사를 비활성화할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>현재 AIStor Operator와 ObjectStore를 다운그레이드했으나, 업그레이드 시에는 kubernetes 설정과 manifest을 git에 저장해 두는 것이 권장됩니다.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16519</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>16475</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Production AIStor Upgrade Plan Review</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim08:38 AM</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Pedro Juarez</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>고객은 AIStor 업그레이드 계획을 검토하고, 필요 시 추가 조정 및 전체적인 위험 여부를 확인해 달라고 요청했다. 또한 롤백 시나리오와 잠재적 위험 수준을 사전에 파악하고 싶어했다.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>업그레이드 과정에서 private Nexus 인증서 문제로 StatefulSet이 삭제될 수 있고, 최신 Operator 릴리스에서 외부 토큰 검증에 영향을 미치는 알려진 이슈가 있어 내부 메타데이터가 변경될 위험이 있다.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Pedro Juarez가 private registry에서 Helm 업그레이드를 수행하는 가이드를 제공했고, Ramon de Klein은 IDP 검증 결과가 정상이면 업그레이드가 안전하다고 안내했다. Ali Yaldaz는 IDP 토큰 검증 절차를 제시했고, Deepak Thimmaiah는 롤백 시 메타데이터 문제를 언급했다.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>외부 토큰 검증에 대한 알려진 이슈가 존재하며, 롤백은 완전히 지원되지 않지만 MinIO 지원팀과 협업하면 가능할 수 있다.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16475</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>16429</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Preventing Audit Log Loop When Storing via Kafka to AIStor</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim08:52 AM</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Jiuker</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>사용자가 감사 로그를 Kafka를 통해 AIStor 버킷에 저장하고자 하며, 무한 루프 가능성에 대해 특정 버킷을 감사 대상에서 제외할 수 있는지, 아키텍처와 운영에 대한 최선의 실천 방안을 문의했습니다. 또한, Kafka 역할, AIStor에 데이터 저장 방법, 그리고 루프 조건과 같은 세부 사항을 요청했습니다. 최종적으로 기능이 언제 릴리즈될지에 대한 정보를 원했습니다.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>OpenSearch에 1TB 이상의 로그를 저장하면서 로드가 높아져서 Kafka를 도입해 성능을 개선하고자 하는 상황이 원인입니다.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Jiuker는 Kafka를 통해 수집한 로그를 OpenSearch에 먼저 저장한 뒤, OpenSearch를 MinIO(AiStor)로 스냅샷 백업하도록 제안했습니다. 또한, 버킷별 필터링 기능을 통해 무한 루프를 방지하도록 설계하고, AIStor를 백업용으로만 사용하도록 권고했습니다.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16429</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>16387</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Inquiry regarding kubectl-directpv upgrade for latest infrastructure stack</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim05:06 PM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>고객이 인프라를 이전 스택에서 최신 이미지로 업데이트할 때 DirectPV 플러그인을 업그레이드해야 하는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe는 v5.1.0 버전으로 업그레이드할 것을 권고하고, 소규모 환경에서 먼저 테스트한 뒤 진행하라고 조언했습니다. 또한 Praveen은 서버와 플러그인 버전을 동일하게 유지하고 최신 상태로 업데이트할 것을 권장했습니다. 따라서, 플러그인을 v5.1.0으로 업그레이드하고, 테스트 환경에서 검증한 뒤 운영 환경에 적용하는 것이 가장 적절합니다.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16387</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>16385</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Delta Sharing Update Fails in RELEASE.2026-02-07</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Harshavardhana11:27 AM</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Harshavardhana</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>고객이 Delta Sharing을 AIStore 테이블에 적용하려 할 때 "Unable to update share: json: cannot unmarshal array" 오류가 발생한다고 문의했다.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>서버가 테이블 namespace를 배열 형식으로 반환하지만, mc 클라이언트는 문자열을 기대하여 JSON 파싱에 실패했다.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>mc 클라이언트를 최신 릴리스(2026-02-19)로 업그레이드하면 문제를 해결할 수 있다.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>16335</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Spread Zone Allocation and Rack-Level Fault Tolerance Validation</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:44 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Pedro Juarez</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim은 스프레드존 설정 시 동일 랙에 2개 이상의 포드가 같은 erasure set에 배치될 가능성을 확인하고 싶어한다.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>노드 수를 각 랙마다 같은 개수로 배치(예: 9개 랙에 6개 서버, 또는 18개 랙에 3개 서버)하고 anti‑affinity를 사용해 스프레드존을 적용한다. spreadZoneConfig를 적절히 설정한다.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16335</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>16323</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Inquiry regarding official validation tools for MinIO to AIStor migration</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RIA CHOI04:22 PM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>고객이 MinIO에서 AIStor로 마이그레이션하기 전에 클러스터가 준비되었는지, 설치 후 마이그레이션이 정상적으로 완료되었는지를 검증할 수 있는 공식 스크립트나 도구가 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>AIStor로의 마이그레이션은 기존 MinIO 업그레이드와 동일한 검증 절차를 따르기 때문에 별도의 공식 검증 도구가 필요 없다는 것입니다.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>따라서 기존 MinIO 업그레이드 시 사용하는 검증 절차와 도구를 그대로 적용하면 됩니다.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16323</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>16321</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DirectPV Node Server error logs</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RIA CHOI01:44 PM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>고객은 DirectPV Node Server에서 간헐적으로 발생하는 오류가 어떤 상황에서 나타나는지, 이는 알려진 이슈인지, 재시작 없이 방지하거나 완화할 수 있는 조치가 있는지에 대해 알고 싶어합니다.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>이 오류는 Kubernetes 컨트롤러의 캐시와 etcd 간에 발생하는 레이스 컨디션으로 인해, 메모리 내 UID가 etcd에 존재하는 객체의 UID와 일치하지 않아 ‘Precondition failed’가 발생함으로써 발생합니다.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Kubernetes 버전을 해당 upstream fix가 포함된 버전으로 업데이트하고, DirectPV를 최신 릴리스로 업그레이드하며, 필요 시 리스너리/레디니스 프로브를 설정해 포드가 stuck 상태일 때 자동 재시작하도록 구성합니다.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16321</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>16281</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Abnormal behavior regarding Goroutine on specific node</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jihun Na04:57 PM</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>고객이 특정 AIStor 노드에서 고루틴 수가 128K로 급증하고 다른 노드는 10K 이하로 유지되는 현상을 분석해 달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16281</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>16280</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unusually High and Sustained Goroutine Count on a Single Objectstore Pod</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim04:56 PM</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Krutika Dhananjay</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>애플리케이션(Application)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>고객이 goroutine 수 급증 현상을 보고하며, aistor-console을 v0.0.28 이상으로 업그레이드하기 위해 어떤 objectstore 이미지를 적용해야 하는지를 문의했다.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>aistor-console v0.0.24 버전에서 폴더를 ZIP으로 다운로드할 때 채널을 닫지 않아 goroutine이 누수되는 버그가 존재하며, 이는 대규모 객체 다운로드 시 120K+ goroutine이 생기는 원인이 되었다.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>문제가 발생한 노드에서 minio 프로세스를 재시작하고, aistor-console을 v0.0.28 이상으로 업그레이드한다. 이를 위해 AiStor 버전을 2025-12-20T04-58-37Z 이상으로 업데이트할 필요가 있다.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16280</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>16176</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DirectPV Disk Replacement Procedure for Degraded Disk</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim02:56 PM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Felvine Sakwe</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>고객이 DirectPV에서 Degraded 상태인 디스크를 교체하기 전 필요한 절차와 전용 스크립트 또는 자동화를 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>디스크가 Degraded 상태여서 교체가 필요합니다.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>대체를 위해 먼저 kubectl directpv discover, kubectl directpv init drives.yaml --dangerous 를 실행한 뒤 replace.sh &lt;OLD-DRIVE-ID&gt; &lt;NEW-DRIVE-ID&gt; 스크립트를 실행합니다. 스크립트가 모든 필요한 절차(드라이브 코어닝, 파드 영향 최소화 등)를 수행하므로 노드 코어닝이나 파드 삭제, 파일시스템 마운트 해제는 사전 단계에서 필요 없습니다.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16176</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>16121</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MinIO Server Fails to Start When One DirectPV Disk is Missing</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RIA CHOI04:09 PM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Praveen</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>고객은 MinIO가 20개의 드라이브 중 하나가 실패했을 때 19개의 드라이브로도 실행할 수 있는지 문의했습니다. 또한 DirectPVVolume CRD가 동일한 /dev/sdr를 두 개 참조하는 현상을 확인하고, 왜 발생하는지 원인을 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>한 드라이브가 LOST 상태로 표시되어 MinIO가 시작되지 못했고, DirectPV는 남은 디스크의 가용 공간을 기준으로 볼륨을 자동 할당하기 때문에 동일한 드라이브에 두 개의 볼륨이 생성됩니다.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>고객은 'kubectl directpv suspend drives' 명령으로 손상된 드라이브의 볼륨을 일시 중지했고, MinIO가 정상 작동합니다. 장기적으로는 unique-drive-selection 기능을 활성화해 1:1 드라이브-볼륨 매핑을 설정할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16121</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>16062</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ObjectStore Fails After Upgrade Due to TLS Certificate Verification Error</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim01:28 PM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>네트워크(Network)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>고객이 ObjectStore Operator가 private Nexus 레지스트리에서 이미지를 끌어오지 못해 TLS 인증 오류가 발생함을 보고하며, Helm 차트에 CA 인증서 마운트 방법이나 필요한 설정을 알려달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Operator는 자체적으로 이미지를 pull하려고 하지만 컨테이너 런타임은 private registry의 CA를 신뢰하고 있어, Operator가 CA를 알지 못해 'x509: certificate signed by unknown authority' 오류가 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>작업자는 AIStor 풀 StatefulSet을 수동으로 삭제해 Operator가 컨테이너 런타임을 사용해 이미지를 pull하도록 하여 오류를 회피했고, 향후 Operator가 런타임을 활용하도록 업데이트될 예정입니다.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>작업자는 상태 정상이 되었다고 보고했고, 서비스 중단 없이 임시 해결책이 효과적이었습니다.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16062</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>16005</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Audit Logs Generated Only from Restarted Pods After mc admin service restart</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim08:59 AM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>고객은 mc admin service restart 명령을 실행한 뒤, 54개의 노드 중 하나만에서만 오디트 로그가 생성되는 문제를 보고했습니다.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>노드들을 하나씩 재시작하거나 mc admin service restart를 다시 실행하여 모든 노드에서 로그가 정상적으로 수집되도록 했습니다.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/16005</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>15974</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ILM expiration timing on versioned buckets</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Grahit A Desai04:12 PM</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Grahit A Desai</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>고객은 ILM 만료 동작이 1일 이후에도 지연되어 객체가 남아 있는 것이 정상인지, 그리고 ILM 실행이 백그라운드 스캐너에 의존하는지 여부를 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ILM은 백그라운드 스캐너를 통해 실행되며, 실시간으로 삭제하지 않고 스캐너가 객체를 스캔하는 시점에 삭제됩니다.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>이 지연은 정상이며, scanner speed=fast 설정을 통해 스캐너 속도를 높여 지연 시간을 단축할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>스캐너 실행 간격과 속도에 대한 구체적 값은 제공되지 않았다.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15974</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>15973</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>How to collect object size distribution</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RIA CHOI04:08 PM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Shubhendu Ram Tripathi</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>RIA CHOI는 1천만 개 객체의 크기 분포를 보고 싶으며, mc find 사용 여부를 묻고 있습니다.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Shubhendu는 mc admin prometheus metrics play/ | grep minio_cluster_objects_size_distribution 명령을 사용해 각 객체 크기 범위별 개수를 조회하는 방법을 제안했습니다. 이 명령은 클러스터 전역에서 객체 크기 분포를 제공하며, 사용자가 필요로 하는 정보를 정확히 반환합니다.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15973</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>15964</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Audit Webhook Error Persists After Disabling and Service Restart</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim03:21 PM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Praveen</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>사용자는 오픈서치로 전송되는 감사 로그가 지속적으로 "Error: not connected to target server/service" 를 표시하며, audit_webhook을 disable 했음에도 동일한 오류가 계속 발생하고, 54개의 노드 중 일부 노드에서만 감사 로그가 전송되는 문제를 해결할 수 있는 방법을 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Fluent Bit pod의 CPU 한계(1로 설정)로 인해 OpenSearch에 과부하가 발생해 연결이 끊겼으며, audit_webhook 설정이 모든 노드에 일관되게 적용되지 않아 일부 노드에서만 로그가 전송되었습니다.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Fluent Bit pod의 CPU 한계를 2로 증가시켜 오류를 제거하고, audit_webhook 설정을 enable=off 으로 전역적으로 적용한 뒤, 필요한 경우 pod를 재시작하여 설정을 반영하며, Prometheus 메트릭을 모니터링해 큐 길이와 실패 수를 확인합니다.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15964</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>15856</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Impact of Large Kubelet Mount Paths &amp; Changing Kubelet Root Directory</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>RIA CHOI05:18 PM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Bala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>RIA CHOI는 /var/lib/kubelet/pods 에서 수천 개의 마운트 경로가 생성될 때 OS 레벨의 디스크 IOPS, 대역폭, 파일 시스템 성능에 영향을 미칠지 여부를 묻습니다. 또한 DirectPV가 볼륨을 관리 중일 때 kubelet 루트 디렉터리를 수정하는 것이 안전한지 궁금합니다. 마지막으로 kubelet 루트가 다른 디스크로 이동될 때 기존 볼륨, 마운트 작업, 연결 워크플로우에 문제가 생길지에 대해 알고 싶어합니다.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>kubelet 루트 디렉터리를 NVMe 장치로 옮기고, DirectPV Deployment와 DaemonSet에 새 kubelet 경로를 반영한 뒤 Kubernetes 서비스와 MinIO, DirectPV 노드 및 컨트롤러 포드를 중지합니다. 그 다음 노드를 재부팅하고 서비스를 재시작하면 됩니다. 재부팅 후 DirectPV는 정상 동작하며 기존 볼륨에는 영향이 없습니다.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15856</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>15855</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Understanding how 'mc du' works internally</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>RIA CHOI05:09 PM</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Grahit A Desai</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>사용자는 mc du 명령이 내부적으로 캐시된 데이터를 사용하여 작업하는지, 아니면 새로 객체 목록을 가져와 각 객체의 메타데이터를 디스크에서 직접 읽는지 궁금합니다.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>mc du는 새로 목록을 가져와서 각 객체의 메타데이터를 디스크에서 직접 읽습니다. 백그라운드 스캐너의 캐시를 사용하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15855</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>15844</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unexpected Cross-Traffic Between Two AIStor Objectstores in the Same Kubernetes Cluster</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:30 AM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Jeeva</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>네트워크(Network)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>고객은 같은 Kubernetes 클러스터에 배포된 서로 다른 객체스토어가 서로 통신하도록 설계되었는지와, NodePort를 사용해 warp 로드를 B에서 수행할 때 A의 NIC 사용량이 비정상적으로 증가하는 현상에 대해 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>MinIO 클러스터는 서로 완전히 격리되어 통신하지 않으며, 두 객체스토어가 동일한 Kubernetes 네트워크를 공유함으로써 NodePort/ClusterIP에서 발생하는 트래픽 라우팅이 다른 객체스토어의 노드에 영향을 주어 NIC 사용량이 증가한 것으로 판단됩니다. 특히 bond1에서 NodePort를 사용하면 트래픽이 노드 간 라우팅되어 A의 10개 노드에 부하가 걸리는 현상이 확인되었습니다.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>NodePort 서비스의 externalTrafficPolicy를 'Local'로 설정하면 트래픽이 해당 노드에 로컬 엔드포인트로만 전달되어 교차 트래픽이 줄어들 수 있습니다. 현재 외부 트래픽 정책이 Local로 설정되어 있으므로, 필요하면 내부 트래픽 정책이나 CNI 라우팅 구성을 점검해 추가적인 성능 최적화를 진행합니다.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15844</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>15832</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>User-Level and Prefix-Level Quota Support</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim08:54 AM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>사용자는 버킷 수준이 아니라 사용자별 혹은 특정 접두어(prefix)별로 할당량(quota)을 설정할 수 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>AiStor는 사용자 또는 접두어에 대한 할당량을 지원하지 않으며, 버킷 수준만 지원합니다.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>해당 기능은 현재 불가하므로, 버킷 수준의 할당량만 설정하시면 됩니다.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15832</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>15826</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>How to check prefix-level usage</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RIA CHOI03:42 PM</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Praveen,Grahit A Desai</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>고객은 AIStor에서 프리픽스 수준 사용량을 직접 제공하는 API나 webhook이 있는지 문의했습니다. 없다면 mc du를 오프피크 시간에 실행해 사용량 메트릭을 수집하는 것이 적절한지 확인하고 싶어 합니다.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>mc du는 ListObjects 호출을 수행해 대용량 버킷/프리픽스에서 느리고 리소스를 많이 소비합니다. 현재 스캐너 메트릭은 버킷 단위 또는 전체 사용량만 제공해 프리픽스 수준 메트릭이 부족합니다.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>현재는 오프피크 시간에 mc du를 실행해 프리픽스 사용량을 수집하도록 권장합니다. ListObjects 호출 비용을 모니터링하기 위해 mc admin trace를 사용하도록 안내했습니다. 인벤토리 기능이 도입되면 프리픽스 수준 사용량 리포트가 제공될 예정입니다.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>인벤토리 기능은 테스트 중이며, 향후 명확한 출시 일정이 발표될 예정입니다.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15826</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>15795</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Memory Tuning for Large Downloads in MinIO Console</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim02:53 PM</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>고객은 MinIO Console Object Browser를 통해 대용량 파일을 다운로드할 때, object-store pods의 메모리 사용량이 크게 증가할 수 있는지 궁금해했습니다.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>다운로드 시 객체 브라우저가 스트리밍 방식을 사용하므로, 객체 스토어 또는 콘솔 백엔드 API에서 버퍼링되지 않아 메모리 사용량이 크게 늘어나지 않습니다.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15795</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>15794</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Required Permissions for Replacing the Root MinIO Credential</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim12:43 PM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Grahit A Desai</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>사용자는 admin.DetachUserOrGroupPolicy와 admin.ListPolicies 액션을 찾을 수 없어서 필요한 권한 설정이 불확실합니다.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>사용자는 서비스 계정에 아래와 같은 최소 권한 정책을 붙여 주면 됩니다. 정책은 admin:CreatePolicy, admin:DeletePolicy, admin:GetPolicy, admin:ListUserPolicies, admin:UpdatePolicyAssociation, admin:CreateServiceAccount, admin:ListServiceAccounts 등을 허용하도록 정의합니다.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15794</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>15769</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>How to Find the Prefix-level Usage in a Bucket</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim04:53 PM</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Grahit A Desai</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim은 버킷에 많은 파일과 여러 접두어가 있는 상황에서 특정 키 접두어의 현재 사용량을 확인할 수 있는 방법을 찾고 있습니다. mc du 대신 다른 방법이 있는지 확인하고자 합니다.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>mc ls --recursive --summarize 명령이 대규모 객체(3PB)에서 실행 시 mc du와 동일한 시간이 걸려 성능 문제가 발생하고 있습니다. 대용량 객체를 가진 접두어에서 목록화가 비용이 많이 들기 때문입니다.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>mc ls --recursive --summarize 명령을 사용하여 접두어별 크기와 객체 수를 요약하도록 제안했습니다. 대규모 접두어의 경우 다른 메타데이터 수집 방법이나 사전 객체 배치 계획을 검토하도록 권장했습니다.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15769</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>15752</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Storage Info Mismatch</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim03:36 PM</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Deepak Thimmaiah</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim reported that the bucket count displayed on the test cluster’s bucket page is incorrect—showing 2 buckets while there are actually 4—despite the summary and UI overall matching mc results, and asked what else should be checked.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>After performing multiple tests, including changing root credentials, switching the object store between nodes, and reinitializing disks, the MinIO scanner appears not to be running, as evidenced by the absence of scanner info and lack of output from scanner status commands.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Verify that the MinIO scanner is running by checking minio logs for scanner activity and, if it is not running, start or restart the scanner (or MinIO) to trigger the correct bucket counting.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15752</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>15683</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AIStor and Keycloak JWT Integration Inquiry</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim03:24 PM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>고객이 Keycloak에서 발급받은 JWT를 AIStor에서 인증·인가에 사용할 수 있는지, 그리고 JWT를 이용해 AssumeRoleWithWebIdentity STS API를 호출해 임시 자격증명을 획득하고 S3 API에 접근하는 절차가 가능한지 물어보았습니다.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15683</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>15644</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>How to Update minio Password Using Helm</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim11:36 AM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Jeeva</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>사용자가 Helm 차트에서 MinIO 루트 자격 증명을 변경했을 때, 서비스가 정상적으로 재시작되는지와 운영 중인 MinIO 파드가 어떻게 재인증되는지에 대해 확인하고자 합니다.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>루트 자격 증명을 변경하면 기존에 발급된 임시 토큰이 무효화되므로 MinIO 서비스가 재시작되거나 파드가 재배포되어야 재인증이 이루어집니다.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2025년 8월 15일 이후 AIStor 릴리스에서는 Helm 업그레이드나 상태 집합 재배포 시 파드 내부에서 MinIO 서비스가 재시작되며, 임시 토큰이 자동으로 갱신됩니다. 운영 환경에서는 테스트 환경에서 먼저 검증 후 적용해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15644</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>15631</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Safe Procedure for Swapping Objectstores Between Two Nodes</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim05:08 PM</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Bala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>고객은 EC 8:3로 구성된 MinIO 객체 저장소를 두 노드( worker12와 worker23 ) 간에 교환하고자 하며, 기존 데이터를 보존하면서 안전한 절차를 알고 싶어합니다.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1) worker12와 worker23에 연결된 pod, PVC, DirectPV 볼륨 및 드라이브를 식별합니다.
+2) 두 노드를 cordon하고, 해당 노드의 pod를 삭제해 Pending 상태로 둡니다.
+3) PVC(및 필요 시 PV)를 삭제해 DirectPV 볼륨을 수동으로 제거하도록 kubectl directpv clean 혹은 directpv remove 명령을 사용하고, 드라이브를 kubectl directpv remove 로 제거한 뒤, kubectl directpv discover 와 init 로 재초기화합니다.
+4) 노드를 uncordon 하면 스케줄러가 PV nodeAffinity를 기준으로 pod를 재배치하고, quorum이 유지되는 한 MinIO가 자동으로 데이터를 복구합니다.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>수동으로 finalizer를 삭제하거나 kubectl delete directpvdrives 명령을 직접 실행하는 것은 권장되지 않으며, 직접 편집은 사전 원인을 파악한 후에만 수행해야 합니다.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15631</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>15618</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Request for MinKMS API and SDK Documentation</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:30 AM</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Andreas</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>고객은 MinKMS의 API/SDK 문서가 부족해 사용법 안내를 요청했습니다. 또한 MinKMS와 AIStor를 사용해 Kubernetes 시크릿, PostgreSQL 비밀번호 같은 민감 정보를 암호화 및 저장하고자 합니다.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>CLI 전용 문서만 제공되어 API 예제 및 SDK 지원 여부가 명확하지 않아 추가 자료가 필요합니다.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>MinKMS와 AIStor를 사용해 암호화된 객체를 저장할 수 있지만, AIStor는 비밀 관리 시스템이 아니므로 비밀 회전 및 무효화 기능은 별도로 구현해야 합니다. 또한 Go용 kms-go SDK만 제공되고, Java/Python SDK는 없으므로 직접 구현하거나 다른 언어용 래퍼를 작성해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>고객은 이후 추가 질문 없이 대화를 종료했습니다.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15618</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>15558</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Intermittent TCP Disconnections on Broadcom NIC Nodes in a Cilium-Based Cluster</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim01:38 PM</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>James Jones</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>네트워크(Network)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>고객은 Broadcom NIC를 장착한 노드에서 TCP 연결 끊김이 발생하고 패킷 손실이 보고되었으며, Cilium pod 재시작 후 해결되는 현상을 보고했습니다. 또한, MinIO가 과거에 유사한 Broadcom NIC 이슈를 보았는지 확인하고 해결 방안을 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Broadcom NIC에서 하드웨어, 펌웨어, 또는 드라이버 문제가 있을 가능성이 높으며, 네트워크 스택 튜닝이 필요할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>펌웨어와 드라이버를 최신 버전으로 업데이트하고, Linux 커널 튜닝(IRQ, RX/TX 큐, NUMA, 드라이버 파라미터)을 적용하거나 Broadcom NIC를 Intel NIC로 교체하면 문제가 해결됩니다.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Dell KB 문서에서 동일한 Broadcom NIC 연결 끊김 문제가 보고됨.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15558</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>15539</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Discrepancy Between MinIO Console and Pod Status After Node Drain</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:41 AM</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>고객은 3개의 노드가 드레인되고 오프라인 상태가 되자, mc admin info와 콘솔에서 대부분의 노드가 오프라인으로 표시되는 현상을 보고했습니다. 이 현상이 왜 발생하는지, 그리고 실제 서비스가 정상 동작 중임을 어떻게 확인할 수 있는지 확인 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>mc admin info 명령이 내부 스캔을 완료하지 못해 오프라인 노드 수를 잘못 계산하는 버그가 있습니다. 콘솔도 동일한 호출을 사용하기 때문에 잘못된 정보를 표시합니다. 이 버그는 최근 마스터 브랜치에서 수정되었습니다.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>새로운 릴리스가 배포되면 버그가 수정되어 정확한 노드 상태가 표시됩니다. 현재는 30초 정도 소요되는 mc admin info 명령을 사용해 확인하고, 문제 발생 시 노드를 다시 온라인 상태로 복구하면 서비스가 정상 동작합니다.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>mc admin info 명령 실행 시 약 30초가 걸립니다.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15539</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>15511</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Object Store Pool Configuration Across Selected Node Ranges</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim06:46 PM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Cesar Celis</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim은 노드 1–58 및 71–74를 하나의 객체 저장소 풀에 포함시키고, 노드 59–70을 제외한 뒤, 이후 노드 59–70 및 75–90으로 두 번째 풀을 만들 수 있는지 여부를 묻는 요청을 했습니다.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Cesar Celis는 Kubernetes에서 비연속 노드 집합을 라벨링하고 pool의 nodeSelector 또는 nodeAffinity를 해당 라벨에 포인팅하면 원하는 풀을 만들 수 있다고 답했습니다. 또한 하드웨어와 드라이브 수가 같은지, EC 파리티 요구사항 충족 여부, 실패 도메인에 걸쳐 반대부착, 새 풀 추가 시 기존 객체 재배분이 자동이 아니라는 점을 주의하라고 조언했습니다.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15511</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>15507</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Node Replacement and Data Migration Procedure (DirectPV)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim12:56 PM</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Praveen</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>고객은 기존 노드를 새 노드로 교체하는 절차와 정확한 단계별 과정을 문의했습니다. 또한 데이터 이전 방법이 있는지 여부를 물었습니다.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>노드를 교체하려면 먼저 해당 노드의 DirectPV 리소스를 삭제하고, PVC 및 PV를 정리한 뒤 같은 호스트명으로 새 노드를 추가합니다. 새 노드를 cordon 해제하고 DirectPV 데몬셋에 참여하도록 하며, 드라이브를 초기화하고 탐색하면 새로운 PVC와 PV가 생성됩니다. 데이터는 직접 이전이 불가능하며 남은 디스크에서 복구(healing) 과정을 통해 재구성됩니다.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15507</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>15493</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AIStor Metrics for Detecting Node Connectivity Issues</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim09:44 AM</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>네트워크(Network)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>고객은 SSH 연결 실패와 재연결 기록을 모니터링할 수 있는 AIStor 메트릭을 요청하고, 해당 메트릭의 상세 설명과 수집 간격을 묻습니다.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>minio_cluster_health_nodes_offline_count 메트릭을 사용하여 노드 오프라인 상태를 감지하고, 이 메트릭은 매 분마다 업데이트되므로 알림을 설정할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15493</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>15462</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Developer Guide for Accessing AIStor over TLS from Spark, StarRocks, and Java Applications</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim09:34 PM</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Anis Eleuch</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>고객이 AIStor에 TLS를 활성화한 후 Spark, StarRocks, Java 기반 애플리케이션에서 액세스하고 사용하는 방법에 대한 개발자 가이드 또는 참조 웹사이트를 제공해 달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>답변자가 Spark에 필요한 Hadoop 설정 예시를 제공하며, https://blog.min.io/spark-minio-kubernetes/ 블로그 링크를 공유했습니다.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15462</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>15445</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Missing Prometheus Metrics in AIStor Object Store</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jiuker12:00 PM</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Jiuker</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>고객이 MinIO에서 minio_api_requests_ttfb_seconds_distribution 및 minio_system_drive_reads_per_sec 메트릭이 보이지 않아 원인을 물어보고 해결책을 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15445</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>15358</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Operational Impact of Multiple StorageClasses in Kubernetes</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim04:18 PM</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Nagashree Mylaraiah, Alexander Kalaj</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>고객은 30개의 StorageClass를 유지하는 것이 쿠버네티스의 성능, 장애 처리 및 관리에 부정적 영향을 미칠지 궁금해했습니다.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Nagashree Mylaraiah와 Alexander Kalaj는 30개의 StorageClass가 쿠버네티스 성능이나 장애 처리에 영향을 주지 않으며, rack‑awareness 스크립트에 의해 관리될 때 관리 오버헤드가 매우 낮다고 답변했습니다.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15358</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>15316</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Command and Parameters for CDP Hadoop to Aistor Transfer</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim02:41 PM</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Shireesh Anjal</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>고객인 Youngkyoo Kim이 CDP Hadoop에서 Aistor로 데이터를 전송할 때 사용하는 명령과 매개변수를 알고 싶어 문의했다.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Shireesh Anjal은 고객에게 https://blog.min.io/migrating-hdfs-to-object-storage/ 문서를 참고하라고 안내했다.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15316</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>15172</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>About Volume Manager Declarative Helm Setup</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim07:19 PM</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Praveen</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim이 prep-job.yaml을 실행했을 때 기존 XFS 파일 시스템이 있는 디스크가 있는 경우 재설치를 위해 예외를 허용하는 옵션이 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>prep-job.yaml은 기본적으로 파일 시스템이 있는 드라이브를 건너뛰도록 설계되어 있으며, 이는 새로운 설치에만 적용됩니다.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>드라이브가 마운트되지 않은 상태라면 discover 및 init 프로세스를 사용하면 재설치를 진행할 수 있습니다. prep job은 예상대로 동작합니다.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15172</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>15110</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Rack awareness configuration in objectstore helm chart</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:05 AM</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Jiuker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>사용자는 MinIO에서 랙 인식 기능을 적용하고자 하며, 58개의 노드가 있고 각 랙에 1~4개의 노드가 배정되어 있는 상황에서 랙 인식을 활성화하기 위해 topology.kubernetes.io/zone 레이블을 각 노드에 추가하고, Helm 차트에 podAntiAffinity 및 topologySpreadConstraints를 설정해야 하는지 묻고 있다. 또한, 이러한 설정을 위한 간단한 예시 구성 파일을 요청하고 있다.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Jiuker는 helm upgrade 명령을 사용한 예시를 제공하며, 각 노드에 topology.kubernetes.io/zone 레이블을 추가하고 podAntiAffinity와 topologySpreadConstraints를 설정하도록 안내했다. 그는 또한 랙이 단지 레이블일 뿐이며, topologySpreadConstraints가 스케줄링을 균등하게 하도록 시도한다는 점을 설명했다.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15110</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>15075</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>LDAP User AccessKey Creation Works in MinIO but Fails in AIStor</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:00 AM</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Harshavardhana</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>고객은 AIStor에서 LDAP 기반 서비스 계정 생성 명령이 실패하고, MinIO에서는 정상적으로 동작하는 이유를 확인하고자 합니다.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>사용자는 명령어를 'mc idp ldap accesskey create alias/ username' 형식으로 실행하면 서비스 계정 생성이 정상적으로 이루어집니다.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/15075</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>14993</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Performance Drop at Small Block Sizes in Warp Tests</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim01:12 PM</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Harshavardhana</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>고객은 소형 객체(64 KiB) 사용 시 동시성 증가에도 네트워크 사용량이 제한되는 현상을 보고하고, 병목 원인을 파악하고 해결책을 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>MinIO는 객체 생성 시 여러 시스템 호출과 EC 스트라이프 단위당 IOP를 필요로 하며, 현재 8개의 EC 드라이브와 8:3 설정이 높은 HA와 대형 스트라이프를 초래해 드라이브 IOPS(≈1000 IOPS)를 초과하지 못하게 합니다.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>스트라이프 크기를 4로 줄이고 MINIO_ERASURE_SET_DRIVE_COUNT를 4로 설정하면 IOP를 두 배로 늘릴 수 있으며, 필요 시 패리티 수를 낮춰 HA를 일부 감소시키는 방안을 권장합니다.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14993</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>14992</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Request for Official Performance Testing Guidelines and Expected Benchmarks</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim12:24 PM</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Eco</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>고객이 MinIO에서 특정 하드웨어 및 네트워크 사양에 따라 기대할 수 있는 벤치마크 수치를 보여주는 공식 성능 테스트 가이드라인이나 문서/공식을 제공해 주실 수 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Eco는 warp benchmark 유틸리티를 사용하고, mc support diag를 실행해 성능에 영향을 주는 일반적인 문제를 해결하도록 권장했습니다. mc support perf 명령으로 기본 테스트를 수행하고, 충분한 클라이언트 트래픽을 확보한 뒤 warp의 옵션으로 다양한 객체 크기와 동시성 수준을 테스트하도록 안내했습니다. 테스트 전에는 실행할 warp 명령을 제공해 주시면 피드백을 받을 수 있도록 했습니다.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14992</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>14920</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MinIO Tuned Profile Has No Performance Impact</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim07:51 PM</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Mark Theunissen</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim은 RHEL 9.4에서 MinIO 튜닝 프로필을 적용했음에도 성능이 향상되지 않았다는 점을 질문하며, 누락된 단계가 있는지 혹은 특정 조건에서만 효과가 나타나는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Mark Theunissen은 RHEL이 이미 최적화되어 있어 튜닝 프로필이 변화를 주지 않았을 수 있고, 일부 매개변수는 네트워크가 최대 Saturation 상태에서만 성능을 향상시킬 수 있다고 설명했습니다. Harshavardhana는 기본 벤치마킹에서 Linux 커널이 이미 적절히 튜닝되어 있어 warp 테스트에서는 큰 이점을 보지 못한다는 점을 덧붙였습니다.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Mark은 warp 테스트 파라미터와 시스템 메트릭을 상세히 제공하여 Klaus Post 또는 Harshavardhana에게 전달하면 보다 정밀한 피드백을 받을 수 있다고 권유했습니다. Harshavardhana는 장기 실행 및 리소스가 집중되는 환경에서 튜닝 프로필이 효과적이며, RHEL 10 또는 Ubuntu 24.04 같은 최신 커널과 XFS NVMe 튜닝을 고려하도록 제안했습니다.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14920</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>14899</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>About recommended pool configuration</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim04:43 PM</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>고객이 AIStor 클러스터의 hot tier에 대해 EC 스트라이프 크기와 parity 블록 크기를 추천해달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14899</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>14898</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Grafana dashboard for AIStor</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim04:36 PM</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Val Bezrukov</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>사용자가 AIStor 콘솔에서 모니터링 기능이 사라졌다고 보고, Prometheus로 메트릭을 전송하고 Grafana에서 확인할 수 있는 템플릿을 제공해 달라고 요청했습니다. 또한 Kubernetes 환경에서 노드 URL 사용 방식에 대해 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>모니터링 대시보드가 아직 제공되지 않았고, v3 메트릭을 모든 MinIO 노드에 설정해야 한다는 점을 인식하지 못해 생긴 문제입니다.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Val Bezrukov는 gziped tar 파일에 포함된 4개의 대시보드와 Prometheus 스크랩 설정 예시를 제공했습니다. 또한 v3 메트릭을 모든 노드에 설정하도록 안내했고, Kubernetes에서 kubernetes_sd_configs를 사용해 자동으로 pod를 탐지하도록 설명했습니다. Shubhendu Ram Tripathi는 ClusterIP가 일반적인 클러스터 수준 메트릭에 적합하며 노드 메트릭은 각 노드를 명시적으로 추가해야 한다고 조언했습니다.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14898</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>14886</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>[RHEL 10] tuned.conf Changes and Performance Tuning Feedback Request</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jiuker10:44 AM</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Harshavardhana</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>고객은 RHEL10 출시 이후 기존 tuned.conf에 변경이 있었는지와 RHEL10 테스트 중 발생한 이슈 또는 추가 성능 개선 제안을 요청했습니다. 또한, MinIO EOS tuning 문서의 새로운 링크 제공을 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>RHEL10이 5.x에서 6.x 커널로 업그레이드되면서 커널 파라미터 조정이 필요할 수 있다고 우려하며, 서버 벤더 정보가 불확실해 최적화를 진행하기 어려웠습니다.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>새 커널은 대부분의 조정이 필요 없으며, 필요 시 TCP 버퍼를 조정해 네트워크 softirq를 줄일 수 있습니다. 기본 tuned-adm 설정을 사용하고, 환경에 맞게 커스텀 조정하면 됩니다.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14886</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>14871</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Possibility to use KES when storing sensitive information</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim03:32 PM</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Andreas</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>고객은 KES 또는 minKMS를 사용해 Kubernetes 비밀을 암호화하고 객체 저장소에 저장한 뒤 사용하는 것이 적절한지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>고객은 KES가 암호화 키를 저장하고 객체를 암호화/복호화만 수행하므로, 비밀 정보를 저장하기에 적합한지에 대해 혼란을 느꼈습니다.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Andreas는 KES가 데이터를 저장하지 않으며, 대신 비밀을 KES 또는 minKMS로 암호화한 뒤 신뢰할 수 없는 저장소에 보관하고 필요할 때 다시 복호화하도록 권장했습니다.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14871</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>14854</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Performance test error of console UI</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim09:17 AM</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Cesar Nieto</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>고객이 AIStor 콘솔의 디버그 섹션에서 성능 테스트를 실행할 때, 하나의 ObjectStore 노드만 성능 지표를 보고하고 나머지 노드가 인증 실패 메시지를 반환하는 문제를 해결하고자 합니다.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>최신 이미지를 적용한 RELEASE.2025-08-29T21-27-49Z 버전에서 이 문제가 해결되었습니다. 업데이트 후 테스트를 재실행하면 모든 노드에서 성능 지표를 정상적으로 받을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14854</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>14810</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Identifying disks in the same erasure set</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim12:52 PM</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Prakash, Allan</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>고객이 물리적 디스크가 동일한 에러레이션 세트에 속하는지를 확인하고 싶어 한다.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>여러 디스크가 동시에 고장났을 때 어떤 세트에 속하는지를 식별하기 위해 필요했다.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>mc admin info &lt;ALIAS&gt; --json 명령어와 jq 스크립트를 사용해 엔드포인트, 풀 인덱스, 세트 인덱스, 디스크 인덱스를 출력하고 정렬하면 세트 정보를 알 수 있다. 또한 mc admin drive top &lt;alias&gt; 명령으로 같은 정보를 확인할 수 있다.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14810</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>14795</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Firewall Rules Needed for Full Access to CONNECT</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim09:26 AM</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Jeeva</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>네트워크(Network)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>고객은 CONNECT 사이트에서 이슈 상세 페이지를 열거나 새 이슈를 만들 때 웹소켓 연결이 실패해 내용이 로드되지 않는 문제를 해결하기 위해 필요한 도메인과 포트를 알려달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>개인 PC에서 Twilio의 웹소켓 서버(wss://tsock.us1.twilio.com/v3/wsconnect)에 접근이 차단되어 페이지가 비정상적으로 로드되고, 브라우저 콘솔에 연결 오류 메시지가 반복적으로 표시됩니다.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>서버에 subnet.min.io(443)와 tsock.us1.twilio.com(443) 도메인을 화이트리스트에 추가하면 웹소켓 연결이 정상적으로 동작합니다.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14795</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>14776</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>The recovery process from the full K8s destroy</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim11:01 AM</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Bala, Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>사용자는 AIStore 환경을 Kubernetes 클러스터가 완전히 파괴되었을 때 데이터 손실 없이 재구축할 수 있는 절차와 정확한 단계 및 필요한 백업 항목을 알고 싶어합니다.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>DirectPV와 관련된 CRDs(directpvdrives, directpvvolumes), ObjectStore, PVC, PV, Secret을 kubectl 또는 Velero로 백업하고, 클러스터를 재구축 후 같은 노드 이름으로 오퍼레이터와 ObjectStore를 재설치하면 기존 볼륨을 재사용하여 데이터가 복구됩니다.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>백업은 AIStore namespace의 모든 리소스를 포함하고, 노드 이름을 동일하게 지정해야 DirectPV가 드라이브를 올바른 노드에 연결합니다.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14776</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>14762</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>About configuring network encryption</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim02:20 PM</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Jeeva Kandasamy</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>사용자는 Helm values.yaml에서 certificates.config.dnsNames에 도메인 이름을 추가하는 방법을 묻고, IP 주소를 SAN에 포함할 수 있는지 여부를 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14762</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>14754</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Object store Console UI change</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Jeeva</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>고객이 최근 버전에서 관측성, 로드 밸런서, 인바운드 트래픽 기능이 UI에서 사라진 이유와 이를 다시 접근할 수 있는 방법을 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>전역 콘솔이 최신 릴리스에서 제거되었으며, UI에서 구성하던 기능들은 Helm 차트나 ObjectStore Custom Resource를 통해 관리하도록 변경되었습니다. 또한 observability 기능은 v3 메트릭스를 사용해 Prometheus와 Grafana에서 시각화하도록 전환되었습니다.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>MinWall 및 기타 기능은 여전히 사용할 수 있으며, MinWall을 포함한 설정은 Helm 차트(예: aistor-objectstore)나 CR에서 구성해야 합니다. 관측성은 Prometheus와 Grafana 대시보드를 활용해 v3 메트릭스로 모니터링하면 됩니다. Global Console이 사라졌으므로, 해당 기능을 사용하려면 aistor 릴리스를 적용하고, 필요한 설정을 Helm 차트에 명시하거나 CR에 정의하십시오.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14754</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>14753</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AIStor docs page</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim10:00 AM</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Jiuker</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>고객은 AIStor 문서 위치를 찾는 것부터 시작해, Helm 설치 시 erasure coding 설정과 StorageClass의 재클레임 정책을 Delete에서 Retain으로 변경하는 방법을 요청했습니다. 또한, 클러스터가 완전히 삭제된 경우 Retain 정책 하에서 기존 데이터를 재접근할 수 있는지 여부와 재사용 절차를 확인했습니다.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Helm 값 파일에서 MINIO_ERASURE_SET_DRIVE_COUNT와 MINIO_STORAGE_CLASS_STANDARD를 operator 컨테이너의 env에 넣었지만 실제 적용은 ObjectStore.spec.env에 설정해야 했습니다. 이로 인해 erasure 설정이 반영되지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14753</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>14738</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Best practices for bucket count</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim06:38 AM</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Alexander Kalaj</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>스토리지(Storage)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Youngkyoo Kim이 AIStor에서 권장되는 버킷 수와 대규모 버킷 수가 성능에 미치는 영향을 묻고 있습니다.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>사용자가 S3의 버킷 제한과 AIStor 적용 가능성을 혼동하여, 5000~10000 버킷 이상을 만들 때의 가이드라인을 찾고 있습니다.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>버킷 수를 100 정도의 베이스라인으로 두고, 새로운 마일스톤(예: 1000)마다 감사 프로세스를 도입해 과도한 버킷 생성을 방지합니다. API와 SCANNER 메트릭을 v3 메트릭 엔드포인트를 통해 모니터링하고, 성능 영향을 감지하면 조치를 취합니다. 필요 시 내부 고객과 협력해 버킷 수를 최소화하도록 권고합니다.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14738</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>14689</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Cannot install volumemanager using helm chart</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Pedro Juarez02:02 PM</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Ramon de Klein</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>사용자가 Legacy Pods가 생성되는 것을 방지하고, replicas 설정이 반영되지 않는 현상을 해결하기를 요청했습니다. 또한, 각 질문마다 별도의 Subnet 티켓이 필요한지 물었습니다.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Helm 차트에서 legacyFlag를 false로 설정해도 Legacy Pods가 생성되는 버그가 존재하고, replicas 값이 차트에서 무시되는 버그가 있었습니다.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>업데이트된 aistor-volumemanager 0.2.0 차트를 사용하고 helm repo update를 수행하면 legacyFlag를 지정할 필요가 없으며, replicas 설정이 정상적으로 적용됩니다.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14689</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>14425</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Welcome to MinIO SUBNET</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>https://subnet.min.io/issues/14425</t>
         </is>
       </c>
     </row>

--- a/subnet_issues.xlsx
+++ b/subnet_issues.xlsx
@@ -499,25 +499,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>고객이 핫 클러스터와 워 arm 클러스터가 서로 다른 AIStor 버전을 사용할 때 ILM 티어링이나 버킷 복제에 호환성 문제가 있는지 문의했습니다.</t>
+          <t>사용자는 서로 다른 AIStor 버전을 실행하는 두 클러스터(핫 티어 2026.02, 워밍 티어 2026.06) 간 ILM 티어링 및 버킷 복제에 호환성 문제가 있는지, 그리고 혼합 버전 배포가 지원된다면 버전 호환성 요구사항이나 제한 사항이 있는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ILM 티어링은 표준 S3 연산만 사용하기 때문에 버전 차이가 영향을 주지 않지만, 복제는 버전마다 스키마나 메타데이터가 달라질 수 있어 호환성에 영향을 줄 수 있습니다.</t>
+          <t>ILM 티어링은 워밍 클러스터를 단순한 S3 호환 스토리지 대상으로 인식하고, 표준 S3 연산(PUT/GET)을 사용해 객체를 이동하기 때문에 두 클러스터가 동일한 MinIO 버전을 실행할 필요가 없습니다. 반면 버킷 복제는 버전 간 스키마나 메타데이터 변경이 있을 수 있어 동일 버전을 실행하는 것이 권장됩니다.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ILM 티어링은 2026.02(핫)와 2026.06(워 arm) 두 버전을 사용해도 호환성 문제가 없으며, 복제의 경우 두 클러스터가 동일한 버전을 실행하도록 권장합니다.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>ILM 티어링에 대해서는 혼합 버전(핫 2026.02, 워밍 2026.06) 사용이 호환성 문제 없이 동작합니다. 버킷 복제의 경우 두 클러스터가 동일 버전을 실행하도록 구성해 스키마/메타데이터 차이로 인한 문제를 방지해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17433</t>
@@ -543,20 +547,36 @@
           <t>jungkeunlee03:49 PM</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>애플리케이션(Application)</t>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>사용자가 현재 사용 중인 MinIO 버전을 확인해 달라고 요청했습니다.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>고객이 현재 사용 중인 MinIO 버전을 확인해 달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>고객이 MinIO 버전을 확인하여 문제를 해결했습니다.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17431</t>
@@ -582,7 +602,11 @@
           <t>Kranthi03:56 PM</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>기능 및 사용법(Features &amp; Usage)</t>
@@ -590,12 +614,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>이슈가 #17431과 중복되는 것 같으므로, #17431에서 논의를 계속하도록 제안합니다.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>고객이 현재 이슈가 #17431과 중복된 것으로 보이며, #17431에서 논의를 계속하자는 요청을 했습니다.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>이슈가 #17431과 동일한 내용이므로 중복으로 판단됩니다.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>이슈를 #17431과 연결하거나 #17431으로 이슈를 이동/닫는 조치를 취합니다.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17430</t>
@@ -633,20 +669,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>고객은 MinIO pod의 RES 값이 노드마다 차이가 크고, buff/cache 메모리가 많이 차지하고 있는 상황을 보고, 메트릭이 해당 메모리를 포함하는지 확인하고 싶어했습니다. 또한 128-node 클러스터에서 일부 노드만 지속적으로 RSS가 3–5배 높은 이유와, 이러한 패턴이 서비스에 영향을 미칠 수 있는지 궁금해했습니다. 더불어 MinIO가 클라이언트 요청 이외에 내부 백그라운드 프로세스를 실행해 메모리를 더 사용하도록 하는지 물었습니다.</t>
+          <t>The user wants to know if MinIO has internal background processes that could cause higher resident memory usage on some nodes.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MinIO는 O_DIRECT 설정으로 인해 메타데이터 I/O가 페이지 캐시를 사용하고, 클러스터 전체에서 한 노드가 리더 락을 잡아 데이터-유스 스캐너와 배치 작업, 복제 리셈과 같은 백그라운드 서비스를 실행하기 때문에 RSS가 비정상적으로 높아집니다. 이러한 서비스는 리더 노드에서만 한 번씩 실행되므로 동일한 노드가 며칠간 높은 RSS를 보입니다. 또한 CPU 사용량이 높은 노드에서는 요청 수가 많아 에러리언과 I/O 버퍼가 메모리를 더 차지합니다.</t>
+          <t>High resident memory on certain nodes is caused by the node holding the leader lock for cluster-wide background services such as data-usage scanner, batch job scheduling, replication resync, site replication healer, and callhome, which keep aggregation state in memory. Additionally, the node runs at very high CPU usage, handling many concurrent requests, which further increases RSS.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>고객은 K8s 메모리 리밋을 지정하거나 서버 설정 파일에서 memLimit을 설정해 MinIO 프로세스의 메모리 사용을 제한할 수 있습니다. 또한 mc support profile --type mem,goroutines를 사용해 힙 프로파일을 캡처하고, mc admin info --json으로 리더 노드를 확인해 높은 RSS가 리더 락과 관련된 백그라운드 서비스 때문임을 검증하면 됩니다.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>To control memory usage, set a Kubernetes memory limit on the container or configure memLimit in the server startup configuration. Capture memory profiles with mc support profile --type mem to analyze the heap. Confirm which node is the leader via mc admin info --json and adjust cluster-level monitoring or admin traffic if necessary.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17428</t>
@@ -674,32 +714,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Felvine Sakwe</t>
+          <t>Felvine Sakwe, Harshavardhana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>네트워크(Network)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>고객은 AIStor 실행 중 Kubernetes 노드에서 메모리 사용량이 비정상적으로 높아지는 현상을 발견하고, MinIO 팀이 AIStor 관련 메모리 사용 현상을 인지하고 있는지 문의했습니다.</t>
+          <t>고객이 AIStor 실행 중인 노드에서 메모리 사용량이 비정상적으로 높으며, AIStor 또는 MinIO가 RSS/PSS에 나타나지 않는 메모리 사용이 있는지 여부와 추가 진단 방법을 문의했습니다.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NIC 드라이버 ice에서 발생한 CVE-2025-39948 버그로 커널 페이지 할당이 누수되어 약 560 GiB의 메모리가 비가시적으로 소비됩니다.</t>
+          <t>분석 결과, Intel ice NIC 드라이버의 메모리 누수(CVE-2025-39948)가 메모리 사용량 증가를 유발하고 있으며, 이는 커널 페이지 할당자로부터 직접 할당된 페이지이기 때문에 RSS/PSS에 나타나지 않습니다.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>커널을 6.12.0-55.72.1.el10_0 이상으로 업데이트하고 재부팅하면 누수된 메모리가 해제됩니다.</t>
+          <t>해결책은 ice 드라이버가 포함된 6.12.0-55.72.1.el10_0 이상의 커널로 업그레이드하고 재부팅한 뒤, 메모리 사용량을 모니터링하며, 필요 시 롤링 업데이트를 수행하는 것입니다.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>해당 문제는 AIStor 자체와 무관하며, 재부팅 시 메모리 누수가 정리됩니다.</t>
+          <t>문제는 AIStor가 아니라 Intel ice NIC 드라이버의 커널 메모리 누수에 기인합니다.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -739,22 +779,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>고객은 XMinioStorageFull 오류의 정확한 원인을 알고 싶습니다. 또한, 드라이브 사용량 임계값을 확인하고 조정할 수 있는지 여부를 문의했습니다. 마지막으로, max_timeout과 preallocate 옵션을 변경하면 서비스 성능에 어떤 영향을 미칠지 궁금합니다.</t>
+          <t>고객은 XMinioStorageFull 오류의 정확한 원인을 파악하고, 드라이브 사용량 임계값을 확인하고 조정 가능한지, 그리고 max_timeout 및 preallocate 옵션을 변경해 문제를 해결할 수 있는지와 성능에 미치는 영향을 문의했습니다.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MinIO는 각 드라이브가 99% 사용량에 도달하면 쓰기를 일시적으로 중단하고, 특정 erasure set에 충분한 드라이브가 없으면 XMinioStorageFull 오류를 반환합니다. 고객 환경에서는 드라이브가 89% 사용량에 머물러 있지만, 일시적인 타임아웃이나 온라인 상태 변화로 인해 쿼럼이 깨져 오류가 발생했습니다.</t>
+          <t>오류는 드라이브가 실제로 가득 차서가 아니라, 쓰기 시점에 대상 복제 세트에서 충분한 드라이브가 사용 가능하지 않아 쿼럼을 만족하지 못할 때 발생합니다. 이는 드라이브가 일시적으로 타임아웃, 오프라인, 복구 중이거나 파일 시스템이 짧은 공간 오류를 일으킬 때 발생합니다.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>로그와 메트릭을 수집해 드라이브 타임아웃·오프라인 현황을 확인하고, 필요 시 max_timeout 값을 45–60초로 늘려 타임아웃으로 인한 드라이브 드롭을 줄입니다. preallocate 옵션은 성능에 영향을 미치지 않으므로 변경하지 않습니다. 평균 95% 사용을 목표로 한다면 드라이브 수준에서 사용률을 모니터링하고, 스케일업 전에 가장 높은 드라이브가 99%를 넘지 않도록 확장합니다.</t>
+          <t>서버 로그와 메트릭을 수집해 드라이브 타임아웃, 오프라인, 복구 활동을 확인하고, 필요 시 max_timeout 값을 늘려 드라이브가 타임아웃으로 인한 드롭을 방지합니다. preallocate 옵션은 문제 해결과 무관하며, 드라이브 사용량 분포를 모니터링하고 필요</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>추가 로그 및 메트릭 수집이 필요하다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -784,7 +824,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kranthi, Thomas</t>
+          <t>Kranthi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -794,18 +834,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>사용자는 12:35에 발생한 대량 요청이 12:50 이후에 goroutine 수를 급증시킬 수 있는지, 문제를 추적할 수 있는 방법, 그리고 API QoS 설정이 문제를 완화할 수 있는지 물었습니다.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>사용자는 12:35에 발생한 작업이 이후 goroutine 증가에 영향을 미쳤는지, mc support profile로 추적 가능한지, 특정 노드에서 데이터를 수집할 수 있는지, 서비스가 정상이라면 계속 운영해도 되는지, API QoS 설정 가이드라인과 초과 요청 시 동작 방식을 묻고 있다.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>디스크 I/O가 포화 상태가 되어 goroutine이 축적되었으며, 트래픽 패턴 변화와 ETL 작업으로 인해 읽기/쓰기 쿼럼 오류가 발생했다.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Prometheus v3 메트릭을 활용해 서버별 go_routine 수를 모니터링하고, 과거 요청률을 기준으로 API QoS에서 RPS와 concurrency를 제한하여 디스크 부하를 낮추며, 15‑20% 여유를 두고 설정해 정상 동작을 유지하도록 조정합니다.</t>
+          <t>Prometheus 메트릭을 활용해 goroutine 수를 모니터링하고, 과거 요청률을 기준으로 API QoS 임계값을 설정하며, 동시성 제한은 즉시 거부, RPS는 MaxDelay(1초) 후 429를 반환한다. 현재는 큐 길이나 대기 시간 조정 옵션이 없다.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>환경이 에어갭 상태여서 로그 및 프로파일 파일을 업로드할 수 없으며, 클러스터 전체에 대해 프로파일링이 가능해 특정 노드만을 대상으로 할 수 없습니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -835,30 +879,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kranthi, Jiuker</t>
+          <t>Jiuker, Kranthi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>고객이 MinIO 서버가 객체 수가 증가함에 따라 메모리 사용량이 상승하고, 내부 메모리 관리 또는 임계값이 있는지, 그리고 메모리 사용이 계속 증가할 경우 어떤 조치를 취해야 할지 문의했습니다.</t>
+          <t>사용자는 MinIO가 내부 메모리 관리나 임계값을 가지고 있는지, 메모리 사용량이 계속 증가하면 조치를 취해야 하는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MinIO의 메모리 사용은 객체 수에 비례하지 않고 작업 부하에 따라 변동하며, 현재 Pod 메모리 제한 128 GiB 안에서 3~7 GiB 사이를 오가고 있습니다.</t>
+          <t>메모리 사용량은 객체 수와 비례하지 않고, 작업과 가비지 컬렉션에 따라 변동하며, 현재 3~7 GiB 사이에서 주기적으로 변동하고 있습니다.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>메모리 사용이 90% 이하로 안정되면 정상으로 판단하고, 90%를 초과하며 지속적으로 상승하면 병렬 작업을 줄이거나 Pod 메모리 제한을 늘려야 합니다.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>메모리 사용량이 Pod 한계의 약 90%를 안정적으로 유지하면 정상이며, 90%를 초과하면 병렬 작업을 줄이거나 Pod 메모리 한계를 늘려야 합니다.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17388</t>
@@ -891,25 +939,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>스토리지(Storage)</t>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RIA CHOI는 객체가 워밍 트리에 성공적으로 전환되었음에도 원본 클러스터의 저장소 사용량이 감소하지 않는 것이 정상인지 궁금해했습니다. 또한, 전환 후 실제로 핫 티어에서 객체가 삭제되었는지 확인하고 회수된 저장 용량을 보는 방법을 요청했습니다. 그리고 대상 클러스터에서 객체 수와 사용량이 증가했다가 감소하는 현상에 대한 설명을 구했습니다.</t>
+          <t>사용자는 객체 티어링 후 소스 클러스터의 저장소 사용량이 감소하지 않는 것이 정상인지, 실제 회수된 저장소 용량을 확인하는 방법과 타깃 클러스터에서 사용량이 감소하는 이유를 문의했습니다.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>트리거는 데이터의 물리적 위치만 변경하므로 논리적 사용량 카운터는 여전히 전체 객체 크기를 그대로 표시합니다. 전환된 객체의 메타데이터가 핫 티어에 남아 있어 스캐너가 다음 주기까지 물리적 공간이 해제되는 것을 반영하지 못합니다. 콘솔에서 보여지는 드라이브 기반 수치는 회수된 공간을 나타내지만, 버킷 사용량은 변하지 않습니다.</t>
+          <t>티어링은 데이터만 이동하고 메타데이터는 남아 있어 논리적 사용량은 변하지 않으며, 실제 물리적 사용량은 드라이브 기반 지표에서만 감소합니다. 또한, 스캐너 주기와 미완성 멀티파트 업로드 정리로 인해 사용량이 변동될 수 있습니다.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>핫 티어 노드의 드라이브 자유 공간(예: df 또는 zmc admin info)을 확인해 회수된 용량을 파악합니다. mc ilm tier info를 사용해 각 티어별 사용량과 객체 수를 보고, mc stat으로 객체의 스토리지 클래스를 확인합니다. 멀티파트 업로드나 덮어쓰기가 발생하면 대상 클러스터 사용량이 일시적으로 증가한 뒤 24시간 후 자동 정리로 감소합니다.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>mc ilm tier info와 mc stat 명령으로 각 티어의 사용량과 객체 상태를 확인하고, df 명령으로 물리적 드라이브 사용량을 모니터링하면 실제 회수된 용량을 확인할 수 있습니다. 또한, 스캐너 주기와 멀티파트 업로드 정리 시간을 고려해 사용량 변동을 이해하면 됩니다.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17386</t>
@@ -937,7 +989,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jiuker, Prakash</t>
+          <t>Jiuker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -947,24 +999,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The user requests confirmation of current and planned support for prefix-level metrics such as storage usage, object count, API activity, quota, owner, usage statistics, alias mappings, and the ability to create and manage prefixes ahead of time like directories.</t>
+          <t>고객이 버킷의 프리픽스 수준에서 저장소 사용량, 객체 수, API 활동 등의 메트릭을 실시간으로 확인하고, 프리픽스에 대한 할당량, 소유자, 사용 통계, 별칭 매핑 등을 관리하고 싶어한다.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Currently there are no real-time prefix-level metrics or metadata.
-Inventory generation provides periodic data only.
-Prefixes are treated as part of the flat object namespace rather than as folders.</t>
+          <t>프리픽스 수준의 메트릭은 현재 MinIO에서 지원되지 않으며, 객체 스토리지의 네임스페이스가 평면적이기 때문에 프리픽스를 폴더처럼 관리할 수 없기 때문이다.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Use the ILM UI and the 'mc inventory generate' command to obtain prefix-level object count and size, though this data is periodic.
-The 'mc du' command can calculate usage, but it is not recommended for large prefixes due to high I/O load.
-Prefix-level quota, owner, usage statistics, and pre-creation of prefixes are not supported at this time.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>현재는 mc inventory를 사용해 주기적으로 프리픽스 객체 수와 크기를 확인할 수 있지만, 실시간 메트릭은 제공되지 않는다. mc du를 사용해 사용량을 계산할 수 있으나 대규모 프리픽스에서는 I/O 부하가 크다. 프리픽스에 대한 할당량, 소유자, 별칭 매핑 등은 버킷 수준에서만 지원된다.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17358</t>
@@ -997,27 +1049,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>RIA CHOI는 AIStor IAM 관리 오버헤드를 줄이기 위해 Apache Polaris와의 연동을 통해 Polaris가 권한 부여를 처리할 수 있는 방법이 있는지 문의했습니다.</t>
+          <t>RIA CHOI는 AIStor IAM 관리 오버헤드를 줄이기 위해 Apache Polaris와 AIStor를 통합해 Polaris가 외부 인증 서비스를 통해 권한을 처리하도록 하고 싶어합니다.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Polaris가 테이블 카탈로그 수준에서 권한을 조회하고 AIStor가 S3 객체 수준에서 권한을 확인하기 때문에 두 시스템 간 연동이 복잡하고 번역 오버헤드가 발생합니다. 이러한 차이로 인해 통합이 단순화 목표를 달성하지 못할 수 있습니다.</t>
+          <t>AIStor IAM 정책 관리를 직접 수행하는 것이 복잡하고 관리 오버헤드가 크기 때문입니다.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AIStor는 외부 시스템에 접근 관리를 위임할 수 있는 Authorization Plugin을 제공하며, 이를 활용해 외부 인증 서비스를 연결할 수 있습니다. 하지만 Polaris와 AIStor의 레벨 차이로 인한 변환 오버헤드를 고려하면 AIStor 테이블 기반 PBAC를 권장합니다. 필요 시 AIStor 테이블에 대한 데모를 제공할 수 있습니다.</t>
+          <t>AIStor는 Authorization Plugin을 통해 외부 시스템에 접근 관리를 위임할 수 있으며, Polaris와의 통합은 테이블 카탈로그 수준과 S3 객체 수준의 차이로 인해 번역 오버헤드가 발생할 수 있습니다. 대신 AIStor 테이블을 사용해 PBAC를 단일 포인트로 관리하면 카탈로그 레이어 오버헤드를 제거할 수 있습니다.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Kranthi는 AIStor 테이블을 활용하면 카탈로그 레이어 오버헤드를 제거하고 PBAC를 단일 포인트로 관리할 수 있다고 안내했습니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1057,20 +1109,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>고객이 버킷이 할당량을 초과했음에도 인벤토리 보고서가 계속 작성되는 현상이 예상되는지 문의했습니다.</t>
+          <t>사용자가 버킷에 할당량을 설정했는데, 인벤토리 리포트가 할당량 초과 후에도 계속 기록되는 현상이 발생했습니다. 이 동작이 정상인지 확인하고 싶어했습니다.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MinIO AIStor의 할당량 검증은 내부 스캐너에 의해 주기적으로 수행되며, 인벤토리 같은 내부 프로세스는 현재 할당량 적용 대상이 아닙니다.</t>
+          <t>인벤토리 프로세스는 현재 내부 프로세스로서 버킷 할당량 검증을 거치지 않기 때문에 할당량 초과 시에도 기록이 계속됩니다.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>인벤토리 프로세스는 할당량이 적용되지 않으므로 현재 그대로 사용하며, 향후 필요 시 문서에 추가 정보를 제공하도록 했습니다.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>현재 인벤토리는 할당량 검증을 거치지 않으므로 별도의 해결책이 필요 없으며, 향후 내부 프로세스에 대한 할당량 적용 옵션이 개발될 예정입니다.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Scanner는 주기적으로 할당량을 평가하며, 실시간이 아니므로 잠시 초과가 발생할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17348</t>
@@ -1108,20 +1164,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>사용자는 AIStor가 대규모 쿠버네티스 환경에서 사용될 때 가장 적합한 로드 밸런싱 방식을 찾고자 한다. 특히 AIStor 전용 튜닝 파라미터, 클라이언트 측 설정(연결 풀, Keep-Alive, 멀티파트 등), 그리고 워크로드 특성이 로드 분포와 대역폭에 미치는 영향에 대한 권장사항을 요청했다. 또한 ECMP와 같은 서버‑사이드 로드 밸런싱을 활용한 베스트 프랙티스와 참조 아키텍처를 원한다.</t>
+          <t>The user requested guidance on the most suitable load balancing strategy for AIStor in large‑scale Kubernetes deployments, including server‑side and client‑side options, tuning parameters, and best practices to achieve even request distribution and high throughput. They also asked whether recommendations differ based on workload patterns such as sequential GET/PUT, ETL, or analytics. Additionally, they sought advice on AIStor‑specific settings and network configuration to optimize load balancing.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>로드 밸런싱이 제대로 구성되지 않거나 단일 엔드포인트에 대한 요청이 특정 노드에 집중될 때, 요청이 균등하게 분산되지 않는다. 특히 지속적인 HTTP 연결 재사용은 특정 노드에 트래픽을 몰아 집중도를 높인다. 현재 사용 중인 로드 밸런싱 옵션(인그레스, Cilium BGP, Global Service)이 요청 분산을 충분히 지원하지 못해 이 문제가 발생한다.</t>
+          <t>Requests were observed to cluster on a subset of MinIO pods, indicating uneven load distribution across the cluster. This unevenness may stem from the default load balancing algorithm or from persistent HTTP connections that cause request stickiness.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MinIO는 일반 S3 클라이언트에게는 서버‑사이드 LB를 사용할 때 무작위(random) 선택 알고리즘을 권장한다. 그러나 Spark, Trino 같은 제한된 클라이언트의 경우 요청 수준에서 균등 분산을 보장하기 위해 Sidekick을 사용하도록 권장한다. Sidekick에서는 --host-balance 옵션을 'random'으로 설정하거나 기본 least를 활용해 요청 레벨에서 분산을 개선할 수 있다.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>MinIO recommends using server‑side load balancing with a random selection algorithm for general S3 clients, and employing sidekick for fixed, limited clients such as Spark or Trino to distribute requests at the request level.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17342</t>
@@ -1159,20 +1219,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>고객은 빈 디렉터리 접두사가 삭제 후에도 남아 있는 이유와 --purge 옵션을 사용해야만 완전 삭제가 가능한 이유를 이해하고 싶어하며, 이를 완전히 제거하는 방법을 알고 싶어합니다.</t>
+          <t>고객은 빈 디렉터리처럼 보이는 프리픽스(prefix2)를 찾았으며, mc ls 명령으로 확인했지만 실제 객체가 없었습니다. mc rm -r --force 명령으로 삭제를 시도했지만 프리픽스가 여전히 보입니다. 이 문제를 해결하고 프리픽스를 완전히 제거하려면 어떻게 해야 하나요?</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>mc rm 명령이 --purge 옵션 없이 실행되면 일부 디스크에서 동기화가 완전히 이루어지지 않아 남은 디렉터리 엔트리가 남게 됩니다. 이는 버전이 비활성화된 버킷에서도 발생할 수 있으며, --purge는 모든 디스크에 물리적 삭제를 강제해 이러한 잔여 항목을 제거합니다.</t>
+          <t>MinIO는 디렉터리 마커를 물리적으로 삭제하지 않으면 남아있게 됩니다. mc rm 명령을 --purge 옵션 없이 실행하면 디스크에 남아 있는 디렉터리 잔여물이 남아 삭제가 완전하지 않습니다.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>mc rm -r --force --purge alias/bucket/prefix1/prefix2 명령을 사용하여 물리적으로 삭제를 강제하면 빈 디렉터리 접두사가 완전히 제거됩니다. 버전이 비활성화되어 있으므로 삭제 마커가 없으므로 위험이 최소화됩니다.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>mc rm -r --force --purge를 사용하면 디스크에서 물리적으로 삭제되어 빈 디렉터리 프리픽스가 완전히 사라집니다. 이 옵션은 데이터 손실 위험이 있으므로 주의해서 사용해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17316</t>
@@ -1200,32 +1264,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Felvine Sakwe</t>
+          <t>Bala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>RIA CHOI가 DirectPV 5.0.2에서 발생한 드라이브 오류와 라이선스 체크로 인한 복구 실패를 해결하기 위해 업그레이드 및 복구 절차를 문의했고, 오류 드라이브를 재활성화하고 조건 로그를 정리하는 방법을 요청했다.</t>
+          <t>The user asks whether it is safe to run helm upgrade directpv minio/directpv in their environment. They also want to know how to repair a drive that remains in Error state after reboot. Additionally, they ask whether the drive should be replaced if it stays Error after xfs_repair and how to reset its state and clear condition logs.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DirectPV 5.0.2는 여전히 라이선스 Secret을 요구하므로 복구 작업이 실패하며, 드라이브가 파일시스템 오류로 Error 상태에 머무를 때는 DirectPV가 드라이브를 자동으로 Ready로 전환하지 못한다.</t>
+          <t>The repair job fails because DirectPV 5.0.2 still checks for a valid license secret, which is not present, causing the job to abort before repair. This requirement was removed in DirectPV 5.1.0+, allowing repair to proceed.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DirectPV를 5.1.0+ 버전으로 업그레이드한 뒤, 드라이브를 suspend → repair → resume 순으로 복구하고, xfs_repair 후 node-server를 재시작한다. 직접 상태를 Ready로 변경하려면 kubectl patch 명령으로 status.conditions를 비워 주고 node-server를 재시작해 재조정하도록 한다.</t>
+          <t>Upgrade DirectPV to 5.1.0+ to remove the license check, then suspend the faulty drive, restart the volume consumer pods, run kubectl directpv repair, and resume the drive. If the repair job still fails due to license, manually unmount the drive, run xfs_repair, and restart the node-server. After confirming the drive is healthy, reset its state from Error to Ready by editing or patching the DirectPVDrive resource and clear the DriveHasIOError condition from status.conditions.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DirectPVDrive 리소스 이름은 UUID가 아니라 드라이브 ID이며, 조건 로그를 정리할 때는 --subresource=status 옵션이 필요하다.</t>
+          <t>Manual mount after xfs_repair is not recommended; node restart is sufficient.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1265,16 +1329,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>고객은 AttachDetachPolicyLDAP API가 40~50초 동안 지연되는 원인을 파악하기 위해 필요한 추가 메트릭과 로그를 요청했습니다. 특히, IAM 서브시스템이 전역 잠금을 획득할 때 다른 API 요청에 미치는 영향과 잠금 대기 큐 길이를 확인하고자 합니다. 또한, 이 연산이 비즈니스 시간대에 수행되는 것이 적절한지 여부도 궁금합니다.</t>
+          <t>Youngkyoo Kim requested guidance on additional metrics or logs to investigate the 40-50 second delay when executing the mc idp ldap policy attach command, specifically whether the AttachDetachPolicyLDAP API acquires a lock that can block concurrent requests. He also asked for clarification on which APIs are affected by the write lock, whether policy mapping operations should be avoided during business hours, and how to monitor pod internal wait queue length or lock wait queue. Additionally, he requested metrics to monitor pod internal wait queue length or lock wait queue to see how long requests were queued.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>AttachDetachPolicyLDAP는 정책 매핑 시 쓰기 잠금을 획득하며, 대량 요청이 동일 노드에서 처리될 때 잠금 대기 시간이 길어져 전체 요청 지연이 발생합니다. 이로 인해 Goroutine 수가 급증하고, 10~50초의 응답 시간이 기록됩니다.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>The delay was caused by contention on the IAM subsystem's write lock, which is acquired by the AttachDetachPolicyLDAP API when processing policy mapping requests. When many concurrent requests are processed on the same node, the lock acquisition time can become long, leading to goroutine spikes and high response times. The high goroutine count and lack of minio_api_requests_waiting_total increase suggest that the queue was not full, but the lock contention still caused long wait times for new requests.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Jiuker recommended running policy mapping operations during low peak periods or on a different node to reduce lock contention, and suggested using load balancing to distribute the load. Monitoring metrics such as minio_api_requests_waiting_total, minio_api_requests_incoming_total, and pod CPU/memory/disk I/O can help identify when the system is under heavy load and when lock contention occurs. Reviewing audit logs for high TTFB on ListObjects/ListObjectsV2 and checking lock wait queue length can confirm whether the write lock was the sole cause of the delay.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17274</t>
@@ -1312,22 +1384,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>사용자는 객체 브라우저에서 ‘새 경로 만들기’ 기능이 실제 접두어를 생성하는지, 혹은 이후 객체 업로드를 위한 논리적 경로만 제공하는지에 대해 명확히 해달라고 요청했다. 또한 mc mb 명령으로 생성된 빈 접두어가 0바이트 객체인지, 이로 인해 충돌이 발생할 가능성이 있는지 궁금했다.</t>
+          <t>The user wants to know whether creating a new path in the Object Browser actually creates a persistent prefix in AIStor, and whether the mc mb command creates a zero‑byte folder marker. They also ask if there is an API to create such a marker and whether the observed 0B folder marker is expected or problematic.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>mc mb 또는 객체 브라우저에서 경로를 만들면 AIStor에 0바이트 길이의 접두어(폴더 마커) 객체가 생성된다. 이 객체는 실제 디렉터리로서 존재하지만, 나중에 동일한 접두어로 객체를 업로드하면 충돌이 발생한다.</t>
+          <t>The console treats prefixes as logical representations that disappear if no objects are uploaded. The mc mb command creates a zero‑byte object with a trailing slash, which is considered a folder marker and can cause conflicting objects. This behavior is by design but is discouraged.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>접두어를 만들 때는 mc mb 같은 명령을 사용하지 말고, 객체를 업로드할 때 접두어 경로를 함께 지정해 자동으로 생성되도록 한다. 이미 존재하는 0바이트 접두어가 있다면 삭제하고, ls -r --versions 로 충돌 여부를 확인한다. 이 방법이 충돌을 방지한다.</t>
+          <t>Do not use mc mb to create prefixes; instead upload objects directly with the desired prefix. Use mc ls -r and mc stat -r to confirm no folder marker exists. If a zero‑byte folder marker is present, delete it and upload objects normally; there is no separate API for creating a folder marker.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>콘솔에서도 접두어를 만들면 객체를 업로드해야만 유지되도록 설계된 것이므로, 이는 의도된 동작임을 명시하였다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1367,16 +1439,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>고객은 10.6 PiB 규모의 클러스터에서 ListObjectsV2 요청이 많아 goroutine 수가 급증하고, 이로 인해 일시적인 quorum loss 오류가 발생하는지 궁금합니다.</t>
+          <t>고객은 대용량 ListObjectsV2 요청이 중단(Quorum loss) 현상을 유발하는지 확인하고, 클러스터 리소스 사용량과 노드 오프라인 원인을 분석하기 위해 지원 프로파일을 제공하고 메트릭을 검토하도록 요청했습니다.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>다수의 ListObjectsV2 요청이 클러스터에 과부하를 주어 goroutine 수가 급증했고, 이로 인해 노드/드라이브가 오프라인으로 표시되고 5xx 오류와 quorum loss가 발생했습니다.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Heavy ListObjectsV2 requests cause high goroutine counts, leading to cluster stress, intermittent 5xx errors, read quorum errors, and temporary node/drive offline events.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>지원팀은 ListObject V2 요청량을 모니터링하고, 응답 시간을 기준으로 정렬하여 비효율적인 요청을 식별하며, QoS 정책을 적용해 대규모 재귀 목록 생성을 제한하고, 대시보드를 통해 노드 오프라인 원인을 파악하도록 권고했습니다.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17268</t>
@@ -1409,21 +1489,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>스토리지(Storage)</t>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>고객이 AIStor에서 NFS 기능을 테스트하고자 하여 필요한 바이너리를 제공해달라고 요청했습니다.</t>
+          <t>Youngkyoo Kim requested the necessary binaries to test the NFS functionality of AIStor.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>AIStor는 기본적으로 NFS를 지원하지 않는다는 것이 명시되었습니다.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>AIStor does not natively support NFS, which is why the binaries are not available.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Arvind Gupta will collaborate with Jihun Na to understand the use case and determine next steps.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17267</t>
@@ -1461,22 +1549,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>사용자가 Polaris를 통해 DB 경로를 삭제하지 못하도록 하고, 테이블 경로만 삭제를 허용하는 S3 정책이 가능한지 문의했습니다.</t>
+          <t>사용자가 S3 정책을 사용해 데이터베이스 경로(user/${EMP_ID}/my_${EMP_ID}_catalog/${DB_NAME})에 대한 삭제 권한을 제한하고, 테이블 경로(user/${EMP_ID}/my_${EMP_ID}_catalog/${DB_NAME}/${TABLE_NAME})에 대해서만 삭제 권한을 부여할 수 있는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>S3 정책에서는 경로를 단일 수준으로 제한할 수 없으며, 모든 객체가 개별적으로 삭제되기 때문에, 디렉터리 수준에서 삭제를 차단하려면 deny가 모든 하위 객체를 차단해 버립니다.</t>
+          <t>사용자가 Polaris를 우회해 AIStor 경로에서 테이블을 삭제할 때, 마지막 테이블을 삭제하면 데이터베이스 디렉터리가 사라져 Polaris가 동기화되지 않아 새 테이블 생성이 실패합니다.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sentinel 파일을 DB 생성 시 넣어 DB 디렉터리를 남겨 두고, S3 정책에서 "s3:DeleteObject"를 두 단계 아래 객체에만 허용하도록 설정하며 sentinel 파일 삭제를 deny하고, Sentinel 파일은 특권 아이덴티티로만 생성하도록 조치했습니다.</t>
+          <t>각 데이터베이스 생성 시 sentinel 파일(.sentinel)을 만들고, 해당 파일에 대한 DeleteObject와 PutObject를 Deny하도록 S3 정책을 설정하며, 테이블 수준 이하에 대해서만 DeleteObject를 Allow하도록 구성하면 데이터베이스 디렉터리는 유지되고 테이블 삭제는 가능해집니다.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sentinel 방식을 사용하면 버전링 없이도 DB 디렉터리가 사라지는 문제를 해결할 수 있고, Polaris를 통한 삭제만을 권장해 근본적인 원인을 차단합니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1504,7 +1592,11 @@
           <t>Youngkyoo Kim11:26 AM</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>기능 및 사용법(Features &amp; Usage)</t>
@@ -1512,12 +1604,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>고객은 MinIO AIStor가 AWS S3 Files와 비슷한 NFS/POSIX 공유 파일 시스템 레이어 기능을 지원하는지, 혹은 향후 로드맵에 포함될 예정인지 문의했습니다.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>고객이 MinIO AIStor가 AWS S3 Files와 유사한 NFS/POSIX 공유 파일 시스템 레이어를 현재 지원하는지, 혹은 향후 로드맵에 이 기능을 구현할 계획이 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17179</t>
@@ -1545,7 +1649,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kranthi</t>
+          <t>Kranthi, Harshavardhana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1555,22 +1659,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>고객이 감사 로그에서 높은 빈도로 발생하는 HealObject 이벤트가 정상적인 동작인지 확인해 달라고 요청했습니다. 또한 업그레이드 전까지 이 메시지를 무시해도 되는지 묻는 질문도 함께 했습니다.</t>
+          <t>고객이 MinIO 감사 로그에서 HealObject 이벤트가 높은 빈도로 발생하는 것이 정상인지 확인해 달라고 요청했습니다.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>해당 로그는 실제로 복구가 수행되지 않았음에도 불구하고 로그에 기록되는 버그로 인해 발생했습니다.</t>
+          <t>heal audit 로그가 실제 치유가 일어나지 않아도 기록되도록 구현되어 있어, 많은 HealObject 이벤트가 발생했습니다.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>RELEASE.2026-04-11 이상의 버전으로 업그레이드하면 이 로그 스팸이 사라집니다. 업그레이드 전까지는 해당 메시지를 안전하게 무시해도 됩니다.</t>
+          <t>RELEASE.2026-04-11 이후 버전으로 업그레이드하면 해당 로그가 제거됩니다. 업그레이드 전까지는 무시해도 됩니다.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>고객이 현재 저장소 사용률이 92%에 달하며, 인오드 사용량을 확인할 것을 권장했습니다.</t>
+          <t>현재 사용 중인 버전은 RELEASE.2026-02-07이며, 용량 사용률이 92%에 달합니다.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1610,20 +1714,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>고객이 inventory 작업을 실행 중에 삭제했을 때 발생하는 오류 메시지와 원인, 해결 방법을 문의했습니다.</t>
+          <t>사용자가 mc inventory put 명령으로 인벤토리 작업을 시작한 뒤, 실행 중일 때 삭제하고, 이후 'missing request or run metadata' 오류가 발생해 어떻게 처리해야 하는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>삭제 명령이 실행 중인 inventory 작업의 내부 상태를 제거하지 않아, 상태 조회 시 메타데이터가 없다는 오류가 발생했습니다.</t>
+          <t>인벤토리 작업이 실행 중일 때 삭제하면 내부적으로 작업이 계속 실행되고, 메타데이터가 사라져 상태 조회 시 오류가 발생합니다.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>먼저 mc inventory cancel 명령으로 실행 중인 작업을 정상적으로 중지한 뒤, mc inventory rm 명령으로 작업 구성을 삭제합니다.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>mc inventory cancel 명령으로 실행 중인 작업을 정상적으로 중지한 뒤, mc inventory rm 명령으로 인벤토리 구성을 삭제하면 오류가 해결됩니다.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17167</t>
@@ -1656,25 +1764,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>고객이 18개의 MinIO 노드 중 2개의 노드가 30분간 NotReady 상태가 되면서 OOM 이벤트가 발생하고, Spark executor가 설치되었으나 메모리 사용량이 크게 보이지 않아 원인 파악을 요청했습니다.</t>
+          <t>고객은 18개의 MinIO 노드 중 2개에서 30분간 Intermittent Node NotReady 이벤트가 발생하고, OOM이 발생한 원인을 파악하고 싶어합니다.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>500GB 노드의 inode 캐시(xfs_inode)와 lsm_inode_cache가 305GB에 달해 메모리 절대량을 차지하고, MinIO가 19%(약 95GB) 메모리를 사용하며 Spark 실행이 72GB를 추가로 차지해 총 470GB가 되면서 커널 OOM이 발생했습니다.</t>
+          <t>노드의 커널 inode 캐시(xfs_inode)가 500GB 노드에서 약 305GB를 차지하고, MinIO가 19%(95GB)와 Spark 실행 시 72GB를 추가로 사용해 총 470GB를 초과해 OOM이 발생했습니다.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AIStor 노드에서 Spark 실행을 중지하고, Spark 파드에 실제 메모리 요청/제한을 설정하며, 필요 시 MinIO 포드를 일시 중지 후 drop_caches를 실행해 inode 캐시를 해제하고, 노드 메모리를 늘리는 것을 검토합니다.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Spark 실행을 AIStor 노드에서 제외하고, Spark 파드에 메모리 요청/제한을 설정하며, MinIO 파드를 중지한 뒤 drop_caches 명령으로 inode 캐시를 비우는 것이 권장됩니다.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>500GB 노드가 가장 메모리 여유가 적어 OOM에 취약했습니다.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17142</t>
@@ -1712,20 +1824,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>사용자는 minio 서비스가 포트 9000에 두 개의 포트 이름(http‑minio와 management)을 가지고 있음을 발견하고, 각 포트 이름의 의도된 목적과 내부 사용자에게는 어떤 엔드포인트를 사용해야 하는지를 문의했습니다.</t>
+          <t>Ria는 9000번 포트에 두 개의 포트 이름(http‑minio와 management)이 있는 이유와 내부 사용자가 어떤 포트 이름을 사용해야 하는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>포트 9000에 두 개의 포트 이름이 지정되어 있어 혼란이 생긴 상태이며, 관리 포트 이름이 MinIO Operator에 의해 정의되지 않은 점이 불확실성을 높였습니다.</t>
+          <t>MinIO Operator가 동일 포트에 여러 포트 이름을 정의하고, 'management' 포트 이름은 표준 정의에 포함되지 않아 혼란이 발생했습니다.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Javier는 MinIO Operator가 정의한 표준 포트 이름을 설명하고, 내부 사용자는 객체 작업을 위해 http‑minio(또는 TLS가 활성화된 경우 https‑minio) 포트 9000을 사용해야 함을 안내했습니다. 관리 포트 이름은 정의되지 않았으므로 Cesar Celis에게 확인을 요청했습니다.</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>내부 사용자는 TLS가 비활성화된 경우 http‑minio, TLS가 활성화된 경우 https‑minio를 사용하여 9000번 포트에서 객체 작업을 수행해야 합니다. 'management' 포트 이름은 표준이 아니므로 별도로 확인이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17140</t>
@@ -1758,25 +1874,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>스토리지(Storage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ria가 'operation lock timed out' 오류가 무엇을 의미하며, 왜 그로 인해 포드에서 goroutine이 급증했는지를 설명해 달라고 요청했습니다.</t>
+          <t>고객이 pod에서 'operation lock timed out' 오류가 발생하고 goroutine 수가 급증한 원인과 의미를 문의했습니다. 오류가 최근에만 발생했으며, 5/21, 5/22, 5/26에 각각 한 번씩 발생했다고 보고했습니다.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>이 오류는 포드가 분산 락을 획득하는 데 필요한 정족수를 일정 시간 안에 충족하지 못했음을 나타내며, 흔한 원인은 락을 보유한 장기 작업, 포드 간 일시적 네트워크 지연, 또는 느린 디스크 I/O입니다.</t>
+          <t>분산 락을 획득하지 못해 타임아웃이 발생했으며, 이는 장시간 실행되는 작업, 일시적인 네트워크 지연, 느린 드라이브 I/O 등이 원인일 수 있다. 락을 획득하려는 노드가 quorum에 도달하지 못해 발생한다. goroutine 수가 급증한 것은 락 대기 중인 요청이 한꺼번에 풀리면서 발생하는 정상적인 현상이다.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>우리는 문제를 모니터링하고, 재발 시 해당 포드의 로그를 수집한 뒤 'mc admin profile --type goroutine' 명령으로 블로킹 작업을 확인하도록 권고했습니다. 빈번하게 발생하지 않는 한 즉각적인 조치는 필요하지 않습니다.</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>MinIO 로그를 확인하고, goroutine 스파이크 시점에 mc admin profile --type goroutine 명령을 실행해 블로커를 확인한다. 오류가 빈번해지면 모니터링을 계속하고 필요 시 지원팀에 문의한다.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17139</t>
@@ -1804,30 +1924,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kranthi</t>
+          <t>Felvine Sakwe, Kranthi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>스토리지(Storage)</t>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>고객이 노드 드레인 중 메트릭이 상승한 것이 정상인지 확인 요청했습니다.</t>
+          <t>고객이 노드를 드레인할 때 minio_cluster_health_capacity_usable_total_bytes와 minio_cluster_health_capacity_usable_free_bytes가 증가하는 현상이 정상인지 확인 요청</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>드레인된 드라이브가 0 총 공간 보고 시 메트릭 계산이 불량해져 다른 풀의 공간이 포함돼 값이 상승했습니다. 이 버그는 다중 풀 환경에서 발생했습니다.</t>
+          <t>드레인된 드라이브가 TotalSpace=0으로 보고되면, 메트릭 계산 시 다른 드라이브의 공간을 포함해 합산해 버리는 버그가 존재</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Kranthi가 버그를 찾고 고친 버전을 릴리스했습니다. 고객은 새 버전으로 업그레이드하면 정상됩니다.</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>버그를 수정한 새로운 버전(Release.2026-05-28T20-50-32Z)을 배포하고 업그레이드</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Diagnostics check에서 metric이 일시적으로 증가 후 복구되는 것을 확인</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17116</t>
@@ -1865,22 +1989,22 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>고객이 디스크 교체 후 복구 중에 minio_cluster_erasure_set_write_tolerance 메트릭이 3에서 4로 증가한 이유와 복구 속도를 높이기 위한 설정 조정 방법을 문의했습니다.</t>
+          <t>사용자는 헬링 중에 minio_cluster_erasure_set_write_tolerance 값이 3에서 4로 변하는 이유와 정상인지, 그리고 헬링 속도를 높이기 위한 설정 조정 방법을 문의했습니다.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>복구가 진행될 때 MinIO는 손상된 드라이브 수에 따라 parity를 1씩 증가시켜 쓰기 허용 오류 수를 3에서 4로 높이는 동작을 수행합니다.</t>
+          <t>헬링 중 드라이브가 오프라인이거나 복구 중일 때, MinIO는 자동으로 파리티를 +1씩 업그레이드하여 새 쓰기가 EC:4로 처리되므로, minio_cluster_erasure_set_write_tolerance 값이 4로 증가합니다.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>heal 서브시스템의 max_sleep, max_io, drive_workers 값을 낮추고 서비스 재시작해 복구 속도를 높이며, 클러스터 활용률이 70%일 때 I/O 대기 시간이 병목인지 모니터링하도록 안내했습니다.</t>
+          <t>heal 서브시스템의 max_sleep을 0s, max_io를 10000, drive_workers를 적절히 늘리고 서비스 재시작하여 헬링 스루풋을 높일 수 있습니다. 또한 70% 클러스터 활용도에서는 소스 드라이브 I/O 대기 시간이 병목이므로 minio_node_drive_reads_await를 모니터링하며 필요 시 조정합니다.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>I/O 대기 시간이 병목이 될 가능성이 있으므로, 드라이브 읽기 지연을 관찰해 설정을 조정해야 합니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1915,21 +2039,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>네트워크(Network)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim은 Cilium BGP가 10초간 연결이 끊겼다가 1분 뒤 재연결하면서 5xx 오류가 발생하고 GFP_ATOMIC 할당 오류를 관찰했다고 보고했습니다. Red Hat은 메모리 부족을 의심하며 vm.min_free_kbytes 값을 두 배 또는 네 배로 늘리면 AIStor 측에 영향을 미칠 수 있는지 확인해 주실 것을 요청했습니다. 따라서 그는 AIStor 측에 이 값을 증가시켜도 문제가 발생하지 않는지 검증해 주길 바랍니다.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>고객이 vm.min_free_kbytes 값을 2배 또는 4배로 증가시킬 경우 AIStor에 미치는 영향이 있는지 확인해 달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Red Hat 보고서에 따르면, GFP_ATOMIC 할당 실패가 메모리 부족으로 인한 것으로, 네트워크 패킷이 드롭되고 5xx 오류가 발생했습니다.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Kranthi는 AIStor가 vm.min_free_kbytes에 대한 구체적 권장 사항이 없으며, 표준 기준에 따라 값을 증가시킬 수 있다고 답변했습니다. 그는 또한 transparent_hugepage와 같은 다른 메모리 매개변수를 검토할 것을 제안했습니다. 그리고 비프로덕션 환경에서 먼저 테스트해 보고 결과를 관찰할 것을 권고했습니다.</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>AIStor에서는 vm.min_free_kbytes에 대한 구체적 권장값이 없으며, 표준에 따라 값을 늘리고, 다른 메모리 파라미터(transparent_hugepage 등)를 검토하며, 비프로덕션 환경에서 먼저 테스트해 보는 것이 좋습니다.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17065</t>
@@ -1957,7 +2089,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>R RIA CHOI</t>
+          <t>RIA CHOI, Kranthi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1967,22 +2099,22 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>고객은 객체스토어 pod의 readiness probe 실패와 EC set quorum 오류 발생 원인, 그리고 이러한 현상이 다른 풀에도 영향을 미치는 조건과, 반복되는 30 EC set 오류가 정상인지 여부를 문의했다.</t>
+          <t>고객은 readiness probe 실패와 EC 세트 쿼럼 오류가 발생한 원인과 이를 방지하기 위해 주의해야 할 환경 요소를 파악하고자 한다. 또한, EC 세트 tolerence가 최소 수준으로 떨어지는 상황과 30개 EC 세트에서 동시에 발생한 쿼럼 오류의 원인을 알고 싶어한다.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>pod 0-47이 직접 엔드포인트로 과도한 요청을 받아 goroutine 수가 급증하고 메모리 사용량이 증가하면서 readiness probe 실패를 일으켰고, 이로 인해 클러스터에서 quorum 연결이 끊어져 여러 EC set에서 read/write quorum 오류가 발생했다.</t>
+          <t>Pod 0-47이 직접 엔드포인트로 사용되어 과도한 요청이 들어와 goroutine이 급증하고 메모리 사용량이 급증하면서 readiness probe가 실패하고, 이로 인해 EC 세트 쿼럼이 손실되는 현상이 발생했다. Pod가 일시적으로 비활성화되면서 모든 EC 세트의 쓰기 허용량이 최소값으로 떨어졌고, 이로 인해 여러 EC 세트에서 쿼럼 오류가 동시에 보고되었다.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>직접 pod에 접근하는 대신 LoadBalancer 서비스 엔드포인트를 사용하도록 전환하고, 트래픽 부하를 모니터링하며 필요 시 스케일링하거나 요청을 분산시켜 goroutine 스파이크와 메모리 증가를 방지한다.</t>
+          <t>Pod 0-47에 대한 직접 접근을 중단하고 LoadBalancer 엔드포인트를 사용하도록 전환하여 goroutine 스파이크와 메모리 급증을 방지한다. 추가적으로 Prometheus 접근 방식을 NodePort에서 Service로 변경하고, 트래픽 부스트 시나리오를 모니터링하며, 클라이언트가 느리게 읽는 경우를 추적한다.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>지속적으로 30 EC set 오류가 반복되는 경우는 비정상적이며, 클러스터 모니터링 도구를 활용해 트래픽 패턴과 노드 상태를 상세히 분석할 필요가 있다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2022,20 +2154,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>사용자가 IAM 캐시 갱신 로그가 클러스터 성능에 영향을 주는지 확인하고, 개선 방안이 있는지 문의했습니다. 또한, 해당 처리 중 읽기/쓰기 접근에 영향을 받지 않는지 여부를 물었습니다.</t>
+          <t>고객이 IAM 캐시 갱신 로그가 성능에 영향을 미치는지, 그리고 기존 데이터 접근(read/write)이 영향을 받는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>로그에 따르면, 오래된 IAM 데이터가 감지되어 캐시가 새로 빌드되었고, 서비스 계정 4786개와 정책 매핑 3741개를 로드하는 데 각각 14.82초와 9.85초가 걸려 전체 갱신이 35.85초가 소요되었습니다.</t>
+          <t>서비스 계정과 정책 매핑 수가 많아 IAM 캐시 갱신에 35.85초가 걸려, 그 동안은 이전 캐시를 사용해 접근 제어가 수행됩니다.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>시스템은 35.85초 동안 이전 캐시를 기반으로 접근 제어를 수행하므로 현재 읽기/쓰기 작업에 큰 영향이 없으며, 서비스 계정과 정책 매핑을 정리하거나 통합해 로드 시간을 단축하도록 권고합니다.</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>사용하지 않는 서비스 계정과 정책 매핑을 정리하거나 통합해 갱신 시간을 단축하고, IAM 변경이 있을 때는 갱신이 완료될 때까지 반영되지 않으므로 주기적으로 검토하도록 권장합니다.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17030</t>
@@ -2068,21 +2204,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>고객은 AIStor warm tier에 ILM을 적용할 때 버전 관리가 필요한지, 기존 데이터를 한 번에 warm tier로 이동하는 최선 방법은 무엇인지, 초기 마이그레이션 시 스캐너를 튜닝할 필요가 있는지 문의했습니다.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>고객은 ILM을 사용해 hot tier에서 warm tier로 데이터를 이동하려고 합니다. 버전 관리 필요 여부, 초기 마이그레이션 방법, 스캐너 성능 조정 여부를 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>고객은 hot tier에서 warm tier로 데이터를 이동하고, 특정 버킷 프리픽스에만 ILM을 적용하려는 계획을 가지고 있습니다. 따라서 ILM 설정과 초기 마이그레이션 방법에 대한 정보를 필요로 합니다.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>버전 관리는 필수는 아니며, ILM 규칙에 prefix 필터와 transition 조건을 설정하면 기존 객체를 한 번에 warm tier로 이동할 수 있습니다. 스캐너를 fastest 모드로 설정해도 되며, 필요에 따라 조정할 수 있습니다. ILM 규칙이 네임스페이스를 순회해 객체를 마크하고 다른 프로세스가 실제 전환을 수행합니다.</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>ILM tiering does not require bucket versioning; set ILM rules with prefix filter and transition condition. For initial migration, configure ILM rule to transition existing objects older than X days. Scanner can be set to fastest but monitor performance.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/17000</t>
@@ -2110,7 +2254,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kranthi</t>
+          <t>Jimmy Martin, Kranthi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2120,20 +2264,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>We would like to identify which objects were stored on the failed drive. Is there a supported way to list the objects that were located on a specific failed drive?</t>
+          <t>사용자는 클러스터에서 드라이브가 고장났을 때, 해당 드라이브에 저장된 객체를 식별하고 싶어합니다. 또한 특정 고장난 드라이브에 저장된 객체를 나열할 수 있는 지원되는 방법이 있는지 묻습니다.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>One disk is currently offline due to a physical issue.</t>
+          <t>고장난 드라이브는 물리적 문제로 인해 오프라인 상태이며, 이는 클러스터의 EC 세트에서 하나의 드라이브가 실패한 상황입니다.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>When you replace the drive, MinIO will automatically initiate healing and rebuild the data on the new drive using data from other drives in the erasure-coded set.</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>MinIO는 고장난 드라이브에 대한 객체 목록을 직접 제공하지 않으며, 대신 드라이브를 교체하고 자동 복구(Healing)를 수행하도록 권장합니다. mc ls 명령으로 객체를 확인할 수 있지만, 파트 정보는 알 수 없으므로 전체 복구를 신뢰하는 것이 가장 안전합니다.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Rack awareness 설정으로 같은 EC 세트에서 4개 이상의 드라이브가 동시에 실패할 가능성은 낮습니다.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16958</t>
@@ -2166,27 +2314,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>고객이 단일 드라이브가 실패한 후 minio_cluster_health_capacity_usable_total_bytes가 모든 서버에서 증가한 원인을 묻고 있다.</t>
+          <t>고객이 단일 드라이브 실패 후 minio_cluster_health_capacity_usable_total_bytes가 모든 서버에서 증가한 이유를 이해하고 싶어합니다.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>드라이브가 degraded 상태에서 I/O 오류로 용량이 감소하고, 실패 후 오프라인 처리되면서 MinIO가 다음 최소 용량 드라이브를 사용해 클러스터 용량을 재계산해 증가했다.</t>
+          <t>드라이브가 장애 상태에서 I/O 오류를 반환하면서 해당 드라이브의 용량이 감소하고, 클러스터가 오프라인으로 표시되면서 최소 공간 기준이 다음 가장 낮은 드라이브로 전환되어 전체 사용 가능한 용량이 증가합니다.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>드라이브를 교체하고 노드를 드레인한 뒤 정상 용량이 복구되었으며, 단일 드라이브 교체 시에는 노드 드레인 없이 Direct PV 문서에 따라 교체하면 된다.</t>
+          <t>단일 드라이브 실패 시 해당 드라이브만 교체하고, 필요 시 노드 드레인 없이 교체를 진행하며, mc admin info --json으로 상태를 확인하고, 클러스터가 정상 상태가 되면 메트릭이 정상으로 돌아옵니다.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>인프라팀이 노드 종료를 요구했고, 온라인 교체가 선호된다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2216,7 +2364,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kaan Kabalak</t>
+          <t>Kaan Kabalak, Raul-Mircea Crivineanu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2226,20 +2374,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>고객이 mc inventory를 매일 실행하지만 특정 시각을 지정할 수 없어서 9시와 10시 사이에만 실행되는 상황에 대해 정확한 시작 시간을 맞출 수 있는 방법이 있는지 문의했습니다.</t>
+          <t>고객은 mc inventory 실행 시 정확한 시작 시간을 지정할 수 있는 방법이 있는지 문의했습니다. 또한 mc inventory에 커스텀 시작 시간을 지원하도록 향후 기능이 추가될 계획이 있는지 물었습니다.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>mc inventory의 스케줄링 옵션은 daily만 지원하고, 커스텀 시작 시간을 지정하는 옵션이 없기 때문에 원하는 시각에 실행되지 못합니다.</t>
+          <t>mc inventory의 스케줄링 옵션이 'daily'만 지원하고, 커스텀 시작 시간을 지정할 수 없기 때문에 실행 시간이 9~10시 사이로 제한됩니다.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>크론 작업을 사용해 schedule: once 옵션과 함께 원하는 시각에 mc inventory를 실행하도록 설정하거나, 향후 Edge 릴리스에서 제공될 예정인 커스텀 시작 시간 기능을 기다리도록 안내했습니다.</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>현재는 cronjob을 사용해 원하는 시점에 mc inventory를 실행하거나, Edge 릴리스에서 제공되는 별도 스냅샷 기능을 활용할 수 있습니다. 향후 Edge 릴리스에 커스텀 시작 시간을 지원하는 기능이 추가될 예정입니다.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16908</t>
@@ -2265,20 +2417,36 @@
           <t>RIA CHOI04:23 PM</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ali Yaldaz</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>RIA CHOI는 4월 9일 오전 9시부터 10시까지 마이그레이션 기간 동안 엔지니어링 스탠바이 지원을 요청했습니다.</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>오퍼레이터가 'policybindings.min.io' 리소스를 찾지 못해 정책 바인딩을 생성하거나 업데이트할 수 없다는 오류가 발생했습니다.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>MinIO Operator가 policybindings.min.io CRD를 찾지 못해 리소스 생성 및 업데이트가 실패했습니다.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16752</t>
@@ -2311,23 +2479,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>애플리케이션(Application)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>고객이 시스템에서 "context canceled" 오류가 intermittent하게 발생하며, 이 오류가 언제 트리거되는지와 실제 애플리케이션에 미치는 영향을 확인하고 싶어 합니다.</t>
+          <t>사용자가 GetObjectInfo에서 context canceled 오류가 언제 발생하고, 실제 애플리케이션에 어떤 영향이 있는지 확인해 달라고 요청했습니다.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>오류는 GetObjectInfo 호출 시 내부 메타 캐시 walk 과정 중에 클라이언트가 연결을 끊거나 타임아웃이 발생해 컨텍스트가 취소되면서 발생합니다. 업그레이드 이후 로깅 개선으로 오류가 더 빈번히 보이기도 합니다.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Kranthi가 설명한 바와 같이, 클라이언트가 캐시에서 연결을 끊으면 Context cancelations이 발생합니다.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>오류는 업그레이드 이후에만 관찰되며, 고부하 상황에서 특히 빈번히 발생합니다. 문제는 클라이언트 연결 관리와 캐시 동기화에 관련되어 있습니다.</t>
+          <t>오류는 버전 2025.10에서 2026.02로 업그레이드한 이후에 발생하기 시작했습니다.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2367,20 +2539,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>고객이 재시작 버튼을 클릭하면 서비스에 끊김이나 연결 중단이 발생하는지 여부와, 5초 간단단한 중단이 예상되는지 확인하고 싶어 합니다. 재시작이 전체 서비스 중단이 아닌 롤링 재시작인지 궁금합니다.</t>
+          <t>사용자가 Restart 버튼을 클릭했을 때 서비스에 다운타임이나 연결 중단이 발생하는지 확인해 달라고 요청했습니다. 또한 테스트 결과 10개의 노드만 재시작되고 5초 간단한 중단이 있었는데, 이 동작이 예상되는 것인지 물었습니다.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>롤링 재시작 시 노드가 한 번에 일부만 재시작되며, 인그레스/로드 밸런서가 재시작 노드를 즉시 감지하지 못해 잠시 트래픽이 중단됩니다. MinIO 자체는 가용성을 유지하며, 나머지 노드가 계속 서비스를 제공합니다.</t>
+          <t>MinIO는 롤링 재시작을 수행하며 일부 노드만 재시작됩니다. Ingress/LoadBalancer가 재시작 중인 노드를 즉시 감지하지 못해 5초 간단한 중단이 발생했습니다. 보안상의 이유로 핫 리로드가 불가능합니다.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>인그레스 헬스 체크 간격과 준비 프로브를 짧게 조정하고, 로드 밸런서의 활성 헬스 체크를 1~2초로 설정해 재시작 노드를 빠르게 감지하도록 하세요. 트래픽이 적은 시간에 재시작을 수행하면 사용자에게 영향을 최소화할 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>로드 밸런서와 Ingress의 헬스 체크를 짧은 간격으로 설정하고, 활성 헬스 체크를 활성화하여 재시작 노드를 빠르게 감지하도록 합니다. 또한 트래픽이 적은 시간에 재시작을 수행합니다.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16679</t>
@@ -2418,22 +2594,22 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>사용자는 MinIO AIStor 서버에서 TLS 없이 HTTP만으로 SFTP(및 FTP) 접근을 활성화하고, SFTP 비공개 키를 어떻게 제공할 수 있는지 문의했습니다.</t>
+          <t>The user requests guidance on enabling SFTP access on their AIStor server, which currently operates over HTTP without TLS. They also ask whether SFTP and FTP services can be added without changing the HTTP endpoint, and how to supply the private key for SFTP.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SFTP를 활성화했으나 TLS가 구성되지 않아 operator가 TLS 개인 키를 SSH 호스트 키로 사용하도록 설계되어 /tmp/minio/certs/private.key 파일이 없기 때문에 시작에 실패했습니다.</t>
+          <t>The SFTP server fails to start because the TLS private key is missing; the operator uses the TLS private key as the SSH host key. Since TLS is not configured on the server, the required private key file is not present, causing the error.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TLS를 먼저 구성하고(디폴트 자동 생성이 사용 가능) objectStore.sftp.enabled를 true로 설정해 Helm 업그레이드를 수행하면 operator가 TLS 개인 키를 SSH 호스트 키로 자동 사용합니다. 커스텀 인증서가 필요하면 certificates.disableAutoCert를 false로 두고 sftp.domainName을 인증서 도메인에 맞추면 됩니다.</t>
+          <t>Configure TLS on the AIStor server; the operator will automatically generate TLS certificates and use the private key as the SSH host key for SFTP. In the values.yaml, set objectStore.certificates.disableAutoCert to false (default) and enable objectStore.sftp.enabled. If using custom certificates, set objectStore.sftp.domainName to match one of the certificate domains; note that FTPS requires TLS, while plain FTP works but is not recommended.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>고객은 현재 TLS를 구성할 수 없으므로 SFTP 사용을 보류하기로 결정했습니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2463,30 +2639,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Matthieu ROLLA</t>
+          <t>Matthieu ROLLA,Jeeva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>고객은 mc license update 명령 실행 후 내부 MinIO 서버에 라이선스가 적용되었는지 확인하고, 서비스 중단 여부를 묻습니다. 또한 전체 라이선스 업데이트 절차(Helm 업그레이드와 mc license update)를 문의하며, 에어갭 환경에서 나타나는 재신청 오류 로그가 계속 뜨는 이유와 이를 비활성화할 수 있는 방법을 요청합니다.</t>
+          <t>The user updated the license via mc license update but noticed the operator secret remained unchanged and wonders if it will auto‑update after 24 hours. They also want to verify the license was applied to the internal MinIO server, know whether mc license update causes downtime, and understand the recommended procedure for a full license update. Additionally, in an air‑gapped environment, they encounter continuous renewal errors and ask why and how to disable them.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>mc license update는 MinIO 서버 내부 설정만 갱신하며, Operator가 사용하는 Kubernetes secret은 별도로 갱신되지 않습니다. 에어갭 환경에서는 SUBNET 포털에 접속하지 못해 정기 재신청 스케줄러가 인증서 오류를 발생시켜 로그를 남깁니다.</t>
+          <t>The operator secret is a separate Kubernetes secret that is not updated by mc license update, so it remains with the old license value. The renewal errors occur because the cluster attempts to contact the SUBNET portal for license renewal, but in an air‑gapped environment the TLS certificate cannot be verified, leading to repeated error logs. The renewal scheduler runs daily and cannot be disabled in the current release.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>내부 서버에 라이선스가 적용되었는지 확인하려면 mc license info ALIAS를 실행하고, mc license update는 서비스 재시작 없이 즉시 적용됩니다. 전체 라이선스 업데이트 절차는 Helm 차트에서 license 값을 먼저 업데이트한 뒤 mc license update를 실행하는 것이 권장됩니다. 에어갭 환경에서 발생하는 재신청 오류는 SUBNET 포털 접속이 불가능해 발생하며 현재는 스케줄러를 비활성화할 방법이 없으므로 무시해도 됩니다.</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>To fully update the license, first update the Kubernetes secret using Helm (helm upgrade --set license=NEW_LICENSE_KEY) so new pods receive the license, then run mc license update to apply it to the running server without downtime. Verify the update by running mc license info, which reads the internal config; if the license appears, it has been applied. In an air‑gapped environment, the renewal errors are expected and can be safely ignored; there is currently no way to disable the renewal scheduler.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Renewal scheduler disabling will be available in the next release.</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16667</t>
@@ -2524,20 +2704,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Y Kim이 ObjectStore operator pod의 복제본 수가 1개 이상이어야 고가용성을 보장하는지 여부를 확인하도록 요청했습니다.</t>
+          <t>고객이 ObjectStore operator pod의 복제본을 1개 이상 유지해야 고가용성을 보장할 수 있는지 확인해 달라고 요청했습니다.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Operator는 하나의 리더 pod만 활성화되고, 리더가 아닌 다른 pod는 대기 상태이며, 복수의 리더가 동시에 동작하면 동시성 문제가 발생합니다. 리더는 Lease를 사용해 상태를 관리하며, 리더가 만료되면 다른 pod가 자동으로 리더가 됩니다.</t>
+          <t>AIStor operator는 리더 선출 방식을 사용하며, 복수의 operator pod가 동시에 활성화되면 동시성 문제가 발생합니다. 따라서 하나의 리더 pod만이 리소스를 모니터링하고, 나머지 pod는 대기 상태에 있습니다. 리더가 lease를 갱신하지 않으면 다른 pod가 리더가 되어 운영을 이어갑니다.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>리더-팔로워 구조 덕분에 replica 수를 1로 두어도 고가용성이 확보됩니다. pod가 중단되면 Lease 갱신이 중단되고 다른 pod가 즉시 리더가 되어 서비스를 계속 유지합니다.</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>복제본 수를 1로 유지해도 충분합니다. operator는 가벼운 리소스이며, 비활성화되더라도 object-store는 계속 동작합니다. 리더가 실패하면 다른 pod가 자동으로 리더가 되어 서비스 중단 없이 이어집니다.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16631</t>
@@ -2565,30 +2749,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ali Yaldaz</t>
+          <t>Ramon de Klein, Ali Yaldaz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>고객은 MinIO 설정 파일을 검토해 주시고, minio-global 서비스의 목적과 포트 번호를 알려달라고 요청했으며, Helm 1.0.13 버전에서 .objectStore.configuration를 지정해야 하는지와 headless 및 NodePort 구성을 제외한 최종 values.yaml을 제공해 달라고 요구했습니다.</t>
+          <t>고객은 MinIO에서 AIStor로 마이그레이션하기 전에 MinIO 설정 파일을 검토하고 피드백을 요청했습니다. 또한 minio-global 서비스와 NodePort/Ingress 설정에 대한 설명을 요청했습니다.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>고객은 서비스 노출 방식(NodePort vs. Ingress)과 minio-global 서비스가 존재하는지 여부, 오래된 Helm 차트에서 필요한 기본 설정 필드에 대해 혼란을 겪고 있습니다.</t>
+          <t>사용자는 Helm 차트 버전과 설정 항목에 대한 혼동이 있어 올바른 구성을 확인하고 싶어했습니다. minio-global 서비스가 존재하지 않아 해당 설정이 필요 없다는 점을 명확히 하고 싶어했습니다.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Helm 1.0.13에서는 .objectStore.configuration를 지정해야 하며, minio-global 서비스는 생성되지 않으므로 무시해도 됩니다. 제공된 값 중 headless 및 NodePort 항목을 제외하고 최종 values.yaml을 제공하면 됩니다.</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>Ramon de Klein은 .objectStore.pools[].volumeSize를 .objectStore.pools[].size로 변경하고, 보안 컨텍스트 필드를 생략하도록 권고했습니다. Ali Yaldaz는 Helm 차트 1.0.13에서는 .objectStore.configuration를 지정해야 하며, minio와 wxminio-console은 NodePort, headless는 ClusterIP, Ingress는 minio와 console에만 적용하도록 설정했습니다.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>테스트 환경에서 이미 검증을 완료했습니다.,</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16630</t>
@@ -2616,32 +2804,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>Jeeva, Kranthi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>고객은 두 번째 풀에서 기존 풀과 다른 EC 설정을 사용하고 싶어합니다. 현재 Kubernetes 환경에서 이를 지원하는지 여부를 확인하고자 합니다. 새로운 릴리스가 나올 때까지 해당 구성을 진행하지 않을 예정입니다.</t>
+          <t>사용자는 Kubernetes 환경에서 pool-1이 pool-0과 다른 EC 설정(예: EC=10:4)을 사용할 수 있는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kubernetes ObjectStore CR은 현재 각 풀마다 다른 EC 설정을 지원하지 않습니다. 이 기능은 baremetal에서만 지원됩니다. 따라서 현재 환경에서는 해당 설정이 불가능합니다.</t>
+          <t>Kubernetes 환경에서는 현재 서로 다른 EC 설정을 지원하지 않으며, 이 기능은 baremetal에서만 가능하다고 알려졌습니다.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>팀은 Kubernetes에서 per-pool EC 설정을 지원하도록 작업 중입니다. 진행 상황을 계속 업데이트할 예정입니다. 사용자는 릴리스가 나오면 해당 기능을 활용할 수 있습니다.</t>
+          <t>이 기능은 개발 중이며, 향후 릴리스에서 지원될 예정이므로 사용자는 해당 릴리스를 기다려야 합니다.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>개발 진행이 다른 의존성 문제로 지연되고 있음.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,7 +2859,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ramon de Klein</t>
+          <t>Ramon de Klein, Bala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2681,20 +2869,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>고객은 풀 1을 추가할 때 10분 정도의 다운타임이 발생했는지 확인하고 싶어 합니다. 또한 DNS 해석 오류와 PV 바인딩 속도가 느린 점이 문제인지 묻고 있습니다. 이러한 현상이 예상되는지 여부와 개선 방법을 안내받으려 합니다.</t>
+          <t>사용자는 새 풀을 추가할 때 약 10분간의 다운타임이 발생한 것이 예상되는지, 그리고 그 원인에 대한 이해가 맞는지 확인하고, 1,000개 이상의 PV를 프로비저닝할 때 다운타임을 방지하거나 최소화할 수 있는 방법(튜닝 옵션 등)을 요청했습니다.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>AIStor는 새로운 풀을 위해 상태집합을 생성하면서 재시작되며, 이 과정에서 기존 풀의 서비스가 중단됩니다. 동시에 다수의 PV 바인딩 요청이 클라이언트 사이드 스로틀링으로 지연되어 DNS가 느리게 반응합니다. 결과적으로 새로운 풀의 Pods가 완전히 준비되기 전에 기존 풀이 재시작되어 다운타임이 발생합니다.</t>
+          <t>다운타임은 AIStor가 새 풀을 완전히 준비하기 전에 기존 풀을 재시작하면서 발생했고, PV 프로비저닝 속도가 클라이언트 측 스로틀링으로 인해 느려서 전체 프로비저닝 시간이 길어졌습니다.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AIStor 재시작을 새 풀의 모든 Pods가 실행될 때까지 지연하도록 수정하고, DirectPV의 QPS/Burst를 조정해 클러스터 API 서버의 스로틀링을 완화합니다. PVC 사전 생성 및 이미지 사전 다운로드를 통해 Pod 생성 속도를 높이고, API 서버의 APF 설정을 검토해 최적화합니다. 이러한 조치를 통해 다운타임을 최소화하고 PV 바인딩 성능을 개선할 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>AIStor 재시작을 새 풀이 완전히 준비된 후로 연기하고, DirectPV의 클라이언트 측 QPS/Burst 설정을 조정하거나 DirectPV v5.1.1에서 제공하는 커스텀 QPS/Burst 옵션을 사용해 PV 프로비저닝 속도를 개선하며, API 서버의 Priority &amp; Fairness 설정을 검토해 스로틀링을 완화합니다.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16608</t>
@@ -2722,7 +2914,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim</t>
+          <t>Daniel, Youngkyoo Kim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2732,20 +2924,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>요청자는 DirectPV Helm 업그레이드 시 kubectl directpv uninstall 명령을 건너뛸 수 있는지 확인하고, 전체 업그레이드 절차를 검증해 주시길 요청했습니다.</t>
+          <t>Youngkyoo Kim 요청은 업그레이드 절차와 백업 단계, 그리고 누락된 policybinding CRD에 대한 확인 및 공유를 요청했다.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>kubectl directpv uninstall이 직접 PV namespace를 삭제해 Helm 설치 시 namespace가 아직 종료 중이라 오류가 발생하고, CRD가 기존 필드 매니저 kubectl-directpv-oss를 소유해 Helm의 서버사이드 적용과 충돌합니다.</t>
+          <t>업그레이드 지침이 CRD 소유권, 네임스페이스 삭제 타이밍, 볼륨 크기 매칭, 시크릿 보존 등 필수 단계를 누락해 충돌과 실패를 초래했다.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CRD를 Helm 소유자로 주석/라벨링하고 force-apply를 사용하거나 --skip-crds 옵션을 적용하며, namespace가 완전히 삭제될 때까지 대기 루프를 넣습니다. 기존 secret을 백업·재생성하거나 existingSecret을 false로 설정하고, volumeSize를 size로 교체합니다. 필요 시 운영자 배포를 재시작해 바로 재조정합니다.</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>CRD를 Helm 소유권으로 라벨링·주석 처리하고, --server-side --field-manager=helm --force-conflicts 옵션으로 강제 적용하며, 네임스페이스 삭제 후 대기 루프를 삽입한다. DirectPV 드라이브·볼륨 백업, volumeSize를 size로 교체, 시크릿 백업·재생성, 운영자 재시작, 올바른 이미지 태그 사용, policybinding CRD 설치를 수행한다.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>policybinding CRD가 클러스터에 존재하지 않아 확인이 필요하다.</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16590</t>
@@ -2783,22 +2979,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>고객은 DirectPV 4.1.4에서 5.1.0으로 업그레이드할 때 CRDs이 Terminating 상태에 걸려 있는 상황을 안전하게 복구하고, 올바른 업그레이드 절차를 요청했습니다.</t>
+          <t>The user requests guidance on how to recover from CRDs stuck in Terminating state after an unintended Helm uninstall, and also asks for the correct upgrade procedure from DirectPV 4.1.4 to 5.1.0. They also want confirmation of the recommended steps and whether rollback is possible.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>helm uninstall 시 DirectPV CRDs가 삭제되고, 최종자(finalizer)를 가진 CRDs가 Terminating 상태로 남아 삭제되지 않아 발생했습니다.</t>
+          <t>The Helm uninstall removed the CRDs and set deletionTimestamp on DirectPVVolume and DirectPVDrive resources, leaving them in Terminating state due to finalizers. The namespace was not properly created, causing Helm install failures and subsequent uninstall.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CRDs의 deletionTimestamp를 제거하고 최종자를 삭제한 뒤 DirectPV operator를 helm으로 재설치하고, 백업해 둔 CRs(drive, volume, node)를 복원해 재시동합니다. 업그레이드 시 kubectl directpv uninstall 후 helm repo add minio, helm repo update, helm install directpv minio/directpv 를 사용하며, -n directpv와 같은 namespace 옵션을 사용하지 않습니다.</t>
+          <t>Back up all DirectPV custom resources, remove deletion timestamps and finalizers from the CRDs, then reinstall the DirectPV operator with Helm (helm install directpv minio/directpv) and reapply the backed-up CRs. For upgrading from 4.1.4 to 5.1.0, run kubectl directpv uninstall, add the MinIO Helm repo, update it, and install the chart without specifying a namespace. Avoid using helm uninstall during production to prevent CRD deletion.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>helm 설치 시 -n directpv와 --create-namespace 옵션을 사용하지 않아야 합니다.</t>
+          <t xml:space="preserve">Rollback to v4.1.4 is possible per Appendix A of the documentation.  </t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2828,7 +3024,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ramon de Klein</t>
+          <t>Ramon de Klein, Zach Burnham, Jiuker, Matthieu ROLLA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2838,22 +3034,22 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>사용자는 AIStor Operator 업그레이드가 무중단인지 확인하고 싶다. 또한 서지 전략(maxSurge) 사용 여부와 Graceful Shutdown 보장 여부를 묻는다. 멀티파트 업로드와 복제 작업 처리, MinIO Operator 코드 참조 가능성에 대한 질문도 포함했다.</t>
+          <t>The user wants to confirm whether AIStor Operator upgrades guarantee zero-downtime, details of the rolling restart process, surge strategy, graceful shutdown, handling of multipart uploads and replication, and whether MinIO Operator code can be used as reference. They also ask about removing the MinIO Operator after migration, image pull mechanism during fresh install, and ways to reduce image pull time in an air-gapped environment.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>업그레이드 중 모든 파드가 새 바이너리를 다운로드한 뒤 동시에 서비스를 재시작하면 기존 연결이 끊길 수 있다. 이후 롤링 재시작 시에도 파드 종료 시 연결이 끊길 가능성이 있다. 부적절한 시점에 재시작되면 오래된 이미지 사용으로 복구되지 않을 수 있다.</t>
+          <t>During upgrade, AIStor downloads the new binary to all pods, then restarts services simultaneously, causing a brief downtime; subsequent rolling restart may drop connections; errors can occur if pods restart at the wrong time or use an old image.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>최신 AIStor Operator는 Kubernetes 롤링 업데이트를 사용해 다운타임을 초 단위로 줄인다. 파드는 한 번에 한 개씩 재시작되며, maxUnavailable나 terminationGracePeriodSeconds를 조정할 수 없다. 클라이언트는 재시도 메커니즘을 구현해야 한다.</t>
+          <t>Use the newer AIStor Operator that supports a Kubernetes-friendly rolling upgrade; clients should implement retry logic for intermittent connections; to remove the MinIO Operator, uninstall it via Helm; image pulls are handled by kubelet and can be accelerated by caching images locally or using a private registry.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>업그레이드는 2026년 3월 말에 진행될 예정이며, 개발 환경에서 테스트가 진행 중이다.</t>
+          <t>Upgrade may cause a brief &lt;1 second downtime when services restart simultaneously; clients should implement retry; replication is not affected by the upgrade.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2883,32 +3079,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Daniel, Felvine Sakwe</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>사용자가 pod이 재시작 시 MinIO OpenID 초기화 오류가 발생해 pod이 실행되지 않으므로, 이 검사를 건너뛰거나 임시로 우회해 pod을 실행할 방법을 문의했습니다.</t>
+          <t>사용자는 pod가 오류로 실행되지 않도록 OpenID 검증을 건너뛰거나 일시적으로 우회하고, Kubernetes 환경에서 업그레이드 전에 스냅샷을 찍는 방법을 알고 싶어합니다.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>이 오류는 MinIO 버전을 다운그레이드했을 때 새로운 버전에서 추가된 인증 설정 키가 이전 버전에서 인식되지 않기 때문에 발생한 것입니다.</t>
+          <t>MinIO를 다운그레이드하면서 새로 추가된 설정 키가 이전 버전에서 인식되지 않아, pod가 시작 시 OpenID 검증에서 실패했습니다.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MinIO를 최신 버전으로 다시 업그레이드하면 pod이 정상 실행됩니다. 또는 'mc admin config reset identity_openid' 명령으로 해당 서브시스템의 키를 제거하거나, MINIO_IDENTITY_OPENID_ENABLE=off 환경 변수를 설정해 OpenID 검사를 비활성화할 수 있습니다.</t>
+          <t>mc admin config reset 명령으로 사용하지 않는 서브시스템(예: identity_openid)의 키를 삭제하거나, MINIO_IDENTITY_OPENID_ENABLE=off 환경 변수를 설정해 OpenID 검증을 비활성화하면 pod가 정상 실행됩니다.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>현재 AIStor Operator와 ObjectStore를 다운그레이드했으나, 업그레이드 시에는 kubernetes 설정과 manifest을 git에 저장해 두는 것이 권장됩니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2943,27 +3139,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>스토리지(Storage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>고객은 AIStor 업그레이드 계획을 검토하고, 필요 시 추가 조정 및 전체적인 위험 여부를 확인해 달라고 요청했다. 또한 롤백 시나리오와 잠재적 위험 수준을 사전에 파악하고 싶어했다.</t>
+          <t>고객은 AIStor 업그레이드 계획을 검토해 주시고, 추가 또는 수정이 필요한 부분이 있는지 확인해 달라고 요청했습니다. 또한, 롤백이 필요할 경우의 위험 수준과 대응 방안을 사전에 파악하고 싶다고 문의했습니다.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>업그레이드 과정에서 private Nexus 인증서 문제로 StatefulSet이 삭제될 수 있고, 최신 Operator 릴리스에서 외부 토큰 검증에 영향을 미치는 알려진 이슈가 있어 내부 메타데이터가 변경될 위험이 있다.</t>
+          <t>고객은 AIStor 업그레이드 시 발생할 수 있는 문제와 롤백 위험을 사전에 파악하고자 합니다. 현재는 개발 환경에서 업그레이드를 완료했으나, 프로덕션 환경에서는 추가 검증이 필요합니다.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Pedro Juarez가 private registry에서 Helm 업그레이드를 수행하는 가이드를 제공했고, Ramon de Klein은 IDP 검증 결과가 정상이면 업그레이드가 안전하다고 안내했다. Ali Yaldaz는 IDP 토큰 검증 절차를 제시했고, Deepak Thimmaiah는 롤백 시 메타데이터 문제를 언급했다.</t>
+          <t>지원팀은 업그레이드 계획이 적절하다고 확인하고, Helm upgrade 가이드와 사설 레지스트리 설정을 안내했습니다. 롤백은 지원팀과 함께 진행해야 하며, 메타데이터 변경으로 인한 위험이 있으므로 사전 검증이 필요합니다. 또한, IDP 토큰 검증과 외부 토큰 검증 이슈를 확인하도록 조언했습니다.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>외부 토큰 검증에 대한 알려진 이슈가 존재하며, 롤백은 완전히 지원되지 않지만 MinIO 지원팀과 협업하면 가능할 수 있다.</t>
+          <t>프로덕션 업그레이드 시 사설 Nexus 인증서로 인해 StatefulSet 삭제가 필요할 수 있음.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2993,30 +3189,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jiuker</t>
+          <t>Jiuker, Raul-Mircea Crivineanu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>스토리지(Storage)</t>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>사용자가 감사 로그를 Kafka를 통해 AIStor 버킷에 저장하고자 하며, 무한 루프 가능성에 대해 특정 버킷을 감사 대상에서 제외할 수 있는지, 아키텍처와 운영에 대한 최선의 실천 방안을 문의했습니다. 또한, Kafka 역할, AIStor에 데이터 저장 방법, 그리고 루프 조건과 같은 세부 사항을 요청했습니다. 최종적으로 기능이 언제 릴리즈될지에 대한 정보를 원했습니다.</t>
+          <t>사용자는 특정 버킷을 감사 로그에서 제외할 수 있는지와 Kafka, OpenSearch, AIStor를 이용한 아키텍처에 대한 최선의 실천 방안을 문의했습니다.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>OpenSearch에 1TB 이상의 로그를 저장하면서 로드가 높아져서 Kafka를 도입해 성능을 개선하고자 하는 상황이 원인입니다.</t>
+          <t>현재 1TB/일 이상의 감사 로그를 OpenSearch에 웹훅과 Fluent Bit으로 저장하고 있어 부하가 크고 로그 손실 위험이 있어 Kafka를 도입해 AIStor에 직접 저장하려는 상황입니다.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Jiuker는 Kafka를 통해 수집한 로그를 OpenSearch에 먼저 저장한 뒤, OpenSearch를 MinIO(AiStor)로 스냅샷 백업하도록 제안했습니다. 또한, 버킷별 필터링 기능을 통해 무한 루프를 방지하도록 설계하고, AIStor를 백업용으로만 사용하도록 권고했습니다.</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>감사 로그를 버킷 수준에서 필터링하고, Kafka에서 OpenSearch로 전송한 뒤 OpenSearch가 MinIO(=AIStor)로 스냅샷/백업을 저장하도록 구성합니다.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16429</t>
@@ -3049,21 +3249,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>고객이 인프라를 이전 스택에서 최신 이미지로 업데이트할 때 DirectPV 플러그인을 업그레이드해야 하는지 문의했습니다.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>고객이 인프라를 최신 이미지로 업데이트할 때 DirectPV 플러그인을 업그레이드해야 하는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Felvine Sakwe는 v5.1.0 버전으로 업그레이드할 것을 권고하고, 소규모 환경에서 먼저 테스트한 뒤 진행하라고 조언했습니다. 또한 Praveen은 서버와 플러그인 버전을 동일하게 유지하고 최신 상태로 업데이트할 것을 권장했습니다. 따라서, 플러그인을 v5.1.0으로 업그레이드하고, 테스트 환경에서 검증한 뒤 운영 환경에 적용하는 것이 가장 적절합니다.</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>플러그인을 v5.1.0으로 업그레이드하고, 서버 버전과 일치하도록 유지하며, 먼저 낮은 환경에서 테스트한 뒤 프로덕션에 적용합니다.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16387</t>
@@ -3101,20 +3309,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>고객이 Delta Sharing을 AIStore 테이블에 적용하려 할 때 "Unable to update share: json: cannot unmarshal array" 오류가 발생한다고 문의했다.</t>
+          <t>사용자가 Delta 공유를 업데이트할 때 오류가 발생하고, 명령어 구문이 변경되었는지 여부를 문의했습니다.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>서버가 테이블 namespace를 배열 형식으로 반환하지만, mc 클라이언트는 문자열을 기대하여 JSON 파싱에 실패했다.</t>
+          <t>서버가 테이블 네임스페이스를 문자열 대신 배열로 변경했으나, 클라이언트는 여전히 문자열을 기대해 JSON 파싱 오류가 발생했습니다.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>mc 클라이언트를 최신 릴리스(2026-02-19)로 업그레이드하면 문제를 해결할 수 있다.</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+          <t>mc 클라이언트를 최신 버전(RELEASE.2026-02-19T10-32-25Z)으로 업데이트하면 문제를 해결할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16385</t>
@@ -3152,16 +3364,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim은 스프레드존 설정 시 동일 랙에 2개 이상의 포드가 같은 erasure set에 배치될 가능성을 확인하고 싶어한다.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>사용자는 현재 Spread Zone 설정에서 동일 랙에 있는 두 개 이상의 pod가 같은 erasure set에 배치될 수 있는지 여부를 확인하고 싶어합니다.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>각 랙에 노드 수가 고르지 않아, 랙에 노드가 하나뿐인 경우에 spread zone이 동일 랙에 pod를 중복 배치할 수 있다는 점이 문제의 원인입니다.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>노드 수를 각 랙마다 같은 개수로 배치(예: 9개 랙에 6개 서버, 또는 18개 랙에 3개 서버)하고 anti‑affinity를 사용해 스프레드존을 적용한다. spreadZoneConfig를 적절히 설정한다.</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>노드 수를 각 랙에 동일하게 배치(예: 9개 랙에 6개 노드씩 또는 18개 랙에 3개 노드씩)하거나, spreadZoneConfig를 조정해 anti‑affinity를 강화하여 같은 랙에 pod가 중복 배치되지 않도록 합니다.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>현재 54개의 노드를 29개의 랙에 불균등하게 배치하고 있어, spread zone이 랙에 하나의 노드만 있는 경우에 pod를 중복 배치할 가능성이 있습니다. 재배치를 통해 각 랙에 동일한 노드 수를 확보하면 문제를 방지할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16335</t>
@@ -3194,25 +3414,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>고객이 MinIO에서 AIStor로 마이그레이션하기 전에 클러스터가 준비되었는지, 설치 후 마이그레이션이 정상적으로 완료되었는지를 검증할 수 있는 공식 스크립트나 도구가 있는지 문의했습니다.</t>
+          <t>고객은 MinIO에서 AIStor로 마이그레이션 시 사전 및 사후 클러스터 상태 검증을 위한 공식 스크립트나 도구가 있는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>AIStor로의 마이그레이션은 기존 MinIO 업그레이드와 동일한 검증 절차를 따르기 때문에 별도의 공식 검증 도구가 필요 없다는 것입니다.</t>
+          <t>고객은 마이그레이션 전후에 클러스터가 정상적으로 동작하는지 확인하기 위해 검증 도구가 필요하다고 생각했습니다.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>따라서 기존 MinIO 업그레이드 시 사용하는 검증 절차와 도구를 그대로 적용하면 됩니다.</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+          <t>AIStor 업그레이드 시 별도의 검증 도구가 필요 없으며, 일반 MinIO 업그레이드와 동일한 검증 절차를 따릅니다.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16323</t>
@@ -3250,20 +3474,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>고객은 DirectPV Node Server에서 간헐적으로 발생하는 오류가 어떤 상황에서 나타나는지, 이는 알려진 이슈인지, 재시작 없이 방지하거나 완화할 수 있는 조치가 있는지에 대해 알고 싶어합니다.</t>
+          <t>RIA는 DirectPV Node Server에서 발생하는 간헐적 오류가 언제 발생하는지, 이 현상이 알려진 이슈인지 여부, 그리고 pod를 재시작하지 않고 방지하거나 완화할 수 있는 권장 조치를 알고 싶어합니다.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>이 오류는 Kubernetes 컨트롤러의 캐시와 etcd 간에 발생하는 레이스 컨디션으로 인해, 메모리 내 UID가 etcd에 존재하는 객체의 UID와 일치하지 않아 ‘Precondition failed’가 발생함으로써 발생합니다.</t>
+          <t>이 오류는 컨트롤러의 메모리 캐시와 etcd의 실제 상태가 일치하지 않아 UID 불일치가 발생하는 레이스 컨디션으로 인해 발생합니다.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Kubernetes 버전을 해당 upstream fix가 포함된 버전으로 업데이트하고, DirectPV를 최신 릴리스로 업그레이드하며, 필요 시 리스너리/레디니스 프로브를 설정해 포드가 stuck 상태일 때 자동 재시작하도록 구성합니다.</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>Kubernetes 버전이 업스트림 수정을 포함하고 있는지 확인하고 최신 DirectPV 릴리스를 사용하며, liveness/readiness 프로브를 설정해 pod가 stuck 상태에 들어가면 자동으로 재시작하도록 구성하고, 필요 시 k8s 버전을 업그레이드해 오류 빈도를 줄입니다.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16321</t>
@@ -3289,7 +3517,11 @@
           <t>Jihun Na04:57 PM</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Raul-Mircea Crivineanu</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>클러스터 및 운영(Cluster &amp; Operations)</t>
@@ -3297,12 +3529,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>고객이 특정 AIStor 노드에서 고루틴 수가 128K로 급증하고 다른 노드는 10K 이하로 유지되는 현상을 분석해 달라고 요청했습니다.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>고객은 AIStor 노드 중 하나에서 Goroutine Count가 128K로 급증한 현상을 보고하고, MinIO SUBNET에서 원인 분석을 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>이 티켓은 중복으로 삭제되었습니다.</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16281</t>
@@ -3340,20 +3584,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>고객이 goroutine 수 급증 현상을 보고하며, aistor-console을 v0.0.28 이상으로 업그레이드하기 위해 어떤 objectstore 이미지를 적용해야 하는지를 문의했다.</t>
+          <t>어떤 objectstore 이미지를 적용해야 aistor-console을 v0.0.28 이상으로 업그레이드할 수 있는지 알려달라는 요청</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>aistor-console v0.0.24 버전에서 폴더를 ZIP으로 다운로드할 때 채널을 닫지 않아 goroutine이 누수되는 버그가 존재하며, 이는 대규모 객체 다운로드 시 120K+ goroutine이 생기는 원인이 되었다.</t>
+          <t>aistor-console v0.0.24에서 폴더 다운로드 시 채널을 닫지 않아 goroutine이 누수되는 버그가 발생했다</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>문제가 발생한 노드에서 minio 프로세스를 재시작하고, aistor-console을 v0.0.28 이상으로 업그레이드한다. 이를 위해 AiStor 버전을 2025-12-20T04-58-37Z 이상으로 업데이트할 필요가 있다.</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>affected node에서 minio 프로세스를 재시작하고, aistor-console을 v0.0.28+로 업그레이드하며, objectstore 이미지를 AiStor Version 2025-12-20T04-58-37Z 이상으로 교체한다</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16280</t>
@@ -3391,20 +3639,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>고객이 DirectPV에서 Degraded 상태인 디스크를 교체하기 전 필요한 절차와 전용 스크립트 또는 자동화를 요청했습니다.</t>
+          <t>고객은 DirectPV에서 디스크가 Degraded 상태일 때 교체 전 필요한 절차와 스크립트 사용 여부를 문의했습니다. 또한 교체 후에 replace.sh 스크립트를 실행할 때 드라이브 ID를 사용해야 하는지와 교체 전 노드 코르닝, 파드 삭제, 파일 시스템 언마운트가 필요한지 확인했습니다.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>디스크가 Degraded 상태여서 교체가 필요합니다.</t>
+          <t>DirectPV에서 관리되는 디스크가 Degraded 상태가 되어 교체가 필요합니다.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>대체를 위해 먼저 kubectl directpv discover, kubectl directpv init drives.yaml --dangerous 를 실행한 뒤 replace.sh &lt;OLD-DRIVE-ID&gt; &lt;NEW-DRIVE-ID&gt; 스크립트를 실행합니다. 스크립트가 모든 필요한 절차(드라이브 코어닝, 파드 영향 최소화 등)를 수행하므로 노드 코어닝이나 파드 삭제, 파일시스템 마운트 해제는 사전 단계에서 필요 없습니다.</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>해결 방법은 replace.sh 스크립트를 사용해 물리적 디스크 교체 후 kubectl directpv discover, init, 그리고 replace.sh &lt;OLD-DRIVE-ID&gt; &lt;NEW-DRIVE-ID&gt;를 실행하는 것입니다. 스크립트가 필요한 모든 절차를 수행하며, DirectPV 드라이브를 코르닝해 새로운 볼륨 스케줄링을 방지합니다.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16176</t>
@@ -3437,25 +3689,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>고객은 MinIO가 20개의 드라이브 중 하나가 실패했을 때 19개의 드라이브로도 실행할 수 있는지 문의했습니다. 또한 DirectPVVolume CRD가 동일한 /dev/sdr를 두 개 참조하는 현상을 확인하고, 왜 발생하는지 원인을 요청했습니다.</t>
+          <t>사용자는 MinIO를 설정된 드라이브 수보다 적은 드라이브로 임시 실행할 수 있는지와 드라이브가 실패한 후 동일한 물리 디스크를 참조하는 DirectPVVolume 리소스가 여러 개 생성되는 이유를 묻고 있습니다.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>한 드라이브가 LOST 상태로 표시되어 MinIO가 시작되지 못했고, DirectPV는 남은 디스크의 가용 공간을 기준으로 볼륨을 자동 할당하기 때문에 동일한 드라이브에 두 개의 볼륨이 생성됩니다.</t>
+          <t>MinIO 서버 포드는 물리 디스크(/dev/sdr)가 LOST 상태이기 때문에 FSUUID를 찾지 못해 시작하지 못했습니다.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>고객은 'kubectl directpv suspend drives' 명령으로 손상된 드라이브의 볼륨을 일시 중지했고, MinIO가 정상 작동합니다. 장기적으로는 unique-drive-selection 기능을 활성화해 1:1 드라이브-볼륨 매핑을 설정할 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>kubectl directpv suspend drives 명령으로 LOST 상태의 드라이브를 일시 중지하면 MinIO가 남은 정상 드라이브로 정상 동작합니다.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>DirectPV 볼륨 프로비저닝은 가용 공간을 기준으로 드라이브를 선택하기 때문에 동일한 드라이브에 여러 볼륨이 생성될 수 있으며, 1:1 매핑을 원하면 unique drive selection을 활성화해야 합니다.</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16121</t>
@@ -3488,27 +3744,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>네트워크(Network)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>고객이 ObjectStore Operator가 private Nexus 레지스트리에서 이미지를 끌어오지 못해 TLS 인증 오류가 발생함을 보고하며, Helm 차트에 CA 인증서 마운트 방법이나 필요한 설정을 알려달라고 요청했습니다.</t>
+          <t>고객은 Helm 차트를 사용해 배포된 ObjectStore Operator에 Nexus CA 인증서를 마운트하고, 프라이빗 Nexus 레지스트리에 접근하도록 설정하는 방법에 대한 안내를 요청했습니다.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Operator는 자체적으로 이미지를 pull하려고 하지만 컨테이너 런타임은 private registry의 CA를 신뢰하고 있어, Operator가 CA를 알지 못해 'x509: certificate signed by unknown authority' 오류가 발생했습니다.</t>
+          <t>Operator가 자체적으로 이미지를 풀 때 프라이빗 Nexus의 커스텀 루트 CA를 인식하지 못해 TLS 인증서 검증에 실패했습니다. 컨테이너 런타임은 CA를 신뢰하지만, Operator는 별도로 이미지를 다운로드하기 때문에 인증서가 없으면 오류가 발생합니다.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>작업자는 AIStor 풀 StatefulSet을 수동으로 삭제해 Operator가 컨테이너 런타임을 사용해 이미지를 pull하도록 하여 오류를 회피했고, 향후 Operator가 런타임을 활용하도록 업데이트될 예정입니다.</t>
+          <t>AIStor 풀 StatefulSet을 수동으로 삭제하면, Operator가 최신 버전으로 재생성하면서 컨테이너 런타임을 통해 이미지를 풀어 인증서 검증 문제를 우회할 수 있습니다. 이는 현재 적용 가능한 임시 해결책이며, 향후 Operator 업그레이드 시 이 문제가 해결될 예정입니다.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>작업자는 상태 정상이 되었다고 보고했고, 서비스 중단 없이 임시 해결책이 효과적이었습니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3538,26 +3794,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ramon de Klein</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>애플리케이션(Application)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>고객은 mc admin service restart 명령을 실행한 뒤, 54개의 노드 중 하나만에서만 오디트 로그가 생성되는 문제를 보고했습니다.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>고객은 mc admin service restart 이후 오디오 로그가 54개의 노드 중 하나에서만 발생하는 문제를 보고했습니다.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>audit_webhook 설정에 중복된 endpoint 값이 포함되어 있어 일부 노드에서만 로그가 전송되었습니다.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>노드들을 하나씩 재시작하거나 mc admin service restart를 다시 실행하여 모든 노드에서 로그가 정상적으로 수집되도록 했습니다.</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>mc admin service restart ALIAS를 다시 실행하거나 audit_webhook 설정을 올바른 단일 endpoint로 수정 후 서비스 재시작했습니다.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>문제가 해결된 후 로그가 정상적으로 수집되었습니다.</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/16005</t>
@@ -3595,22 +3859,22 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>고객은 ILM 만료 동작이 1일 이후에도 지연되어 객체가 남아 있는 것이 정상인지, 그리고 ILM 실행이 백그라운드 스캐너에 의존하는지 여부를 문의했습니다.</t>
+          <t>사용자가 ILM 만료 규칙을 설정했으나 1일 후에도 객체가 남아 있어 지연이 예상되는지와 ILM 실행 메커니즘을 문의했습니다.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ILM은 백그라운드 스캐너를 통해 실행되며, 실시간으로 삭제하지 않고 스캐너가 객체를 스캔하는 시점에 삭제됩니다.</t>
+          <t>ILM은 실시간이 아니라 백그라운드 스캐너를 통해 실행되므로 객체가 즉시 삭제되지 않는다.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>이 지연은 정상이며, scanner speed=fast 설정을 통해 스캐너 속도를 높여 지연 시간을 단축할 수 있습니다.</t>
+          <t>scanner speed=fast를 설정하면 스캐너가 더 자주 실행되어 지연을 줄일 수 있다.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>스캐너 실행 간격과 속도에 대한 구체적 값은 제공되지 않았다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3650,16 +3914,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>RIA CHOI는 1천만 개 객체의 크기 분포를 보고 싶으며, mc find 사용 여부를 묻고 있습니다.</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>사용자가 1천만 개 객체의 크기 분포를 확인하고 싶어하며, mc find 명령이 적절한지 묻고 있다.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Shubhendu는 mc admin prometheus metrics play/ | grep minio_cluster_objects_size_distribution 명령을 사용해 각 객체 크기 범위별 개수를 조회하는 방법을 제안했습니다. 이 명령은 클러스터 전역에서 객체 크기 분포를 제공하며, 사용자가 필요로 하는 정보를 정확히 반환합니다.</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
+          <t>mc admin prometheus metrics play/ | grep minio_cluster_objects_size_distribution 명령을 사용하면 객체 크기 분포를 확인할 수 있다.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15973</t>
@@ -3697,20 +3969,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>사용자는 오픈서치로 전송되는 감사 로그가 지속적으로 "Error: not connected to target server/service" 를 표시하며, audit_webhook을 disable 했음에도 동일한 오류가 계속 발생하고, 54개의 노드 중 일부 노드에서만 감사 로그가 전송되는 문제를 해결할 수 있는 방법을 문의했습니다.</t>
+          <t>고객은 audit_webhook을 비활성화하고 서비스 재시작 후에도 'not connected to target server/service' 오류가 계속 발생하며, pod 재시작이 유일한 해결책인지 묻고 있습니다. 또한 54개의 노드 중 일부 노드에서만 audit 로그가 전송되는 현상을 보고하고 있습니다.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Fluent Bit pod의 CPU 한계(1로 설정)로 인해 OpenSearch에 과부하가 발생해 연결이 끊겼으며, audit_webhook 설정이 모든 노드에 일관되게 적용되지 않아 일부 노드에서만 로그가 전송되었습니다.</t>
+          <t>Fluent Bit pod의 CPU 한계가 낮아 로드가 과부하되어 타깃 서버가 연결을 거부했습니다. 또한 audit_webhook 설정이 클러스터 전체에 일관되게 적용되지 않아 일부 노드에서만 로그가 전송되었습니다.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Fluent Bit pod의 CPU 한계를 2로 증가시켜 오류를 제거하고, audit_webhook 설정을 enable=off 으로 전역적으로 적용한 뒤, 필요한 경우 pod를 재시작하여 설정을 반영하며, Prometheus 메트릭을 모니터링해 큐 길이와 실패 수를 확인합니다.</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
+          <t>Fluent Bit pod의 CPU 한계를 2로 늘려 오류를 해결했습니다. audit_webhook 설정을 클러스터 전체에 일관되게 적용하고, 설정 변경 후 모든 노드의 pod를 재시작하거나 mc admin config set 명령을 사용해 enable=off를 적용해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15964</t>
@@ -3743,21 +4019,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>RIA CHOI는 /var/lib/kubelet/pods 에서 수천 개의 마운트 경로가 생성될 때 OS 레벨의 디스크 IOPS, 대역폭, 파일 시스템 성능에 영향을 미칠지 여부를 묻습니다. 또한 DirectPV가 볼륨을 관리 중일 때 kubelet 루트 디렉터리를 수정하는 것이 안전한지 궁금합니다. 마지막으로 kubelet 루트가 다른 디스크로 이동될 때 기존 볼륨, 마운트 작업, 연결 워크플로우에 문제가 생길지에 대해 알고 싶어합니다.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>대규모 mount 경로가 OS 수준의 Disk IOPS, 대역폭, 파일 시스템 성능에 영향을 미치는지, kubelet 루트 디렉터리를 NVMe로 옮길 때 DirectPV가 볼륨을 관리 중인 상태에서 안전한지, 그리고 mount 경로가 다른 디스크로 이동하면 기존 볼륨, 마운트 작업, 부착 워크플로우에 문제가 생기는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>대용량 mount 경로가 파일 시스템 메타데이터 I/O를 과도하게 발생시켜 OS 디스크 I/O가 100%에 달할 수 있다는 우려가 있습니다.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>kubelet 루트 디렉터리를 NVMe 장치로 옮기고, DirectPV Deployment와 DaemonSet에 새 kubelet 경로를 반영한 뒤 Kubernetes 서비스와 MinIO, DirectPV 노드 및 컨트롤러 포드를 중지합니다. 그 다음 노드를 재부팅하고 서비스를 재시작하면 됩니다. 재부팅 후 DirectPV는 정상 동작하며 기존 볼륨에는 영향이 없습니다.</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
+          <t>kubelet 루트 디렉터리를 이동하려면 노드에서 Kubernetes와 MinIO, DirectPV 노드 서버/컨트롤러를 중지하고, /var/lib/kubelet을 새로운 NVMe 드라이브에 마운트한 뒤 노드를 재부팅합니다. 경로가 동일하게 유지된다면 DirectPV DaemonSet을 재시작해도 정상 동작하며, DirectPV는 새로운 kubelet 경로를 인식합니다.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15856</t>
@@ -3795,16 +4079,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>사용자는 mc du 명령이 내부적으로 캐시된 데이터를 사용하여 작업하는지, 아니면 새로 객체 목록을 가져와 각 객체의 메타데이터를 디스크에서 직접 읽는지 궁금합니다.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>고객이 mc du 명령이 내부적으로 어떻게 동작하는지, 캐시된 데이터 사용 여부와 새로 목록을 가져와서 메타데이터를 읽는지 궁금해했습니다.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>mc du는 새로 목록을 가져와서 각 객체의 메타데이터를 디스크에서 직접 읽습니다. 백그라운드 스캐너의 캐시를 사용하지 않습니다.</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
+          <t>mc du는 새 목록을 가져와서 실행하며, 백그라운드 스캐너의 캐시 데이터를 사용하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15855</t>
@@ -3842,20 +4134,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>고객은 같은 Kubernetes 클러스터에 배포된 서로 다른 객체스토어가 서로 통신하도록 설계되었는지와, NodePort를 사용해 warp 로드를 B에서 수행할 때 A의 NIC 사용량이 비정상적으로 증가하는 현상에 대해 문의했습니다.</t>
+          <t>고객이 동일한 Kubernetes 클러스터에 배포된 서로 다른 MinIO 객체스토어가 서로 통신하도록 설계되었는지와, 객체스토어 B가 부하를 주면 객체스토어 A의 NIC 사용량이 증가하는 원인을 알고 싶어합니다.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>MinIO 클러스터는 서로 완전히 격리되어 통신하지 않으며, 두 객체스토어가 동일한 Kubernetes 네트워크를 공유함으로써 NodePort/ClusterIP에서 발생하는 트래픽 라우팅이 다른 객체스토어의 노드에 영향을 주어 NIC 사용량이 증가한 것으로 판단됩니다. 특히 bond1에서 NodePort를 사용하면 트래픽이 노드 간 라우팅되어 A의 10개 노드에 부하가 걸리는 현상이 확인되었습니다.</t>
+          <t>두 객체스토어가 같은 클러스터에 배치되었음에도 서로 통신하지 않으며, NIC 사용량 증가는 Kubernetes 네트워킹 레이어와 NodePort/ClusterIP 라우팅에 의해 발생합니다.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>NodePort 서비스의 externalTrafficPolicy를 'Local'로 설정하면 트래픽이 해당 노드에 로컬 엔드포인트로만 전달되어 교차 트래픽이 줄어들 수 있습니다. 현재 외부 트래픽 정책이 Local로 설정되어 있으므로, 필요하면 내부 트래픽 정책이나 CNI 라우팅 구성을 점검해 추가적인 성능 최적화를 진행합니다.</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>NodePort 서비스에 externalTrafficPolicy를 Local로 설정하면 트래픽이 로컬 엔드포인트로만 전달되어 NIC 사용량이 감소할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15844</t>
@@ -3883,7 +4179,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Krutika Dhananjay</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3893,20 +4189,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>사용자는 버킷 수준이 아니라 사용자별 혹은 특정 접두어(prefix)별로 할당량(quota)을 설정할 수 있는지 문의했습니다.</t>
+          <t>사용자가 버킷 수준의 할당량을 설정할 수 있다는 것을 알고 있지만, 사용자별 또는 특정 접두어별로 할당량을 설정할 수 있는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>AiStor는 사용자 또는 접두어에 대한 할당량을 지원하지 않으며, 버킷 수준만 지원합니다.</t>
+          <t>AiStor에서는 사용자 할당량이나 접두어 할당량을 지원하지 않으며, 버킷 할당량만 지원합니다.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>해당 기능은 현재 불가하므로, 버킷 수준의 할당량만 설정하시면 됩니다.</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>해당 기능은 현재 지원되지 않으므로, 버킷 수준에서만 할당량을 설정해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15832</t>
@@ -3934,7 +4234,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Praveen,Grahit A Desai</t>
+          <t>Praveen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3944,22 +4244,22 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>고객은 AIStor에서 프리픽스 수준 사용량을 직접 제공하는 API나 webhook이 있는지 문의했습니다. 없다면 mc du를 오프피크 시간에 실행해 사용량 메트릭을 수집하는 것이 적절한지 확인하고 싶어 합니다.</t>
+          <t>고객은 4PB 규모의 데이터에서 접두사(프리픽스) 수준 사용량을 확인할 수 있는 API나 웹훅이 있는지 문의했습니다. 현재 mc du를 사용해 오프피크에 정기적으로 실행하려는 방안을 검토 중이며, 이 방법이 가장 효율적인지 여부를 알고 싶어합니다. 또한 ListObjects 호출이 소비하는 리소스를 모니터링할 수 있는 지표가 있는지도 궁금합니다.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>mc du는 ListObjects 호출을 수행해 대용량 버킷/프리픽스에서 느리고 리소스를 많이 소비합니다. 현재 스캐너 메트릭은 버킷 단위 또는 전체 사용량만 제공해 프리픽스 수준 메트릭이 부족합니다.</t>
+          <t>mc du가 ListObjects 호출을 사용해 대규모 버킷에서 느리고 비용이 많이 든다. 현재 스캐너 메트릭은 버킷 수준만 제공해 프리픽스 수준 사용량을 제공하지 않는다.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>현재는 오프피크 시간에 mc du를 실행해 프리픽스 사용량을 수집하도록 권장합니다. ListObjects 호출 비용을 모니터링하기 위해 mc admin trace를 사용하도록 안내했습니다. 인벤토리 기능이 도입되면 프리픽스 수준 사용량 리포트가 제공될 예정입니다.</t>
+          <t>현재는 mc du가 프리픽스 사용량 보고서에 유일한 솔루션이며, 오프피크에 실행하는 것이 권장된다. 인벤토리 기능이 도입될 예정이며, 그때 프리픽스 수준 보고가 가능할 것이다. ListObjects 호출 비용을 모니터링하려면 mc admin trace 명령을 사용해 분석할 수 있다.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>인벤토리 기능은 테스트 중이며, 향후 명확한 출시 일정이 발표될 예정입니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3994,21 +4294,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>고객은 MinIO Console Object Browser를 통해 대용량 파일을 다운로드할 때, object-store pods의 메모리 사용량이 크게 증가할 수 있는지 궁금해했습니다.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>사용자가 MinIO Console Object Browser를 통해 대용량 파일을 다운로드할 때, 객체 저장소 pod의 메모리 사용량이 크게 증가할 수 있는지 확인하고, 이를 조정하거나 최적화할 수 있는 방법이 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>MinIO 객체 저장소 pod는 대용량 파일 다운로드 시 스트리밍 방식으로 처리하므로, 메모리 버퍼링이 발생하지 않아 메모리 사용량이 크게 증가하지 않습니다.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>다운로드 시 객체 브라우저가 스트리밍 방식을 사용하므로, 객체 스토어 또는 콘솔 백엔드 API에서 버퍼링되지 않아 메모리 사용량이 크게 늘어나지 않습니다.</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
+          <t>MinIO는 대용량 파일 다운로드 시 스트리밍으로 처리되므로 메모리 버퍼링이 없으며, 별도의 튜닝이 필요 없으며, 성능 이슈가 있을 경우 mc support profile 및 mc admin trace 명령을 사용해 분석할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15795</t>
@@ -4041,21 +4349,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>고객이 애플리케이션 전용 계정을 만들고, 해당 계정에 필요한 권한을 정의하려고 합니다.</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>사용자는 admin.DetachUserOrGroupPolicy와 admin.ListPolicies 액션을 찾을 수 없어서 필요한 권한 설정이 불확실합니다.</t>
+          <t>사용자가 필요한 정책 액션(admin.DetachUserOrGroupPolicy, admin.ListPolicies)을 찾지 못해 적절한 권한을 정의하기 어려웠습니다.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>사용자는 서비스 계정에 아래와 같은 최소 권한 정책을 붙여 주면 됩니다. 정책은 admin:CreatePolicy, admin:DeletePolicy, admin:GetPolicy, admin:ListUserPolicies, admin:UpdatePolicyAssociation, admin:CreateServiceAccount, admin:ListServiceAccounts 등을 허용하도록 정의합니다.</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+          <t>서비스 계정에 필요한 최소 권한을 포함한 정책 예시를 제공했습니다.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15794</t>
@@ -4083,30 +4399,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Grahit A Desai</t>
+          <t>Grahit A Desai, Allan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>스토리지(Storage)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim은 버킷에 많은 파일과 여러 접두어가 있는 상황에서 특정 키 접두어의 현재 사용량을 확인할 수 있는 방법을 찾고 있습니다. mc du 대신 다른 방법이 있는지 확인하고자 합니다.</t>
+          <t>고객이 특정 키 프리픽스의 현재 사용량을 확인할 수 있는 방법을 문의했습니다.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>mc ls --recursive --summarize 명령이 대규모 객체(3PB)에서 실행 시 mc du와 동일한 시간이 걸려 성능 문제가 발생하고 있습니다. 대용량 객체를 가진 접두어에서 목록화가 비용이 많이 들기 때문입니다.</t>
+          <t>프리픽스에 수많은 파일이 존재해 mc du와 mc ls 명령이 오래 걸리기 때문입니다.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>mc ls --recursive --summarize 명령을 사용하여 접두어별 크기와 객체 수를 요약하도록 제안했습니다. 대규모 접두어의 경우 다른 메타데이터 수집 방법이나 사전 객체 배치 계획을 검토하도록 권장했습니다.</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
+          <t>mc ls --recursive --summarize 명령을 사용하거나, 메타데이터 수집 후 후처리하는 방법을 탐색할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15769</t>
@@ -4144,20 +4464,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim reported that the bucket count displayed on the test cluster’s bucket page is incorrect—showing 2 buckets while there are actually 4—despite the summary and UI overall matching mc results, and asked what else should be checked.</t>
+          <t>사용자가 테스트 클러스터에서 mc admin info와 UI에 표시되는 버킷 수 및 객체 수가 실제와 다르며, 버킷 페이지 정보가 부정확하다고 보고하고, 이 문제를 해결하기 위해 추가로 확인해야 할 사항을 문의했습니다.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>After performing multiple tests, including changing root credentials, switching the object store between nodes, and reinitializing disks, the MinIO scanner appears not to be running, as evidenced by the absence of scanner info and lack of output from scanner status commands.</t>
+          <t>mc admin scanner가 실행되지 않아 메타데이터가 업데이트되지 않아 버킷 수와 객체 수가 실제와 일치하지 않는 것으로 보입니다.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Verify that the MinIO scanner is running by checking minio logs for scanner activity and, if it is not running, start or restart the scanner (or MinIO) to trigger the correct bucket counting.</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15752</t>
@@ -4183,7 +4507,11 @@
           <t>Youngkyoo Kim03:24 PM</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Deepak Thimmaiah, Prakash</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>기능 및 사용법(Features &amp; Usage)</t>
@@ -4191,12 +4519,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>고객이 Keycloak에서 발급받은 JWT를 AIStor에서 인증·인가에 사용할 수 있는지, 그리고 JWT를 이용해 AssumeRoleWithWebIdentity STS API를 호출해 임시 자격증명을 획득하고 S3 API에 접근하는 절차가 가능한지 물어보았습니다.</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>고객은 Keycloak에서 발급받은 JWT를 사용해 AIStor에서 인증 및 권한 부여를 수행할 수 있는지 문의했습니다. 또한, JWT를 STS AssumeRoleWithWebIdentity API에 전달해 임시 자격 증명을 획득하고 S3 API에 접근하는 절차가 가능한지 확인하고자 합니다.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15683</t>
@@ -4234,20 +4574,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>사용자가 Helm 차트에서 MinIO 루트 자격 증명을 변경했을 때, 서비스가 정상적으로 재시작되는지와 운영 중인 MinIO 파드가 어떻게 재인증되는지에 대해 확인하고자 합니다.</t>
+          <t>사용자가 Helm 차트에서 MinIO 루트 자격 증명을 변경하고 Helm 업그레이드를 수행했을 때, 변경이 적용되는지, 그리고 롤링 업데이트가 실패하는지 확인하고 싶어한다.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>루트 자격 증명을 변경하면 기존에 발급된 임시 토큰이 무효화되므로 MinIO 서비스가 재시작되거나 파드가 재배포되어야 재인증이 이루어집니다.</t>
+          <t>MinIO 루트 자격 증명은 내부 서비스와 토큰 서명에 사용되므로 변경 시 기존 임시 토큰이 무효화되고, 서비스 재시작이 필요하다. Helm 차트에서 secretKey만 변경해도 롤링 업데이트가 트리거되지 않아 인증 실패가 발생한다.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2025년 8월 15일 이후 AIStor 릴리스에서는 Helm 업그레이드나 상태 집합 재배포 시 파드 내부에서 MinIO 서비스가 재시작되며, 임시 토큰이 자동으로 갱신됩니다. 운영 환경에서는 테스트 환경에서 먼저 검증 후 적용해야 합니다.</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
+          <t>MinIO 서비스는 Helm 업그레이드나 StatefulSet 롤업/삭제를 통해 재시작해야 하며, 2025년 8월 15일 이후 AIStor 릴리스에서는 pod 자체를 재생성하지 않고 내부에서 서비스 재시작이 이루어져 임시 토큰이 자동 갱신된다. 따라서 Helm 업그레이드 후 pod가 내부적으로 재시작되면 config.env가 업데이트되고, operator는 자동으로 재인증된다.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15644</t>
@@ -4285,21 +4629,22 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>고객은 EC 8:3로 구성된 MinIO 객체 저장소를 두 노드( worker12와 worker23 ) 간에 교환하고자 하며, 기존 데이터를 보존하면서 안전한 절차를 알고 싶어합니다.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>The user wants a documented, safe procedure to swap two objectstores between nodes, including whether deleting PVC/PV and removing DirectPV volumes/drives is sufficient, and how to handle DirectPV volume deletion with Retain reclaimPolicy. They also ask if data will heal automatically after reinitialization and node reassignment, assuming quorum remains.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>The user needs to move objectstores between nodes but is concerned about data loss and proper cleanup of DirectPV resources, especially with Retain reclaimPolicy.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1) worker12와 worker23에 연결된 pod, PVC, DirectPV 볼륨 및 드라이브를 식별합니다.
-2) 두 노드를 cordon하고, 해당 노드의 pod를 삭제해 Pending 상태로 둡니다.
-3) PVC(및 필요 시 PV)를 삭제해 DirectPV 볼륨을 수동으로 제거하도록 kubectl directpv clean 혹은 directpv remove 명령을 사용하고, 드라이브를 kubectl directpv remove 로 제거한 뒤, kubectl directpv discover 와 init 로 재초기화합니다.
-4) 노드를 uncordon 하면 스케줄러가 PV nodeAffinity를 기준으로 pod를 재배치하고, quorum이 유지되는 한 MinIO가 자동으로 데이터를 복구합니다.</t>
+          <t>Bala recommends identifying all related resources, cordoning the nodes, deleting pods and PVCs to trigger DirectPV volume deletion, removing drives with kubectl directpv remove, reinitializing with discover/init, and then uncordoning nodes. For Retain reclaimPolicy, use kubectl directpv clean or directpv remove to delete DirectPV volumes; manual finalizer edits are discouraged. As long as quorum is maintained, MinIO will automatically heal data from healthy disks after reinitialization and node reassignment.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>수동으로 finalizer를 삭제하거나 kubectl delete directpvdrives 명령을 직접 실행하는 것은 권장되지 않으며, 직접 편집은 사전 원인을 파악한 후에만 수행해야 합니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4339,22 +4684,22 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>고객은 MinKMS의 API/SDK 문서가 부족해 사용법 안내를 요청했습니다. 또한 MinKMS와 AIStor를 사용해 Kubernetes 시크릿, PostgreSQL 비밀번호 같은 민감 정보를 암호화 및 저장하고자 합니다.</t>
+          <t>The user requested API documentation for MinKMS, including SDKs for Java and Python, and a usage guide. They also asked whether MinKMS can be used with AIStor to encrypt and store secrets such as Kubernetes secrets and database passwords, and whether automatic credential rotation is supported.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CLI 전용 문서만 제공되어 API 예제 및 SDK 지원 여부가 명확하지 않아 추가 자료가 필요합니다.</t>
+          <t>The user could not find API documentation or SDKs for MinKMS beyond the CLI, and was unsure if MinKMS can handle secret storage and rotation with AIStor.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>MinKMS와 AIStor를 사용해 암호화된 객체를 저장할 수 있지만, AIStor는 비밀 관리 시스템이 아니므로 비밀 회전 및 무효화 기능은 별도로 구현해야 합니다. 또한 Go용 kms-go SDK만 제공되고, Java/Python SDK는 없으므로 직접 구현하거나 다른 언어용 래퍼를 작성해야 합니다.</t>
+          <t>MinKMS can encrypt and store data in AIStor, but secret rotation and invalidation must be implemented separately; AIStor does not automatically rotate secrets.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>고객은 이후 추가 질문 없이 대화를 종료했습니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4394,22 +4739,22 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>고객은 Broadcom NIC를 장착한 노드에서 TCP 연결 끊김이 발생하고 패킷 손실이 보고되었으며, Cilium pod 재시작 후 해결되는 현상을 보고했습니다. 또한, MinIO가 과거에 유사한 Broadcom NIC 이슈를 보았는지 확인하고 해결 방안을 요청했습니다.</t>
+          <t>고객이 Broadcom NIC에서 발생한 TCP 연결 끊김 현상에 대해 MinIO가 과거에 유사 사례를 보았는지와 해결 방안을 문의했습니다.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Broadcom NIC에서 하드웨어, 펌웨어, 또는 드라이버 문제가 있을 가능성이 높으며, 네트워크 스택 튜닝이 필요할 수 있다.</t>
+          <t>Broadcom NIC에서 패킷 손실이 발생해 TCP 연결이 끊기는 현상으로, ip -s link에서 Broadcom 노드만 미스 패킷이 나타났습니다.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>펌웨어와 드라이버를 최신 버전으로 업데이트하고, Linux 커널 튜닝(IRQ, RX/TX 큐, NUMA, 드라이버 파라미터)을 적용하거나 Broadcom NIC를 Intel NIC로 교체하면 문제가 해결됩니다.</t>
+          <t>Cilium pods를 재시작하면 일시적으로 해결되고, Broadcom NIC을 Intel으로 교체하면 문제가 사라집니다. 또한 펌웨어와 드라이버를 최신화하고 Linux 튜닝(IRQ, RX/TX 큐, NUMA, 드라이버 파라미터)을 적용하는 것이 권장됩니다.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Dell KB 문서에서 동일한 Broadcom NIC 연결 끊김 문제가 보고됨.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4449,22 +4794,22 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>고객은 3개의 노드가 드레인되고 오프라인 상태가 되자, mc admin info와 콘솔에서 대부분의 노드가 오프라인으로 표시되는 현상을 보고했습니다. 이 현상이 왜 발생하는지, 그리고 실제 서비스가 정상 동작 중임을 어떻게 확인할 수 있는지 확인 요청했습니다.</t>
+          <t>고객은 3개의 노드를 드레인한 뒤 mc admin info와 MinIO 콘솔에서 62개의 노드가 오프라인으로 표시되는 현상을 보고, 서비스는 정상 동작 중임을 확인하면서 이 차이가 발생할 수 있는 조건을 알고 싶어합니다.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>mc admin info 명령이 내부 스캔을 완료하지 못해 오프라인 노드 수를 잘못 계산하는 버그가 있습니다. 콘솔도 동일한 호출을 사용하기 때문에 잘못된 정보를 표시합니다. 이 버그는 최근 마스터 브랜치에서 수정되었습니다.</t>
+          <t>mc admin info 명령이 내부적으로 오프라인 노드 수를 잘못 계산해 잘못된 값을 반환하는 버그가 존재합니다.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>새로운 릴리스가 배포되면 버그가 수정되어 정확한 노드 상태가 표시됩니다. 현재는 30초 정도 소요되는 mc admin info 명령을 사용해 확인하고, 문제 발생 시 노드를 다시 온라인 상태로 복구하면 서비스가 정상 동작합니다.</t>
+          <t>이 버그는 최신 릴리스에서 수정되었으며, 최신 버전으로 업그레이드하면 정상적으로 노드 상태가 표시됩니다.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>mc admin info 명령 실행 시 약 30초가 걸립니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4504,16 +4849,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim은 노드 1–58 및 71–74를 하나의 객체 저장소 풀에 포함시키고, 노드 59–70을 제외한 뒤, 이후 노드 59–70 및 75–90으로 두 번째 풀을 만들 수 있는지 여부를 묻는 요청을 했습니다.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>고객은 노드 1–58과 71–74만을 같은 객체 저장소 풀에 포함시키고, 59–70은 제외하도록 구성할 수 있는지, 그리고 나중에 59–70과 75–90을 포함한 두 번째 풀을 만들면 정상적으로 동작할지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Cesar Celis는 Kubernetes에서 비연속 노드 집합을 라벨링하고 pool의 nodeSelector 또는 nodeAffinity를 해당 라벨에 포인팅하면 원하는 풀을 만들 수 있다고 답했습니다. 또한 하드웨어와 드라이브 수가 같은지, EC 파리티 요구사항 충족 여부, 실패 도메인에 걸쳐 반대부착, 새 풀 추가 시 기존 객체 재배분이 자동이 아니라는 점을 주의하라고 조언했습니다.</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
+          <t>네, Kubernetes에서는 원하는 노드 집합을 라벨링하고 pool의 nodeSelector 또는 nodeAffinity를 해당 라벨에 지정하면 비연속 노드로도 객체 저장소 풀을 만들 수 있습니다. 이후 남은 노드에 라벨을 지정해 두 번째 풀을 정의하면 됩니다. 단, 각 풀 내에서 하드웨어와 드라이브 수가 동일해야 하고, EC 패리티 요구사항을 충족하며, 실패 도메인에 걸쳐 pod를 분산시키는 anti-affinity를 적용해야 하며, 새 풀을 추가해도 기존 객체는 자동으로 재배치되지 않으므로, 새 쓰기만 새 풀을 사용하고 기존 데이터를 이동하려면 ILM이나 복사 도구를 사용해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15511</t>
@@ -4551,16 +4904,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>고객은 기존 노드를 새 노드로 교체하는 절차와 정확한 단계별 과정을 문의했습니다. 또한 데이터 이전 방법이 있는지 여부를 물었습니다.</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>사용자가 기존 노드를 새 노드로 교체하는 절차와 데이터 직접 마이그레이션 가능 여부를 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>노드를 교체하려면 먼저 해당 노드의 DirectPV 리소스를 삭제하고, PVC 및 PV를 정리한 뒤 같은 호스트명으로 새 노드를 추가합니다. 새 노드를 cordon 해제하고 DirectPV 데몬셋에 참여하도록 하며, 드라이브를 초기화하고 탐색하면 새로운 PVC와 PV가 생성됩니다. 데이터는 직접 이전이 불가능하며 남은 디스크에서 복구(healing) 과정을 통해 재구성됩니다.</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
+          <t>노드 교체 시 기존 노드의 DirectPV 리소스를 삭제하고, PVC와 PV를 제거한 뒤, 동일 호스트명으로 새 노드를 추가하고 드라이브를 초기화합니다. 이후 새 노드가 DirectPV DaemonSet에 참여하면 PVC와 PV가 새로 생성되고, MinIO는 남은 디스크에서 데이터를 복구합니다.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15507</t>
@@ -4598,16 +4959,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>고객은 SSH 연결 실패와 재연결 기록을 모니터링할 수 있는 AIStor 메트릭을 요청하고, 해당 메트릭의 상세 설명과 수집 간격을 묻습니다.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>고객은 특정 노드에서 발생하는 간헐적인 SSH 연결 문제에 대해 알림을 생성할 수 있는 AIStor 메트릭을 찾고, 해당 메트릭의 상세 설명과 수집 주기를 알고 싶어합니다.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>노드가 일시적으로 연결이 끊어졌다가 재연결되는 간헐적인 SSH 연결 실패가 발생하고 있습니다.</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>minio_cluster_health_nodes_offline_count 메트릭을 사용하여 노드 오프라인 상태를 감지하고, 이 메트릭은 매 분마다 업데이트되므로 알림을 설정할 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
+          <t>minio_cluster_nodes_offline_count 메트릭(분 단위로 갱신)을 사용해 노드 오프라인 상태를 감지하고, SSH 연결 문제는 MinIO 메트릭이 직접 포착하지 않으므로 네트워크 모니터링을 병행해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15493</t>
@@ -4640,21 +5009,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>애플리케이션(Application)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>고객이 AIStor에 TLS를 활성화한 후 Spark, StarRocks, Java 기반 애플리케이션에서 액세스하고 사용하는 방법에 대한 개발자 가이드 또는 참조 웹사이트를 제공해 달라고 요청했습니다.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>고객이 TLS를 활성화한 후 Spark, StarRocks, Java 기반 애플리케이션에서 AIStor에 접근하고 사용하는 방법에 대한 개발자 가이드나 참조 웹사이트를 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>답변자가 Spark에 필요한 Hadoop 설정 예시를 제공하며, https://blog.min.io/spark-minio-kubernetes/ 블로그 링크를 공유했습니다.</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
+          <t>Anis Eleuch은 MinIO 블로그 링크와 Spark에서 TLS를 활성화하기 위한 Hadoop 설정 예시를 제공했습니다.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15462</t>
@@ -4682,7 +5059,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jiuker</t>
+          <t>Mark Theunissen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4692,12 +5069,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>고객이 MinIO에서 minio_api_requests_ttfb_seconds_distribution 및 minio_system_drive_reads_per_sec 메트릭이 보이지 않아 원인을 물어보고 해결책을 요청했습니다.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>고객이 MinIO API 요청 지연 시간( TTFB ) 메트릭이 Prometheus에 표시되지 않는 이유와 해결 방법을 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>현재 MinIO 버전에서 minio_api_requests_ttfb_seconds_distribution 메트릭이 수집되지 않는 버그가 존재합니다.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>버그가 다음 릴리스에서 수정되었으므로 최신 MinIO 버전으로 업그레이드하면 메트릭이 표시됩니다.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15445</t>
@@ -4725,26 +5114,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nagashree Mylaraiah, Alexander Kalaj</t>
+          <t>Alexander Kalaj</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>스토리지(Storage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>고객은 30개의 StorageClass를 유지하는 것이 쿠버네티스의 성능, 장애 처리 및 관리에 부정적 영향을 미칠지 궁금해했습니다.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>고객이 30개의 StorageClass를 유지하는 것이 Kubernetes의 성능, 장애 처리, 관리 측면에서 운영 부담을 초래하는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Nagashree Mylaraiah와 Alexander Kalaj는 30개의 StorageClass가 쿠버네티스 성능이나 장애 처리에 영향을 주지 않으며, rack‑awareness 스크립트에 의해 관리될 때 관리 오버헤드가 매우 낮다고 답변했습니다.</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
+          <t>MinIO 팀은 30개의 StorageClass를 생성해도 Kubernetes에 성능이나 장애 처리에 영향을 주지 않으며, 관리 오버헤드도 낮다고 답변했습니다.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15358</t>
@@ -4782,16 +5179,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>고객인 Youngkyoo Kim이 CDP Hadoop에서 Aistor로 데이터를 전송할 때 사용하는 명령과 매개변수를 알고 싶어 문의했다.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>CDP Hadoop에서 Aistor로 데이터를 전송할 때 사용되는 명령어와 파라미터를 알려달라는 요청</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Shireesh Anjal은 고객에게 https://blog.min.io/migrating-hdfs-to-object-storage/ 문서를 참고하라고 안내했다.</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
+          <t>문서에서 명시된 명령어와 파라미터를 확인하도록 안내했습니다.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15316</t>
@@ -4829,20 +5234,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim이 prep-job.yaml을 실행했을 때 기존 XFS 파일 시스템이 있는 디스크가 있는 경우 재설치를 위해 예외를 허용하는 옵션이 있는지 문의했습니다.</t>
+          <t>고객은 prep-job.yaml 실행 시 기존 XFS 파일 시스템이 존재하면 프로세스가 건너뛰어 재설치 옵션이 있는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>prep-job.yaml은 기본적으로 파일 시스템이 있는 드라이브를 건너뛰도록 설계되어 있으며, 이는 새로운 설치에만 적용됩니다.</t>
+          <t>prep-job.yaml는 기존 파일 시스템이 있는 드라이브를 건너뛰도록 설계되었습니다.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>드라이브가 마운트되지 않은 상태라면 discover 및 init 프로세스를 사용하면 재설치를 진행할 수 있습니다. prep job은 예상대로 동작합니다.</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
+          <t>prep job은 새 설치용이며, 기존 파일 시스템이 있는 경우에는 드라이브가 마운트되지 않은 상태에서 discover 및 init 명령을 사용하면 됩니다.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15172</t>
@@ -4875,21 +5284,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>사용자는 MinIO에서 랙 인식 기능을 적용하고자 하며, 58개의 노드가 있고 각 랙에 1~4개의 노드가 배정되어 있는 상황에서 랙 인식을 활성화하기 위해 topology.kubernetes.io/zone 레이블을 각 노드에 추가하고, Helm 차트에 podAntiAffinity 및 topologySpreadConstraints를 설정해야 하는지 묻고 있다. 또한, 이러한 설정을 위한 간단한 예시 구성 파일을 요청하고 있다.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>고객이 MinIO 객체 저장소에 랙 인식 기능을 적용하려고 하며, 노드에 topology.kubernetes.io/zone 라벨을 추가하고 Helm 차트에서 podAntiAffinity와 topologySpreadConstraints를 설정해야 하는지, 그리고 예시 구성 파일을 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>노드 수가 랙마다 다르기 때문에 topologySpreadConstraints의 maxSkew 설정이 영향을 받을 수 있다는 우려가 있습니다.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Jiuker는 helm upgrade 명령을 사용한 예시를 제공하며, 각 노드에 topology.kubernetes.io/zone 레이블을 추가하고 podAntiAffinity와 topologySpreadConstraints를 설정하도록 안내했다. 그는 또한 랙이 단지 레이블일 뿐이며, topologySpreadConstraints가 스케줄링을 균등하게 하도록 시도한다는 점을 설명했다.</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr"/>
+          <t>Jiuker은 Helm 차트에 podAntiAffinity와 topologySpreadConstraints를 설정하는 예시 명령어를 제공하고, 랙은 단순 라벨이므로 노드에 라벨만 붙이면 되고, topologySpreadConstraints는 노드를 균등하게 배치하려는 시도를 한다고 설명했습니다.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15110</t>
@@ -4922,21 +5339,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>애플리케이션(Application)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>고객은 AIStor에서 LDAP 기반 서비스 계정 생성 명령이 실패하고, MinIO에서는 정상적으로 동작하는 이유를 확인하고자 합니다.</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>사용자는 동일한 LDAP 설정에서 MinIO에서는 명령이 성공하지만 AIStor에서는 실패하는 이유를 확인해 달라고 요청했다.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>AIStor는 ‘mc admin accesskey create &lt;alias&gt; username’ 명령을 지원하지 않으며, 올바른 구문은 ‘mc idp ldap accesskey create alias/ username’이다. 잘못된 명령 사용으로 사용자 존재 여부를 확인하지 못해 오류가 발생했다.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>사용자는 명령어를 'mc idp ldap accesskey create alias/ username' 형식으로 실행하면 서비스 계정 생성이 정상적으로 이루어집니다.</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
+          <t>‘mc idp ldap accesskey create alias/ username’ 명령을 사용하거나, AIStor에서 지원되는 LDAP 명령 구문을 확인해 올바르게 실행한다. 또한 LDAP에 사용자가 존재하는지 재확인한다.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/15075</t>
@@ -4969,25 +5394,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>고객은 소형 객체(64 KiB) 사용 시 동시성 증가에도 네트워크 사용량이 제한되는 현상을 보고하고, 병목 원인을 파악하고 해결책을 요청했습니다.</t>
+          <t>작은 객체 크기(64 KiB)에서 동시성 증가에도 네트워크 대역폭이 1.5 GB/s에 머무르는 이유와 성능을 개선할 방법을 알고 싶다. 현재 드라이브 IOPS가 1000 이하이며, 5–6 GB/s의 드라이브 대역폭이 있음에도 불구하고 병목이 발생한다. 이러한 상황에서 IOPS와 네트워크 사용량을 최적화하려는 요청이다.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MinIO는 객체 생성 시 여러 시스템 호출과 EC 스트라이프 단위당 IOP를 필요로 하며, 현재 8개의 EC 드라이브와 8:3 설정이 높은 HA와 대형 스트라이프를 초래해 드라이브 IOPS(≈1000 IOPS)를 초과하지 못하게 합니다.</t>
+          <t>작은 객체는 IOPS에 의존하며, EC 스트라이프 크기와 HA 설정으로 인해 각 EC 세트가 하나의 I/O 단위로 동작해 드라이브 IOPS가 한계에 도달한다. 또한 객체 저장 시 여러 시스템 호출(mkdir, fsync, O_DIRECT 등)이 발생해 전체 지연이 증가한다.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>스트라이프 크기를 4로 줄이고 MINIO_ERASURE_SET_DRIVE_COUNT를 4로 설정하면 IOP를 두 배로 늘릴 수 있으며, 필요 시 패리티 수를 낮춰 HA를 일부 감소시키는 방안을 권장합니다.</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr"/>
+          <t>EC 스트라이프 크기를 4로 줄여 IOPS를 두 배로 늘리고, HA를 낮추어 드라이브 수를 줄이며, io_uring 기반 I/O를 도입해 CPU 사용량과 지연을 감소시킨다. 현재 설정을 MINIO_ERASURE_SET_DRIVE_COUNT=4로 변경해 테스트해 보라.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>클러스터 정보와 진단 데이터를 업로드했으며, 현재 스트라이프 크기는 8, 패리티 3이다.</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14993</t>
@@ -5025,16 +5454,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>고객이 MinIO에서 특정 하드웨어 및 네트워크 사양에 따라 기대할 수 있는 벤치마크 수치를 보여주는 공식 성능 테스트 가이드라인이나 문서/공식을 제공해 주실 수 있는지 문의했습니다.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>고객이 특정 하드웨어와 네트워크 사양에 대한 공식 성능 테스트 가이드라인이나 벤치마크 수치를 제공해 주실 수 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Eco는 warp benchmark 유틸리티를 사용하고, mc support diag를 실행해 성능에 영향을 주는 일반적인 문제를 해결하도록 권장했습니다. mc support perf 명령으로 기본 테스트를 수행하고, 충분한 클라이언트 트래픽을 확보한 뒤 warp의 옵션으로 다양한 객체 크기와 동시성 수준을 테스트하도록 안내했습니다. 테스트 전에는 실행할 warp 명령을 제공해 주시면 피드백을 받을 수 있도록 했습니다.</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
+          <t>Eco는 warp 벤치마크 유틸리티를 사용하고, mc support diag와 perf를 실행해 문제를 해결하며, 충분한 클라이언트 트래픽과 적절한 동시성을 설정하고, warp 명령을 사전에 공유해 피드백을 받도록 권장했습니다.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14992</t>
@@ -5062,30 +5499,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mark Theunissen</t>
+          <t>Mark Theunissen, Harshavardhana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>네트워크(Network)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim은 RHEL 9.4에서 MinIO 튜닝 프로필을 적용했음에도 성능이 향상되지 않았다는 점을 질문하며, 누락된 단계가 있는지 혹은 특정 조건에서만 효과가 나타나는지 문의했습니다.</t>
+          <t>사용자는 RHEL 9.4에서 MinIO 튜닝 프로파일을 적용한 뒤 warp와 mc support perf 테스트를 실행했으나 성능 차이가 거의 없다고 보고하며, 설정을 놓친 것인지 혹은 특정 조건에서만 효과가 있는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Mark Theunissen은 RHEL이 이미 최적화되어 있어 튜닝 프로필이 변화를 주지 않았을 수 있고, 일부 매개변수는 네트워크가 최대 Saturation 상태에서만 성능을 향상시킬 수 있다고 설명했습니다. Harshavardhana는 기본 벤치마킹에서 Linux 커널이 이미 적절히 튜닝되어 있어 warp 테스트에서는 큰 이점을 보지 못한다는 점을 덧붙였습니다.</t>
+          <t>RHEL 커널이 이미 대부분의 워크로드에 대해 최적화되어 있어 튜닝 프로파일이 변화를 주지 않았거나, warp 테스트가 네트워크를 최대한 활용하지 않아 튜닝 파라미터가 발휘되지 않았기 때문일 수 있습니다.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Mark은 warp 테스트 파라미터와 시스템 메트릭을 상세히 제공하여 Klaus Post 또는 Harshavardhana에게 전달하면 보다 정밀한 피드백을 받을 수 있다고 권유했습니다. Harshavardhana는 장기 실행 및 리소스가 집중되는 환경에서 튜닝 프로필이 효과적이며, RHEL 10 또는 Ubuntu 24.04 같은 최신 커널과 XFS NVMe 튜닝을 고려하도록 제안했습니다.</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
+          <t>네트워크를 최대한 활용하거나 장기간 실행되는 워크로드에서 테스트를 수행하고, RHEL10 또는 Ubuntu 24.04와 같은 최신 커널을 사용하며 XFS와 같은 파일시스템을 최신 버전으로 조정하면 튜닝 프로파일의 효과를 확인할 수 있습니다. 또한 warp 테스트 시 사용한 파라미터와 사전/사후 시스템 메트릭을 제공하면 보다 정확한 피드백을 받을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14920</t>
@@ -5111,20 +5552,36 @@
           <t>Youngkyoo Kim04:43 PM</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Val Bezrukov</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>스토리지(Storage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>고객이 AIStor 클러스터의 hot tier에 대해 EC 스트라이프 크기와 parity 블록 크기를 추천해달라고 요청했습니다.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>고객이 AIStor용 58개의 NVMe 노드로 구성된 핫 티어에 대한 EC 스트라이프 크기와 패리티 블록 크기를 추천해 달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>고객이 현재 하드웨어 구성을 업데이트하고, 핫 티어와 콜드 티어를 어떻게 구성할지 고민 중이며, EC 설정을 최적화하려고 합니다.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Val Bezrukov 제안에 따라 5개 SATA 노드 그룹을 8개로 늘리는 것이 좋습니다.</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14899</t>
@@ -5162,20 +5619,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>사용자가 AIStor 콘솔에서 모니터링 기능이 사라졌다고 보고, Prometheus로 메트릭을 전송하고 Grafana에서 확인할 수 있는 템플릿을 제공해 달라고 요청했습니다. 또한 Kubernetes 환경에서 노드 URL 사용 방식에 대해 문의했습니다.</t>
+          <t>고객이 AIStor 콘솔에서 모니터링 기능이 사라졌으며, Prometheus와 Grafana에 메트릭을 전송하고 대시보드를 확인할 수 있는 템플릿을 요청했습니다. 또한 Kubernetes 환경에서 노드 URL을 ClusterIP 또는 NodePort로 제공해도 되는지 문의했습니다. 시스템 대시보드에서 드라이브 그룹 패널이 데이터 없이 표시되는 이유를 물었습니다.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>모니터링 대시보드가 아직 제공되지 않았고, v3 메트릭을 모든 MinIO 노드에 설정해야 한다는 점을 인식하지 못해 생긴 문제입니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Val Bezrukov는 gziped tar 파일에 포함된 4개의 대시보드와 Prometheus 스크랩 설정 예시를 제공했습니다. 또한 v3 메트릭을 모든 노드에 설정하도록 안내했고, Kubernetes에서 kubernetes_sd_configs를 사용해 자동으로 pod를 탐지하도록 설명했습니다. Shubhendu Ram Tripathi는 ClusterIP가 일반적인 클러스터 수준 메트릭에 적합하며 노드 메트릭은 각 노드를 명시적으로 추가해야 한다고 조언했습니다.</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
+          <t>Val Bezrukov이 gziped tar 파일에 4개의 대시보드를 제공하고, Prometheus 스크랩 설정 예시를 제공했습니다. ClusterIP를 사용하면 클러스터 수준 메트릭을 수집할 수 있고, 노드 메트릭은 모든 노드를 명시적으로 추가하거나 kubernetes_sd_configs를 사용해 자동으로 탐지하도록 설정해야 합니다. 또한 v3 메트릭을 모든 MinIO 노드에 설정해야 대시보드가 정상 동작합니다.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14898</t>
@@ -5213,20 +5674,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>고객은 RHEL10 출시 이후 기존 tuned.conf에 변경이 있었는지와 RHEL10 테스트 중 발생한 이슈 또는 추가 성능 개선 제안을 요청했습니다. 또한, MinIO EOS tuning 문서의 새로운 링크 제공을 요청했습니다.</t>
+          <t>사용자는 RHEL10이 출시되면서 기존 tuned.conf에 변경이 있었는지, RHEL10 테스트 중 발생한 이슈나 추가 성능 개선 제안이 있는지, 그리고 https://github.com/miniohq/eos/tree/master/docs/tuning URL의 새 링크를 제공해 달라고 요청했습니다.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>RHEL10이 5.x에서 6.x 커널로 업그레이드되면서 커널 파라미터 조정이 필요할 수 있다고 우려하며, 서버 벤더 정보가 불확실해 최적화를 진행하기 어려웠습니다.</t>
+          <t>사용자는 RHEL10이 5.x 커널에서 6.x 커널로 업그레이드되었으므로 커널 파라미터 조정이 필요할 수 있다고 우려했습니다.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>새 커널은 대부분의 조정이 필요 없으며, 필요 시 TCP 버퍼를 조정해 네트워크 softirq를 줄일 수 있습니다. 기본 tuned-adm 설정을 사용하고, 환경에 맞게 커스텀 조정하면 됩니다.</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
+          <t>Harshavardhana는 최신 커널이 크게 조정이 필요 없으며, 일반적인 tuned-adm 권장 사항이 대부분의 워크로드에 적용된다고 설명했습니다. 또한 대용량 전송 시 TCP 버퍼 조정이 소프트IRQ를 줄이는 데 도움이 될 수 있다고 제안했습니다.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14886</t>
@@ -5264,20 +5729,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>고객은 KES 또는 minKMS를 사용해 Kubernetes 비밀을 암호화하고 객체 저장소에 저장한 뒤 사용하는 것이 적절한지 문의했습니다.</t>
+          <t>고객이 Kubernetes secrets나 credentials를 KES에 저장할 수 있는지, 아니면 다른 방법을 권장하는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>고객은 KES가 암호화 키를 저장하고 객체를 암호화/복호화만 수행하므로, 비밀 정보를 저장하기에 적합한지에 대해 혼란을 느꼈습니다.</t>
+          <t>KES는 stateless 서버이며, KMS 키를 캐시해 객체 암호화/복호화에 사용되며, 실제 데이터 저장을 위한 기능이 아님.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Andreas는 KES가 데이터를 저장하지 않으며, 대신 비밀을 KES 또는 minKMS로 암호화한 뒤 신뢰할 수 없는 저장소에 보관하고 필요할 때 다시 복호화하도록 권장했습니다.</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
+          <t>비밀을 KES 또는 MinKMS로 암호화한 뒤 객체 저장소에 저장하고, 필요 시 복호화하여 사용한다. 비밀이 객체 저장소에서 사용되지 않는 한 저장해도 된다.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14871</t>
@@ -5310,21 +5779,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>고객이 AIStor 콘솔의 디버그 섹션에서 성능 테스트를 실행할 때, 하나의 ObjectStore 노드만 성능 지표를 보고하고 나머지 노드가 인증 실패 메시지를 반환하는 문제를 해결하고자 합니다.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Youngkyoo Kim이 AIStor Console의 성능 테스트에서 대부분의 ObjectStore 노드가 인증 실패 메시지를 반환하고, 단일 노드만 성능 지표를 보고하며, TLS 여부와 관계없이 발생하는 문제를 해결해 달라고 요청했습니다.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>AIStor Console 성능 테스트에서 인증 실패가 발생한 것은 버그로, 2025-08-29 릴리스에서 수정되었습니다.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>최신 이미지를 적용한 RELEASE.2025-08-29T21-27-49Z 버전에서 이 문제가 해결되었습니다. 업데이트 후 테스트를 재실행하면 모든 노드에서 성능 지표를 정상적으로 받을 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
+          <t>RELEASE.2025-08-29T21-27-49Z 최신 이미지를 적용하여 문제를 해결했습니다.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14854</t>
@@ -5362,20 +5839,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>고객이 물리적 디스크가 동일한 에러레이션 세트에 속하는지를 확인하고 싶어 한다.</t>
+          <t>사용자는 물리 디스크가 동일한 복원 집합에 속하는지 확인하고, 여러 디스크가 실패했을 때 디스크가 속한 복원 집합을 식별하는 방법을 찾고 싶어합니다.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>여러 디스크가 동시에 고장났을 때 어떤 세트에 속하는지를 식별하기 위해 필요했다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>mc admin info &lt;ALIAS&gt; --json 명령어와 jq 스크립트를 사용해 엔드포인트, 풀 인덱스, 세트 인덱스, 디스크 인덱스를 출력하고 정렬하면 세트 정보를 알 수 있다. 또한 mc admin drive top &lt;alias&gt; 명령으로 같은 정보를 확인할 수 있다.</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr"/>
+          <t>mc admin info &lt;alias&gt; --json 명령을 실행하고, jq를 사용해 endpoint, pool_index, set_index, disk_index를 추출한 뒤 정렬하면 각 디스크가 속한 복원 집합 정보를 확인할 수 있습니다. 또한 mc admin drive top &lt;alias&gt; 명령으로도 같은 정보를 얻을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14810</t>
@@ -5413,20 +5894,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>고객은 CONNECT 사이트에서 이슈 상세 페이지를 열거나 새 이슈를 만들 때 웹소켓 연결이 실패해 내용이 로드되지 않는 문제를 해결하기 위해 필요한 도메인과 포트를 알려달라고 요청했습니다.</t>
+          <t>고객은 CONNECT 사이트에서 이슈 상세 페이지를 열거나 새 이슈를 작성할 때 필요한 도메인과 포트를 방화벽에 열어야 한다는 목록을 요청했습니다.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>개인 PC에서 Twilio의 웹소켓 서버(wss://tsock.us1.twilio.com/v3/wsconnect)에 접근이 차단되어 페이지가 비정상적으로 로드되고, 브라우저 콘솔에 연결 오류 메시지가 반복적으로 표시됩니다.</t>
+          <t>문제는 CONNECT가 Twilio의 웹소켓 서비스에 연결하지 못해 이슈 상세 페이지가 로드되지 않는 것으로 보입니다.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>서버에 subnet.min.io(443)와 tsock.us1.twilio.com(443) 도메인을 화이트리스트에 추가하면 웹소켓 연결이 정상적으로 동작합니다.</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr"/>
+          <t>방화벽에서 subnet.min.io(443)과 tsock.us1.twilio.com(443) 도메인을 허용하면 문제를 해결할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14795</t>
@@ -5464,18 +5949,22 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>사용자는 AIStore 환경을 Kubernetes 클러스터가 완전히 파괴되었을 때 데이터 손실 없이 재구축할 수 있는 절차와 정확한 단계 및 필요한 백업 항목을 알고 싶어합니다.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>고객이 AIStore 환경을 Kubernetes 클러스터가 완전히 파괴된 경우 데이터 손실 없이 재구축할 수 있는지와 재구축 절차를 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>클러스터가 완전히 파괴되어 데이터 복구가 필요한 상황이 발생했습니다.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>DirectPV와 관련된 CRDs(directpvdrives, directpvvolumes), ObjectStore, PVC, PV, Secret을 kubectl 또는 Velero로 백업하고, 클러스터를 재구축 후 같은 노드 이름으로 오퍼레이터와 ObjectStore를 재설치하면 기존 볼륨을 재사용하여 데이터가 복구됩니다.</t>
+          <t>CRDs(DirectPVDrive, DirectPVVolume, ObjectStore), PV, PVC, secrets를 백업하고, 새 클러스터에 Helm으로 Operator와 ObjectStore를 재설치한 뒤, 백업한 리소스를 적용하면 DirectPV가 드라이브를 올바른 노드에 연결해 데이터가 복구됩니다.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>백업은 AIStore namespace의 모든 리소스를 포함하고, 노드 이름을 동일하게 지정해야 DirectPV가 드라이브를 올바른 노드에 연결합니다.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5505,22 +5994,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jeeva Kandasamy</t>
+          <t>Jeeva</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>기능 및 사용법(Features &amp; Usage)</t>
+          <t>애플리케이션(Application)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>사용자는 Helm values.yaml에서 certificates.config.dnsNames에 도메인 이름을 추가하는 방법을 묻고, IP 주소를 SAN에 포함할 수 있는지 여부를 문의했습니다.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+          <t>사용자는 Helm values.yaml에 domain names를 certificates.config.dnsNames에 추가하려 했으나 certificate.spec.dnsName 오류가 발생했습니다. 또한 IP 주소를 SAN에 포함할 수 있는지 문의했습니다.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>values.yaml에서 dnsName 대신 dnsNames를 사용하고, config 섹션이 잘못 들여쓰기되어 spec.certificates.dnsNames 필드가 인식되지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Helm 차트 v1.0.5가 배포되어 dnsNames 필드가 올바르게 처리됩니다. 이 버전을 사용하면 domain names를 추가할 수 있지만 IP 주소는 지원되지 않습니다.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14762</t>
@@ -5541,7 +6042,11 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>Jeeva</t>
@@ -5554,20 +6059,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>고객이 최근 버전에서 관측성, 로드 밸런서, 인바운드 트래픽 기능이 UI에서 사라진 이유와 이를 다시 접근할 수 있는 방법을 문의했습니다.</t>
+          <t>User wants clarification on why observability, load balancer, and inbound traffic features are no longer visible in the console UI.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>전역 콘솔이 최신 릴리스에서 제거되었으며, UI에서 구성하던 기능들은 Helm 차트나 ObjectStore Custom Resource를 통해 관리하도록 변경되었습니다. 또한 observability 기능은 v3 메트릭스를 사용해 Prometheus와 Grafana에서 시각화하도록 전환되었습니다.</t>
+          <t>The global console was removed in the recent release, and configuration for features like observability and minwall was moved from the UI to Helm charts or Custom Resources to support automation.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>MinWall 및 기타 기능은 여전히 사용할 수 있으며, MinWall을 포함한 설정은 Helm 차트(예: aistor-objectstore)나 CR에서 구성해야 합니다. 관측성은 Prometheus와 Grafana 대시보드를 활용해 v3 메트릭스로 모니터링하면 됩니다. Global Console이 사라졌으므로, 해당 기능을 사용하려면 aistor 릴리스를 적용하고, 필요한 설정을 Helm 차트에 명시하거나 CR에 정의하십시오.</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>Use the new ObjectStore console UI and configure features via Helm charts or Custom Resources; for observability, use v3 metrics scraped by Prometheus and visualized in Grafana; minwall can still be deployed through Helm or CR.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14754</t>
@@ -5600,21 +6109,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>클러스터 및 운영(Cluster &amp; Operations)</t>
+          <t>기능 및 사용법(Features &amp; Usage)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>고객은 AIStor 문서 위치를 찾는 것부터 시작해, Helm 설치 시 erasure coding 설정과 StorageClass의 재클레임 정책을 Delete에서 Retain으로 변경하는 방법을 요청했습니다. 또한, 클러스터가 완전히 삭제된 경우 Retain 정책 하에서 기존 데이터를 재접근할 수 있는지 여부와 재사용 절차를 확인했습니다.</t>
+          <t>사용자는 AIStor 문서 URL과 Helm을 사용해 Volume Manager를 설치할 때 erasure coding 매개변수와 directpv-min-io StorageClass의 reclaim 정책을 Delete에서 Retain으로 변경하는 방법을 요청했습니다.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Helm 값 파일에서 MINIO_ERASURE_SET_DRIVE_COUNT와 MINIO_STORAGE_CLASS_STANDARD를 operator 컨테이너의 env에 넣었지만 실제 적용은 ObjectStore.spec.env에 설정해야 했습니다. 이로 인해 erasure 설정이 반영되지 않았습니다.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+          <t>문서에서 해당 설정 항목을 찾지 못했고, 환경 변수를 잘못된 위치에 추가했기 때문에 erasure coding 설정이 적용되지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>ObjectStore.spec.env에 MINIO_ERASURE_SET_DRIVE_COUNT와 MINIO_STORAGE_CLASS_STANDARD 환경 변수를 추가한 뒤, 운영체제와 ObjectStore를 업그레이드하면 erasure coding 설정이 반영됩니다. 또한 StorageClass의 reclaimPolicy를 Retain으로 설정하면 PVC 삭제 시 볼륨이 보존됩니다.</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14753</t>
@@ -5652,20 +6169,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Youngkyoo Kim이 AIStor에서 권장되는 버킷 수와 대규모 버킷 수가 성능에 미치는 영향을 묻고 있습니다.</t>
+          <t>고객이 AIStor에서 버킷 수에 대한 권장 사항을 묻고, 100개 이하로 유지해야 하는지, 1000개까지 지원 요청이 가능한지, 5000~10000개 이상 생성 시 가이드라인이 있는지 문의했습니다.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>사용자가 S3의 버킷 제한과 AIStor 적용 가능성을 혼동하여, 5000~10000 버킷 이상을 만들 때의 가이드라인을 찾고 있습니다.</t>
+          <t>Eco와 Alexander는 많은 버킷이 스캐너 프로세스에 부하를 주어 성능 저하를 일으킬 수 있다고 언급했습니다.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>버킷 수를 100 정도의 베이스라인으로 두고, 새로운 마일스톤(예: 1000)마다 감사 프로세스를 도입해 과도한 버킷 생성을 방지합니다. API와 SCANNER 메트릭을 v3 메트릭 엔드포인트를 통해 모니터링하고, 성능 영향을 감지하면 조치를 취합니다. 필요 시 내부 고객과 협력해 버킷 수를 최소화하도록 권고합니다.</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>Alexander는 버킷 수를 낮게 유지하고, 기준(예: 100개) 이후마다 감사 프로세스를 도입하며, API 및 SCANNER 메트릭을 모니터링하도록 권장했습니다.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Eco는 S3의 기본 100개 버킷 제한과 지원 요청 시 1000개까지 가능함을 언급했습니다.</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14738</t>
@@ -5703,20 +6224,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>사용자가 Legacy Pods가 생성되는 것을 방지하고, replicas 설정이 반영되지 않는 현상을 해결하기를 요청했습니다. 또한, 각 질문마다 별도의 Subnet 티켓이 필요한지 물었습니다.</t>
+          <t>Youngkyoo Kim requested guidance on preventing legacy pods from being deployed, ensuring the controller replicas value is respected, and clarification on whether a new subnet issue ticket is needed for each question.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Helm 차트에서 legacyFlag를 false로 설정해도 Legacy Pods가 생성되는 버그가 존재하고, replicas 값이 차트에서 무시되는 버그가 있었습니다.</t>
+          <t>The Helm chart had a bug that caused legacy pods to be created even when legacyFlag was set to false, and it did not honor the replicas value specified in values.yaml.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>업데이트된 aistor-volumemanager 0.2.0 차트를 사용하고 helm repo update를 수행하면 legacyFlag를 지정할 필요가 없으며, replicas 설정이 정상적으로 적용됩니다.</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr"/>
+          <t>An updated AIStor Volume Manager chart (version 0.2.0) was released; after running helm repo update and installing the new chart, legacy pods are no longer created and the replicas setting works as expected.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14689</t>
@@ -5737,17 +6262,41 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
           <t>기능 및 사용법(Features &amp; Usage)</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>https://subnet.min.io/issues/14425</t>
